--- a/dashboard-LNS/LNS_REV_3_limited_metadata.xlsx
+++ b/dashboard-LNS/LNS_REV_3_limited_metadata.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L114"/>
+  <dimension ref="A1:L100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,355 +901,347 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2612367365</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.7202/1039633ar</t>
-        </is>
-      </c>
+          <t>https://openalex.org/W2795511659</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>A/r/tography and Teacher Education in the 21st Century</t>
+          <t>Methods and Procedures in PIRLS 2016.</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>2017</v>
       </c>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>In this article, we summarize research on Prince Edward Island where a Prince Edward Island teacher, identifying as an a/r/tographer, designed a digital and multiliteracies unit, as part of a directed studies course in her Master of Education program. Small in scope, this single participant case study was designed to give a fuller picture to three difficulties teachers often face when teaching new literacies. These are (1) applying multiliteracies theory, (2) thinking across literacies domains, and (3) assessing literacies holistically. Findings are derived from our six research conversations, and our discussion highlights the necessity of artistic ways of being and thinking for teacher education programs in the 21 st century.</t>
-        </is>
-      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>['Sean Wiebe', 'Claire Caseley Smith']</t>
+          <t>['Michael O. Martín', 'Ina V. S. Mullis', 'Martin Hooper']</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>[['University of Prince Edward Island', 'https://ror.org/02xh9x144']]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="K11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://doi.org/10.7202/1039633ar</t>
+          <t>http://files.eric.ed.gov/fulltext/ED580352.pdf</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2612367365</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.7202/1039633ar</t>
-        </is>
-      </c>
+          <t>https://openalex.org/W3048553956</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>A/r/tography and Teacher Education in the 21st Century</t>
+          <t>Where Did Reading Proficiency Improve over Time? PISA in Focus. No. 103.</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>In this article, we summarize research on Prince Edward Island where a Prince Edward Island teacher, identifying as an a/r/tographer, designed a digital and multiliteracies unit, as part of a directed studies course in her Master of Education program. Small in scope, this single participant case study was designed to give a fuller picture to three difficulties teachers often face when teaching new literacies. These are (1) applying multiliteracies theory, (2) thinking across literacies domains, and (3) assessing literacies holistically. Findings are derived from our six research conversations, and our discussion highlights the necessity of artistic ways of being and thinking for teacher education programs in the 21 st century.</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>['Sean Wiebe', 'Claire Caseley Smith']</t>
+          <t>['Francesco Avvisati']</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>[['University of Prince Edward Island', 'https://ror.org/02xh9x144']]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://doi.org/10.7202/1039633ar</t>
+          <t>https://eric.ed.gov/?id=ED605963</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2612367365</t>
+          <t>https://openalex.org/W4220958171</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://doi.org/10.7202/1039633ar</t>
+          <t>https://doi.org/10.7202/1087050ar</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>A/r/tography and Teacher Education in the 21st Century</t>
+          <t>Field Testing A Campus Preparation Mental Health Resource</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>In this article, we summarize research on Prince Edward Island where a Prince Edward Island teacher, identifying as an a/r/tographer, designed a digital and multiliteracies unit, as part of a directed studies course in her Master of Education program. Small in scope, this single participant case study was designed to give a fuller picture to three difficulties teachers often face when teaching new literacies. These are (1) applying multiliteracies theory, (2) thinking across literacies domains, and (3) assessing literacies holistically. Findings are derived from our six research conversations, and our discussion highlights the necessity of artistic ways of being and thinking for teacher education programs in the 21 st century.</t>
+          <t>This research investigated whether a mental health literacy resource could increase Grade 12 students’ mental health literacy. Bachelor of Education students (N = 8) from a university in rural Atlantic Canada created a board game and mental health seminar based on the resource. They applied the resource through the board game and seminar to Grade 12 students at two local high schools. There were positive albeit modest outcomes across a number of measures related to mental health literacy and post-secondary schooling preparation. Participants regarded the resource as helpful, and they were likely to recommend it to their peers. This resource holds promise for supporting students as they transition from high school to post-secondary settings.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>['Sean Wiebe', 'Claire Caseley Smith']</t>
+          <t>['Chris Gilham', 'Yifeng Wei', 'Stan Kutcher', 'Catherine MacIntyre', 'Sharon MacCuspic', 'Wanda Fougere']</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>[['University of Prince Edward Island', 'https://ror.org/02xh9x144']]</t>
+          <t>[['St. Francis Xavier University', 'https://ror.org/01wcaxs37'], ['University of Alberta', 'https://ror.org/0160cpw27'], ['Dalhousie University', 'https://ror.org/01e6qks80'], ['St. Francis Xavier University', 'https://ror.org/01wcaxs37'], ['St. Francis Xavier University', 'https://ror.org/01wcaxs37']]</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K13" t="b">
         <v>1</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://doi.org/10.7202/1039633ar</t>
+          <t>https://doi.org/10.7202/1087050ar</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2795511659</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>https://openalex.org/W3094932340</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1080/02601370.2020.1836052</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Methods and Procedures in PIRLS 2016.</t>
+          <t>Varieties of employment: a comparison of skill-based activities at work among youth and young adults in Canada</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>According to practice engagement theory within the field of adult education, everyday workplace activities offer an opportunity for skill development among youth and young adults; yet, prior research highlights the prevalence of routine and low-skill work within entry-level jobs. Utilising data from the Programme for the International Assessment of Adult Competencies (PIAAC), the objective of the following study is to demonstrate how workplace literacy, numeracy, and problem-solving activities differ among people aged 16 to 34 in Canada. Latent class analysis provides a typology of literacy, numeracy, and problem-solving activities at work and generates insight into how socio-demographic and employment factors are associated with each group. The findings highlight that employment cannot be uniformly characterised as low-skill. Rather, there are unique employment groups with differing literacy, numeracy, and problem-solving activity characteristics. Nevertheless, socio-demographic factors do matter for gaining access to employment that involves daily skill-based activities. While age, parental education, immigration background, and education level are significantly associated with the latent classes, economic and employment characteristics reduce the magnitude of these associations. Together, the results suggest that access to skill-based activities at work are more or less accessible for certain groups and connect to other aspects of early-career job quality and occupational segregation.</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>['Michael O. Martín', 'Ina V. S. Mullis', 'Martin Hooper']</t>
+          <t>['Ashley Pullman', 'Michelle Y. Chen']</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[['University of Ottawa', 'https://ror.org/03c4mmv16']]</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>76</v>
+        <v>4</v>
       </c>
       <c r="K14" t="b">
         <v>0</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>http://files.eric.ed.gov/fulltext/ED580352.pdf</t>
+          <t>https://doi.org/10.1080/02601370.2020.1836052</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://openalex.org/W3048553956</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>https://openalex.org/W2342001105</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/ets2.12097</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Where Did Reading Proficiency Improve over Time? PISA in Focus. No. 103.</t>
+          <t>The Prediction of Labor Force Status: Implications From International Adult Skill Assessments</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>This report investigates the prediction of labor force status using observed variables, such as gender, age, and immigrant status, and more importantly, measured skill variables, including literacy proficiency and a categorical rating of educational attainment based on the 1994 International Adult Literacy Survey (IALS), the 2003 Adult Literacy and Life Skills Survey (ALL), and the 2011 Programme for the International Assessment of Adult Competencies (PIAAC) projects. We explored the regression relations in the past two decades for six trend countries and subnational regions that provide data for all assessments: the United States, Norway, the Netherlands, Italy, Canada's English-speaking region, and Canada's French-speaking region. Probit regression models with latent predictors were used in this cross-sectional study to investigate how those variables are structurally related to labor market outcomes. Results show the importance of literacy proficiency and education in determining individuals' labor force status across countries/regions, but with key differences among these countries/regions.</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>['Francesco Avvisati']</t>
+          <t>['Tongyun Li', 'Matthias von Davier', 'Gregory R. Hancock', 'Irwin S. Kirsch']</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[['Educational Testing Service', 'https://ror.org/03b5q4637'], ['Educational Testing Service', 'https://ror.org/03b5q4637'], ['University of Maryland, College Park', 'https://ror.org/047s2c258'], ['Educational Testing Service', 'https://ror.org/03b5q4637']]</t>
         </is>
       </c>
       <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="b">
         <v>1</v>
       </c>
-      <c r="K15" t="b">
-        <v>0</v>
-      </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://eric.ed.gov/?id=ED605963</t>
+          <t>https://doi.org/10.1002/ets2.12097</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://openalex.org/W4220958171</t>
+          <t>https://openalex.org/W1983406153</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://doi.org/10.7202/1087050ar</t>
+          <t>https://doi.org/10.1080/09500693.2013.871658</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Field Testing A Campus Preparation Mental Health Resource</t>
+          <t>Science Engagement and Literacy: A retrospective analysis for students in Canada and Australia</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2022</v>
+        <v>2013</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>This research investigated whether a mental health literacy resource could increase Grade 12 students’ mental health literacy. Bachelor of Education students (N = 8) from a university in rural Atlantic Canada created a board game and mental health seminar based on the resource. They applied the resource through the board game and seminar to Grade 12 students at two local high schools. There were positive albeit modest outcomes across a number of measures related to mental health literacy and post-secondary schooling preparation. Participants regarded the resource as helpful, and they were likely to recommend it to their peers. This resource holds promise for supporting students as they transition from high school to post-secondary settings.</t>
+          <t>Given international concerns about students' pursuit (or more correctly, non-pursuit) of courses and careers in science, technology, engineering and mathematics, this study is about achieving a better understanding of factors related to high school students' engagement in science. The study builds on previous secondary analyses of Programme for International Student Assessment (PISA) datasets for New Zealand and Australia. For the current study, we compared patterns of science engagement and science literacy for male and female students in Canada and Australia. The study's secondary analysis revealed that for all PISA measures included under the conceptual umbrella of engagement in science (i.e. interest, enjoyment, valuing, self-efficacy, self-concept and motivation), 15-year-old students in Australia lagged their Canadian counterparts to varying, albeit modest, degrees. Our retrospective analysis further shows, however, that gender equity in science engagement and science literacy is evident in both Canadian and Australian contexts. Additionally, and consistent with our previous findings for indigenous and non-indigenous students in New Zealand and Australia, we found that for male and female students in both countries, the factor most strongly associated with variations in engagement in science was the extent to which students participate in science activities outside of school. In contrast, and again for both Canadian and Australian students, the factors most strongly associated with science literacy were students' socioeconomic backgrounds, and the amount of formal time spent doing science. The implications of these results for science educators and researchers are discussed.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>['Chris Gilham', 'Yifeng Wei', 'Stan Kutcher', 'Catherine MacIntyre', 'Sharon MacCuspic', 'Wanda Fougere']</t>
+          <t>['Amanda Woods‐McConney', 'Mary Oliver', 'A. McConney', 'Renato Schibeci', 'Dorit Maor']</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>[['St. Francis Xavier University', 'https://ror.org/01wcaxs37'], ['University of Alberta', 'https://ror.org/0160cpw27'], ['Dalhousie University', 'https://ror.org/01e6qks80'], ['St. Francis Xavier University', 'https://ror.org/01wcaxs37'], ['St. Francis Xavier University', 'https://ror.org/01wcaxs37']]</t>
+          <t>[['Murdoch University', 'https://ror.org/00r4sry34'], ['The University of Western Australia', 'https://ror.org/047272k79'], ['Murdoch University', 'https://ror.org/00r4sry34'], ['Murdoch University', 'https://ror.org/00r4sry34'], ['Murdoch University', 'https://ror.org/00r4sry34']]</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="K16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://doi.org/10.7202/1087050ar</t>
+          <t>https://doi.org/10.1080/09500693.2013.871658</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://openalex.org/W3094932340</t>
+          <t>https://openalex.org/W1990092605</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/02601370.2020.1836052</t>
+          <t>https://doi.org/10.1016/j.compedu.2014.01.010</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Varieties of employment: a comparison of skill-based activities at work among youth and young adults in Canada</t>
+          <t>Promoting reading comprehension with the use of technology</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2020</v>
+        <v>2014</v>
       </c>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>According to practice engagement theory within the field of adult education, everyday workplace activities offer an opportunity for skill development among youth and young adults; yet, prior research highlights the prevalence of routine and low-skill work within entry-level jobs. Utilising data from the Programme for the International Assessment of Adult Competencies (PIAAC), the objective of the following study is to demonstrate how workplace literacy, numeracy, and problem-solving activities differ among people aged 16 to 34 in Canada. Latent class analysis provides a typology of literacy, numeracy, and problem-solving activities at work and generates insight into how socio-demographic and employment factors are associated with each group. The findings highlight that employment cannot be uniformly characterised as low-skill. Rather, there are unique employment groups with differing literacy, numeracy, and problem-solving activity characteristics. Nevertheless, socio-demographic factors do matter for gaining access to employment that involves daily skill-based activities. While age, parental education, immigration background, and education level are significantly associated with the latent classes, economic and employment characteristics reduce the magnitude of these associations. Together, the results suggest that access to skill-based activities at work are more or less accessible for certain groups and connect to other aspects of early-career job quality and occupational segregation.</t>
-        </is>
-      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>['Ashley Pullman', 'Michelle Y. Chen']</t>
+          <t>['Larysa Lysenko', 'Philip C. Abrami']</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>[['University of Ottawa', 'https://ror.org/03c4mmv16']]</t>
+          <t>[['Concordia University', 'https://ror.org/0420zvk78'], ['Concordia University', 'https://ror.org/0420zvk78']]</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="K17" t="b">
         <v>0</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/02601370.2020.1836052</t>
+          <t>https://doi.org/10.1016/j.compedu.2014.01.010</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2342001105</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1002/ets2.12097</t>
-        </is>
-      </c>
+          <t>https://openalex.org/W2548469526</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>The Prediction of Labor Force Status: Implications From International Adult Skill Assessments</t>
+          <t>NOTIONS OF LITERACY IN THE K–12 SCHOOL SYSTEM IN BRITISH COLUMBIA EDUCATION SINCE 2002: A CONTESTED TERRAIN</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1258,140 +1250,132 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>This report investigates the prediction of labor force status using observed variables, such as gender, age, and immigrant status, and more importantly, measured skill variables, including literacy proficiency and a categorical rating of educational attainment based on the 1994 International Adult Literacy Survey (IALS), the 2003 Adult Literacy and Life Skills Survey (ALL), and the 2011 Programme for the International Assessment of Adult Competencies (PIAAC) projects. We explored the regression relations in the past two decades for six trend countries and subnational regions that provide data for all assessments: the United States, Norway, the Netherlands, Italy, Canada's English-speaking region, and Canada's French-speaking region. Probit regression models with latent predictors were used in this cross-sectional study to investigate how those variables are structurally related to labor market outcomes. Results show the importance of literacy proficiency and education in determining individuals' labor force status across countries/regions, but with key differences among these countries/regions.</t>
+          <t>Developing literacy competencies has become a central component of educational policy in British Columbia (BC), with policies calling for province-wide assessment and school accountability. Based on the critical policy analysis (Blaikie &amp; Soussan, 2000) of provincial and school district documents, complemented by semi-structured interviews of senior government officials, district-based administrators, and literacy coordinators, this article discusses how the synergistic effect of the policy discourses of accountability and assessment framed the ways of thinking, conceptually and practically, about literacy mainly in terms of its instrumental value in holding public schools accountable to performance indicators. The article concludes by discussing the necessity of redefining literacy to challenge the view of literacy as a mere set of technical and human skills for economic growth to shift the dialogue toward policy alternatives that view literacy as set of capabilities for sociocultural and political change.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>['Tongyun Li', 'Matthias von Davier', 'Gregory R. Hancock', 'Irwin S. Kirsch']</t>
+          <t>['Jeff Park', 'Gérald Fallon']</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>[['Educational Testing Service', 'https://ror.org/03b5q4637'], ['Educational Testing Service', 'https://ror.org/03b5q4637'], ['University of Maryland, College Park', 'https://ror.org/047s2c258'], ['Educational Testing Service', 'https://ror.org/03b5q4637']]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/ets2.12097</t>
+          <t>https://files.eric.ed.gov/fulltext/EJ1111582.pdf</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://openalex.org/W1983406153</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1080/09500693.2013.871658</t>
-        </is>
-      </c>
+          <t>https://openalex.org/W3177421727</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Science Engagement and Literacy: A retrospective analysis for students in Canada and Australia</t>
+          <t>Multiple Perspectives on Digital Literacies Research Methods in Canada.</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2013</v>
+        <v>2020</v>
       </c>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Given international concerns about students' pursuit (or more correctly, non-pursuit) of courses and careers in science, technology, engineering and mathematics, this study is about achieving a better understanding of factors related to high school students' engagement in science. The study builds on previous secondary analyses of Programme for International Student Assessment (PISA) datasets for New Zealand and Australia. For the current study, we compared patterns of science engagement and science literacy for male and female students in Canada and Australia. The study's secondary analysis revealed that for all PISA measures included under the conceptual umbrella of engagement in science (i.e. interest, enjoyment, valuing, self-efficacy, self-concept and motivation), 15-year-old students in Australia lagged their Canadian counterparts to varying, albeit modest, degrees. Our retrospective analysis further shows, however, that gender equity in science engagement and science literacy is evident in both Canadian and Australian contexts. Additionally, and consistent with our previous findings for indigenous and non-indigenous students in New Zealand and Australia, we found that for male and female students in both countries, the factor most strongly associated with variations in engagement in science was the extent to which students participate in science activities outside of school. In contrast, and again for both Canadian and Australian students, the factors most strongly associated with science literacy were students' socioeconomic backgrounds, and the amount of formal time spent doing science. The implications of these results for science educators and researchers are discussed.</t>
-        </is>
-      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>['Amanda Woods‐McConney', 'Mary Oliver', 'A. McConney', 'Renato Schibeci', 'Dorit Maor']</t>
+          <t>['Michelle Schira Hagerman', 'Pamela Beach', 'Megan Cotnam-Kappel', 'Cristyne Hébert']</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>[['Murdoch University', 'https://ror.org/00r4sry34'], ['The University of Western Australia', 'https://ror.org/047272k79'], ['Murdoch University', 'https://ror.org/00r4sry34'], ['Murdoch University', 'https://ror.org/00r4sry34'], ['Murdoch University', 'https://ror.org/00r4sry34']]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="K19" t="b">
         <v>0</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/09500693.2013.871658</t>
+          <t>https://files.eric.ed.gov/fulltext/EJ1278419.pdf</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://openalex.org/W1990092605</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.compedu.2014.01.010</t>
-        </is>
-      </c>
+          <t>https://openalex.org/W2761186951</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Promoting reading comprehension with the use of technology</t>
+          <t>Making Sense of the Performance (Dis)advantage for Immigrant Students Across Canada</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>International achievement measures such as the Programme for International Student Assessment (PISA) have traditionally reported a significant gap between non-migrant and immigrant student groups—a result that is often referred to as the immigrant performance disadvantage . This article examines first- and second-generation immigrant student achievement results in greater detail across Canada. Overall, Canadian achieve ment results are atypical in relation to the international community in that immigrant student groups significantly outperform non-migrants in some provincial jurisdictions, and also significantly underperform in other provincial jurisdictions, in relation to reading, mathematics, and scientific literacy. This article examines these diverse results in relation to the available literature and offers a conceptual framework that explains the unique case of Canada. The framework highlights the importance of assessing immigrant student achievement by taking into account the level of individual characteristics, provincial policies, as well as sociocultural and demographic contexts across Canada.</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>['Larysa Lysenko', 'Philip C. Abrami']</t>
+          <t>['Louis Volante', 'Don A. Klinger', 'Özge Bilgili', 'Melissa Siegel']</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>[['Concordia University', 'https://ror.org/0420zvk78'], ['Concordia University', 'https://ror.org/0420zvk78']]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="K20" t="b">
         <v>0</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.compedu.2014.01.010</t>
+          <t>http://files.eric.ed.gov/fulltext/EJ1157248.pdf</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2548469526</t>
+          <t>https://openalex.org/W2520023658</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NOTIONS OF LITERACY IN THE K–12 SCHOOL SYSTEM IN BRITISH COLUMBIA EDUCATION SINCE 2002: A CONTESTED TERRAIN</t>
+          <t>Language Assessment Literacy as Professional Competence: The Case of Canadian Admissions Decision Makers</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1400,1490 +1384,1518 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Developing literacy competencies has become a central component of educational policy in British Columbia (BC), with policies calling for province-wide assessment and school accountability. Based on the critical policy analysis (Blaikie &amp; Soussan, 2000) of provincial and school district documents, complemented by semi-structured interviews of senior government officials, district-based administrators, and literacy coordinators, this article discusses how the synergistic effect of the policy discourses of accountability and assessment framed the ways of thinking, conceptually and practically, about literacy mainly in terms of its instrumental value in holding public schools accountable to performance indicators. The article concludes by discussing the necessity of redefining literacy to challenge the view of literacy as a mere set of technical and human skills for economic growth to shift the dialogue toward policy alternatives that view literacy as set of capabilities for sociocultural and political change.</t>
+          <t>Abstract This language assessment literacy project involves the collaboration of assessment professionals and admissions officers at higher education institutions across Canada. Following a survey with 20 institutions (Baker, Tsushima, &amp; Wang, 2014), workshops were held at eight institutions across the country dealing with the use of language test scores in university admissions decision making. Recordings of these workshops were analyzed within the typology of workplace knowledge developed by Eraut and his colleagues (Eraut 1994, 2000, 2004a, 2004b; McKee &amp; Eraut, 2012). In addition, participants commented on the usefulness of the workshop materials for their work responsibilities. Results provided insights into a) the language assessment literacy (LAL) base needed for these specific users, including both propositional and procedural components, and b) the possibilities of conceptualizing LAL for these score users as a type of professional workplace competence. Resume Ce projet de sensibilisation en evaluation linguistique a ete effectue avec la collaboration de professionnels de l’evaluation et de responsables des admissions dans les etablissements d’enseignement superieur a travers le Canada. Suite a un sondage effectue aupres de 20 institutions (Baker, Tsushima et Wang, 2014), des ateliers ont ete organises dans huit etablissements a travers le pays traitant de l’utilisation des resultats des tests de langue dans la prise des decisions d’admission. Les enregistrements de ces ateliers ont ete analyses dans la typologie des connaissances en milieu de travail developpe par Eraut et ses collegues (Eraut, 1994, 2000, 2004a, 2004b ; McKee et Eraut, 2012). Les participants ont formule des observations sur l’utilite du materiel d’atelier pour leurs responsabilites professionnelles. Les resultats nous aident a mieux comprendre a) les notions en evaluation de langues les plus pertinentes pour ces utilisateurs specifiques et b) le potentiel de concevoir la « litteratie en evaluation » comme etant un type de competence professionnelle en milieu de travail.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>['Jeff Park', 'Gérald Fallon']</t>
+          <t>['Beverly Baker']</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[['University of Ottawa', 'https://ror.org/03c4mmv16']]</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K21" t="b">
         <v>0</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>https://files.eric.ed.gov/fulltext/EJ1111582.pdf</t>
+          <t>https://doaj.org/article/691bd3989c59430ba70f84b178daf87a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://openalex.org/W3177421727</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>https://openalex.org/W2015223621</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1080/15434303.2014.981334</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Multiple Perspectives on Digital Literacies Research Methods in Canada.</t>
+          <t>Interpreting the Impact of the Ontario Secondary School Literacy Test on Second Language Students Within an Argument-Based Validation Framework</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>AbstractThis article draws on Kane's (2006) argument-based validation framework to synthesize evidence derived from a large-scale, mixed-method explanatory study on the impact of the Ontario Secondary School Literacy Test (OSSLT) on second language (L2) students. The purpose of the OSSLT is to ensure that students have acquired the essential reading and writing skills that apply to all subject areas in the Ontario provincial curriculum up to the end of Grade 9 in Canada. Kane's framework is used both to specify the proposed interpretations and uses of the OSSLT results by laying out the network of inferences and assumptions involved in this test and to elaborate whether the proposed interpretations and uses have been supported by empirical evidence from the study. Findings from the study show that the results of the OSSLT, a test constructed and normed for first language English speakers, should be interpreted differently and with caution for second language students. By synthesizing the empirical evidence within an argument-based validation framework, we can fully understand the impact of the OSSLT in relation to test design, test accommodation, and literacy classroom practices in the Canadian context. Notes1 This study was supported by a standard research grant from the Social Sciences and Humanities Research Council (SSHRC) of Canada.2 In this article we use L2 students in a broad sense. According to the recent Ontario Ministry of Education document, English as a Second Language (ESL) / English Literacy Development (ELD) students are referred to as English Language Learners (ELLs). A detailed definition of the six categories of ELLs can be found in Ontario Ministry of Education (Citation2007).3 Facets of the OSSLT item formats, text types, skills and strategies of reading and the four writing tasks are italicized in the paper as they are defined by EQAO.</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>['Michelle Schira Hagerman', 'Pamela Beach', 'Megan Cotnam-Kappel', 'Cristyne Hébert']</t>
+          <t>['Liying Cheng', 'Youyi Sun']</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[["Queen's University", 'https://ror.org/02y72wh86'], ["Queen's University", 'https://ror.org/02y72wh86']]</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="K22" t="b">
         <v>0</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>https://files.eric.ed.gov/fulltext/EJ1278419.pdf</t>
+          <t>https://doi.org/10.1080/15434303.2014.981334</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2761186951</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>https://openalex.org/W4200527048</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1177/10451595211046971</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Making Sense of the Performance (Dis)advantage for Immigrant Students Across Canada</t>
+          <t>Individual Learning Accounts: A Comparison of Implemented and Proposed Initiatives</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>International achievement measures such as the Programme for International Student Assessment (PISA) have traditionally reported a significant gap between non-migrant and immigrant student groups—a result that is often referred to as the immigrant performance disadvantage . This article examines first- and second-generation immigrant student achievement results in greater detail across Canada. Overall, Canadian achieve ment results are atypical in relation to the international community in that immigrant student groups significantly outperform non-migrants in some provincial jurisdictions, and also significantly underperform in other provincial jurisdictions, in relation to reading, mathematics, and scientific literacy. This article examines these diverse results in relation to the available literature and offers a conceptual framework that explains the unique case of Canada. The framework highlights the importance of assessing immigrant student achievement by taking into account the level of individual characteristics, provincial policies, as well as sociocultural and demographic contexts across Canada.</t>
+          <t>Access to lifelong learning opportunities has long been discussed in terms of the economic benefits conferred by access to and engagement in further education by members of the labor force, particularly within the global knowledge economy. However, equitable access to lifelong education opportunities, particularly for low-skilled adults in the labor force, has been lacking. The Organisation for Economic Cooperation and Development (OECD) identified three models for funding adult learning: (1) individual learning accounts, (2) individual savings accounts, and (3) training vouchers. The current study discusses examples of these models, either proposed or implemented, across four countries or economic blocks—France, Canada, the United Kingdom, and the United States. In addition, to understand the importance of providing funding for education and training to adults with low levels literacy skills, we use data from the Program for the International Assessment for Adult Competencies (PIAAC) to compare participation in adult education and training (AET) by literacy skill levels. In all countries examined, adults with low literacy skills participated in AET at lower rates than those with middle and high levels of literacy skills. To be successful in reaching adults most in need of skill upgrading, financing models need to provide adequate funds for meaningful skill upgrades, have well-structured information sources (e.g., websites) that are easily navigated by the target population, and include policies to screen educational providers for program quality.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>['Louis Volante', 'Don A. Klinger', 'Özge Bilgili', 'Melissa Siegel']</t>
+          <t>['Phyllis Cummins', 'A. Katherine Harrington', 'Takashi Yamashita']</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[['Miami University', 'https://ror.org/05nbqxr67'], ['Scripps (United States)', 'https://ror.org/04x9v7g36'], ['Scripps Institution of Oceanography', 'https://ror.org/04v7hvq31'], ['University of Akron', 'https://ror.org/02kyckx55'], ['University of Maryland, Baltimore', 'https://ror.org/04rq5mt64']]</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="K23" t="b">
         <v>0</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>http://files.eric.ed.gov/fulltext/EJ1157248.pdf</t>
+          <t>https://doi.org/10.1177/10451595211046971</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2520023658</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>https://openalex.org/W3096522693</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s11125-020-09519-5</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Language Assessment Literacy as Professional Competence: The Case of Canadian Admissions Decision Makers</t>
+          <t>Increasing physical literacy in youth: A two-week Sport for Development program for children aged 6-10</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2016</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
+        <v>2020</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>cc-by</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Abstract This language assessment literacy project involves the collaboration of assessment professionals and admissions officers at higher education institutions across Canada. Following a survey with 20 institutions (Baker, Tsushima, &amp; Wang, 2014), workshops were held at eight institutions across the country dealing with the use of language test scores in university admissions decision making. Recordings of these workshops were analyzed within the typology of workplace knowledge developed by Eraut and his colleagues (Eraut 1994, 2000, 2004a, 2004b; McKee &amp; Eraut, 2012). In addition, participants commented on the usefulness of the workshop materials for their work responsibilities. Results provided insights into a) the language assessment literacy (LAL) base needed for these specific users, including both propositional and procedural components, and b) the possibilities of conceptualizing LAL for these score users as a type of professional workplace competence. Resume Ce projet de sensibilisation en evaluation linguistique a ete effectue avec la collaboration de professionnels de l’evaluation et de responsables des admissions dans les etablissements d’enseignement superieur a travers le Canada. Suite a un sondage effectue aupres de 20 institutions (Baker, Tsushima et Wang, 2014), des ateliers ont ete organises dans huit etablissements a travers le pays traitant de l’utilisation des resultats des tests de langue dans la prise des decisions d’admission. Les enregistrements de ces ateliers ont ete analyses dans la typologie des connaissances en milieu de travail developpe par Eraut et ses collegues (Eraut, 1994, 2000, 2004a, 2004b ; McKee et Eraut, 2012). Les participants ont formule des observations sur l’utilite du materiel d’atelier pour leurs responsabilites professionnelles. Les resultats nous aident a mieux comprendre a) les notions en evaluation de langues les plus pertinentes pour ces utilisateurs specifiques et b) le potentiel de concevoir la « litteratie en evaluation » comme etant un type de competence professionnelle en milieu de travail.</t>
+          <t>Abstract Regular physical activity significantly improves health outcomes, yet rates of childhood physical activity remain alarmingly low. Physical literacy has been identified as the foundation for quality physical education, suggesting that sport, education, and public health interventions should seek to increase physical literacy to promote physical activity. A two-week day camp program for children aged 6–10 facing barriers to positive development, was developed and delivered by a Sport for Development facility in Toronto, Canada. Utilizing fundamental movement skills (FMS) as a teaching tool and a pre- and post-assessment, the camp aimed to increase physical literacy and promote engagement in physical activity. Results indicate a significant increase in FMS (t (44) = 4.37, p &amp;lt; .001) as well as improved self-perceptions of physical literacy (t (40) = 14.96, p &amp;lt; .001). The largest FMS increases were found in running and balance and the most significant impacts were among low baseline performers.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>['Beverly Baker']</t>
+          <t>['Marika Warner', 'Jackie Robinson', 'Bryan Heal', 'Jenny Lloyd', 'James Mandigo', 'Bess Lennox', 'Larkin Davenport Huyer']</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>[['University of Ottawa', 'https://ror.org/03c4mmv16']]</t>
+          <t>[['Wilfrid Laurier University', 'https://ror.org/00fn7gb05'], ['University of the Fraser Valley', 'https://ror.org/04h6w7946'], ["Queen's University", 'https://ror.org/02y72wh86']]</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>https://doaj.org/article/691bd3989c59430ba70f84b178daf87a</t>
+          <t>https://doi.org/10.1007/s11125-020-09519-5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2015223621</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1080/15434303.2014.981334</t>
-        </is>
-      </c>
+          <t>https://openalex.org/W3166747656</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Interpreting the Impact of the Ontario Secondary School Literacy Test on Second Language Students Within an Argument-Based Validation Framework</t>
+          <t>Evaluating Ocean Perceptions and Ocean Values: The Canadian Ocean Literacy Survey</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>AbstractThis article draws on Kane's (2006) argument-based validation framework to synthesize evidence derived from a large-scale, mixed-method explanatory study on the impact of the Ontario Secondary School Literacy Test (OSSLT) on second language (L2) students. The purpose of the OSSLT is to ensure that students have acquired the essential reading and writing skills that apply to all subject areas in the Ontario provincial curriculum up to the end of Grade 9 in Canada. Kane's framework is used both to specify the proposed interpretations and uses of the OSSLT results by laying out the network of inferences and assumptions involved in this test and to elaborate whether the proposed interpretations and uses have been supported by empirical evidence from the study. Findings from the study show that the results of the OSSLT, a test constructed and normed for first language English speakers, should be interpreted differently and with caution for second language students. By synthesizing the empirical evidence within an argument-based validation framework, we can fully understand the impact of the OSSLT in relation to test design, test accommodation, and literacy classroom practices in the Canadian context. Notes1 This study was supported by a standard research grant from the Social Sciences and Humanities Research Council (SSHRC) of Canada.2 In this article we use L2 students in a broad sense. According to the recent Ontario Ministry of Education document, English as a Second Language (ESL) / English Literacy Development (ELD) students are referred to as English Language Learners (ELLs). A detailed definition of the six categories of ELLs can be found in Ontario Ministry of Education (Citation2007).3 Facets of the OSSLT item formats, text types, skills and strategies of reading and the four writing tasks are italicized in the paper as they are defined by EQAO.</t>
+          <t>This paper describes the development, validation, and key findings of the Canadian Ocean Literacy Survey. Led by the Canadian Ocean Literacy Coalition (COLC) and its research partners, this survey was developed as part of a Canada-wide, mixed methods research initiative examining how ocean literacy is understood and practised across different regions and sectors. The survey included items linked to ocean perceptions, values, and actions as reported by two categories of Canadian respondents: “ocean-engaged” (n=1,359) and “general public” (n=1,010). The survey objectives were as follows: to determine if Canadians would identify Canada as an “ocean nation”; to uncover meaningful patterns in ocean awareness, perceptions, and values by region and subgroups; and to better understand Canadians’ emotional connections to, and relationship with, the ocean, as well as their behavioural intentions and actions.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>['Liying Cheng', 'Youyi Sun']</t>
+          <t>['Lisa Glithero', 'David B. Zandvliet']</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>[["Queen's University", 'https://ror.org/02y72wh86'], ["Queen's University", 'https://ror.org/02y72wh86']]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="K25" t="b">
         <v>0</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/15434303.2014.981334</t>
+          <t>https://cjee.lakeheadu.ca/article/download/1775/1012</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://openalex.org/W4200527048</t>
+          <t>https://openalex.org/W2948994296</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1177/10451595211046971</t>
+          <t>https://doi.org/10.18666/tpe-2019-v76-i3-8850</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Individual Learning Accounts: A Comparison of Implemented and Proposed Initiatives</t>
+          <t>Early Validation Evidence of the Canadian Practitioner-Based Assessment of Physical Literacy in Secondary Physical Education</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Access to lifelong learning opportunities has long been discussed in terms of the economic benefits conferred by access to and engagement in further education by members of the labor force, particularly within the global knowledge economy. However, equitable access to lifelong education opportunities, particularly for low-skilled adults in the labor force, has been lacking. The Organisation for Economic Cooperation and Development (OECD) identified three models for funding adult learning: (1) individual learning accounts, (2) individual savings accounts, and (3) training vouchers. The current study discusses examples of these models, either proposed or implemented, across four countries or economic blocks—France, Canada, the United Kingdom, and the United States. In addition, to understand the importance of providing funding for education and training to adults with low levels literacy skills, we use data from the Program for the International Assessment for Adult Competencies (PIAAC) to compare participation in adult education and training (AET) by literacy skill levels. In all countries examined, adults with low literacy skills participated in AET at lower rates than those with middle and high levels of literacy skills. To be successful in reaching adults most in need of skill upgrading, financing models need to provide adequate funds for meaningful skill upgrades, have well-structured information sources (e.g., websites) that are easily navigated by the target population, and include policies to screen educational providers for program quality.</t>
+          <t>The assessment of physical literacy is vital and challenging for researchers and practitioners. Passport for Life is a Canadian global practitioner-based, formative, criterion-referenced assessment of physical literacy that is recorded in an online program. Students complete eight assessments divided across four broad categories of physical literacy (active participation, fitness, movement, and living skills). This study is an endeavor to uncover initial validation and feasibility evidence for the proposed use of Passport for Life with Grade 10–12 physical education students from various regions of Canada. The Standards for Educational and Psychological Testing were used as the theoretical framework. The results with 1,003 secondary school students provide score validity evidence on the content, format, and administrative guidelines of the items and scales; response process evidence about how the program was valued and how the assessments were implemented; internal structure evidence about how participants performed and the extent of associations between items within each scale; predictive evidence as to how scales related temporally to a second measurement of each assessment scale; and concurrent evidence about how the scales related to those of other components. While drawing attention to certain limitations and adding some recommendations, this article shows that the results generally support the Grade 10–12 Passport for Life relative to its intended use. Subscribe to TPE</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>['Phyllis Cummins', 'A. Katherine Harrington', 'Takashi Yamashita']</t>
+          <t>['Ken R. Lodewyk']</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>[['Miami University', 'https://ror.org/05nbqxr67'], ['Scripps (United States)', 'https://ror.org/04x9v7g36'], ['Scripps Institution of Oceanography', 'https://ror.org/04v7hvq31'], ['University of Akron', 'https://ror.org/02kyckx55'], ['University of Maryland, Baltimore', 'https://ror.org/04rq5mt64']]</t>
+          <t>[['Brock University', 'https://ror.org/056am2717']]</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K26" t="b">
         <v>0</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1177/10451595211046971</t>
+          <t>https://doi.org/10.18666/tpe-2019-v76-i3-8850</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://openalex.org/W3096522693</t>
+          <t>https://openalex.org/W2755884504</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1007/s11125-020-09519-5</t>
+          <t>https://doi.org/10.18666/tpe-2017-v74-i3-7459</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Increasing physical literacy in youth: A two-week Sport for Development program for children aged 6-10</t>
+          <t>Early Validation Evidence of a Canadian Practitioner-Based Assessment of Physical Literacy in Physical Education: Passport for Life</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2020</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>cc-by</t>
-        </is>
-      </c>
+        <v>2017</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Abstract Regular physical activity significantly improves health outcomes, yet rates of childhood physical activity remain alarmingly low. Physical literacy has been identified as the foundation for quality physical education, suggesting that sport, education, and public health interventions should seek to increase physical literacy to promote physical activity. A two-week day camp program for children aged 6–10 facing barriers to positive development, was developed and delivered by a Sport for Development facility in Toronto, Canada. Utilizing fundamental movement skills (FMS) as a teaching tool and a pre- and post-assessment, the camp aimed to increase physical literacy and promote engagement in physical activity. Results indicate a significant increase in FMS (t (44) = 4.37, p &amp;lt; .001) as well as improved self-perceptions of physical literacy (t (40) = 14.96, p &amp;lt; .001). The largest FMS increases were found in running and balance and the most significant impacts were among low baseline performers.</t>
+          <t>Physical and Health Education Canada has developed and implemented a formative, criterion-referenced, and practitioner-based national (Canadian) online educational assessment and support resource called Passport for Life (PFL). It was developed to support the awareness and advancement of physical literacy among PE students and teachers. PFL consists of three assessments for each of the four components (active participation, fitness, movement, and living skills). The aim of this study was to uncover initial validation evidence for its current uses using four of the five broad guidelines (content, response processes, internal structure, relations with other variables) for establishing satisfactory score validity as established by the Standards for Educational and Psychological Testing. We conducted a pilot test with 860 students in Grades 4 and 5 in 2013–2014. We analyzed these data, along with data collected across 2 years for Grades 3 to 6 (n = 1,036 in 2013–2014 and 1,254 in 2014–2015) and Grades 7 to 9 (n = 1,793 in 2013–2014 and 1,151 in 2014–2015). A portion (15 to 25%) of these students completed some of the assessments a second time in each of these years. Validation evidence included the development of PFL by a number of domain experts, the nature and format of the components and scales relative to existing literature and evidence, the administrative procedures to guide teachers to implement the assessments, the alignment of items with each component construct and scale, teacher feedback, and positive and significant relations and temporal (predictive) consistency over the 2 years within and across scales and components. These results provide general support for the PFL and its intended use and highlight several cautions and recommendations. Subscribe to TPE</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>['Marika Warner', 'Jackie Robinson', 'Bryan Heal', 'Jenny Lloyd', 'James Mandigo', 'Bess Lennox', 'Larkin Davenport Huyer']</t>
+          <t>['Ken R. Lodewyk', 'James Mandigo']</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>[['Wilfrid Laurier University', 'https://ror.org/00fn7gb05'], ['University of the Fraser Valley', 'https://ror.org/04h6w7946'], ["Queen's University", 'https://ror.org/02y72wh86']]</t>
+          <t>[['Brock University', 'https://ror.org/056am2717'], ['Brock University', 'https://ror.org/056am2717']]</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="K27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1007/s11125-020-09519-5</t>
+          <t>https://doi.org/10.18666/tpe-2017-v74-i3-7459</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://openalex.org/W3166747656</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>https://openalex.org/W2897980683</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.7202/1057103ar</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Evaluating Ocean Perceptions and Ocean Values: The Canadian Ocean Literacy Survey</t>
+          <t>Counsellor-in-Residence: Evaluation of a Residence-Based Initiative to Promote Student Mental Health</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2021</v>
-      </c>
-      <c r="F28" t="inlineStr"/>
+        <v>2019</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>cc-by-nc-nd</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>This paper describes the development, validation, and key findings of the Canadian Ocean Literacy Survey. Led by the Canadian Ocean Literacy Coalition (COLC) and its research partners, this survey was developed as part of a Canada-wide, mixed methods research initiative examining how ocean literacy is understood and practised across different regions and sectors. The survey included items linked to ocean perceptions, values, and actions as reported by two categories of Canadian respondents: “ocean-engaged” (n=1,359) and “general public” (n=1,010). The survey objectives were as follows: to determine if Canadians would identify Canada as an “ocean nation”; to uncover meaningful patterns in ocean awareness, perceptions, and values by region and subgroups; and to better understand Canadians’ emotional connections to, and relationship with, the ocean, as well as their behavioural intentions and actions.</t>
+          <t>Many universities have implemented campus-based initiatives addressing students’ mental health with the goal of promoting well-being. One such initiative is the newly developed Counsellor-in-Residence (CIR) program at the University of Calgary, which targets students’ mental health by providing residence-based counselling services and mental health programming. In this process evaluation, students completed three waves of data collection conducted over the academic year. Each wave measured students’ mental health literacy, using the Mental Health Literacy Scale (O’Connor &amp;amp; Casey, 2015), and resiliency, using the Connor-Davidson Resilience Scale-25 (Connor &amp;amp; Davidson, 2003). Males reported lower mental health literacy than females (p &amp;lt; .001), and international students reported lower mental health literacy than domestic students (p &amp;lt; .001). No differences in resilience levels were found between groups. These findings suggest that male and international students experience additional barriers to accessing campus-based mental health services. Implications for residence-based mental health programming that target male and international students are discussed.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>['Lisa Glithero', 'David B. Zandvliet']</t>
+          <t>['Tiffany Beks', 'Sharon L. Cairns', 'Serena Smygwaty', 'Olga A.L. Miranda Osorio', 'Sheldon J Hill']</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[['University of Calgary', 'https://ror.org/03yjb2x39'], ['University of Calgary', 'https://ror.org/03yjb2x39'], ['University of Calgary', 'https://ror.org/03yjb2x39'], ['University of Calgary', 'https://ror.org/03yjb2x39'], ['Université du Québec à Montréal', 'https://ror.org/002rjbv21'], ['Université de Montréal', 'https://ror.org/0161xgx34'], ['Université Laval', 'https://ror.org/04sjchr03'], ['University of Calgary', 'https://ror.org/03yjb2x39']]</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>6</v>
       </c>
       <c r="K28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>https://cjee.lakeheadu.ca/article/download/1775/1012</t>
+          <t>https://doi.org/10.7202/1057103ar</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2948994296</t>
+          <t>https://openalex.org/W2271312795</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://doi.org/10.18666/tpe-2019-v76-i3-8850</t>
+          <t>https://doi.org/10.1177/016146811511700102</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Early Validation Evidence of the Canadian Practitioner-Based Assessment of Physical Literacy in Secondary Physical Education</t>
+          <t>Cautions about Inferences from International Assessments: The Case of PISA 2009</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>The assessment of physical literacy is vital and challenging for researchers and practitioners. Passport for Life is a Canadian global practitioner-based, formative, criterion-referenced assessment of physical literacy that is recorded in an online program. Students complete eight assessments divided across four broad categories of physical literacy (active participation, fitness, movement, and living skills). This study is an endeavor to uncover initial validation and feasibility evidence for the proposed use of Passport for Life with Grade 10–12 physical education students from various regions of Canada. The Standards for Educational and Psychological Testing were used as the theoretical framework. The results with 1,003 secondary school students provide score validity evidence on the content, format, and administrative guidelines of the items and scales; response process evidence about how the program was valued and how the assessments were implemented; internal structure evidence about how participants performed and the extent of associations between items within each scale; predictive evidence as to how scales related temporally to a second measurement of each assessment scale; and concurrent evidence about how the scales related to those of other components. While drawing attention to certain limitations and adding some recommendations, this article shows that the results generally support the Grade 10–12 Passport for Life relative to its intended use. Subscribe to TPE</t>
+          <t>Background/Context Two key uses of international assessments of achievement have been (a) comparing country performances for identifying the countries with the best education systems and (b) generating insights about effective policy and practice strategies that are associated with higher learning outcomes. Do country rankings really reflect the quality of education in different countries? What are the fallacies of simply looking to higher performing countries to identify strategies for improving learning in our own countries? Purpose In this article we caution against (a) using country rankings as indicators of better education and (b) using correlates of higher performance in high ranking countries as a way of identifying strategies for improving education in our home countries. We elaborate on these cautions by discussing methodological limitations and by comparing five countries that scored very differently on the reading literacy scale of the 2009 PISA assessment. Population We use PISA 2009 reading assessment for five countries/jurisdictions as examples to elaborate on the problems with interpretation of international assessments: Canada, Shanghai-China, Germany, Turkey, and the US, i.e., countries from three continents that span the spectrum of high, average, and low ranking countries and jurisdictions. Research Design Using the five jurisdiction data in an exemplary fashion, our analyses focus on the interpretation of country rankings and correlates of reading performance within countries. We first examine the profiles of these jurisdictions with respect to high school graduation rates, school climate, student attitudes and disciplinary climate and how these variables are related to reading performance rankings. We then examine the extent to which two predictors of reading performance, reading enjoyment and out of school enrichment activities, may be responsible for higher performance levels. Conclusions This article highlights the importance of establishing comparability of test scores and data across jurisdictions as the first step in making international comparisons based on international assessments such as PISA. When it comes to interpreting jurisdiction rankings in international assessments, researchers need to be aware that there is a variegated and complex picture of the relations between reading achievement ranking and rankings on a number of factors that one might think to be related individually or in combination to quality of education. This makes it highly questionable to use reading score rankings as a criterion for adopting educational policies and practices of other jurisdictions. Furthermore, reading scores vary greatly for different student sub-populations within a jurisdiction – e.g., gender, language, and cultural groups – that are all part of the same education system in a given jurisdiction. Identifying effective strategies for improving education using correlates of achievement in high performing countries should be also done with caution. Our analyses present evidence that two factors, reading enjoyment and out of school enrichment activities, cannot be considered solely responsible for higher performance levels. The analyses suggests that the PISA 2009 results are variegated with regards to attitudes towards reading and out-of-school learning experience, rather than exhibiting clear differences that might explain the different performances among the five jurisdictions.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>['Ken R. Lodewyk']</t>
+          <t>['Kadriye Ercikan', 'Wolff‐Michael Roth', 'Mustafa Asıl']</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>[['Brock University', 'https://ror.org/056am2717']]</t>
+          <t>[['University of British Columbia', 'https://ror.org/03rmrcq20'], ['University of Victoria', 'https://ror.org/04s5mat29'], ['University of Auckland', 'https://ror.org/03b94tp07'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['University of Victoria', 'https://ror.org/04s5mat29']]</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="K29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>https://doi.org/10.18666/tpe-2019-v76-i3-8850</t>
+          <t>https://doi.org/10.1177/016146811511700102</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2755884504</t>
+          <t>https://openalex.org/W3004036534</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://doi.org/10.18666/tpe-2017-v74-i3-7459</t>
+          <t>https://doi.org/10.18666/tpe-2020-v77-i1-8798</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Early Validation Evidence of a Canadian Practitioner-Based Assessment of Physical Literacy in Physical Education: Passport for Life</t>
+          <t>Are You Better Than a 12-Year-Old Student? A Pilot Study to Explore Physical Literacy in Preservice Physical Education Teachers</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Physical and Health Education Canada has developed and implemented a formative, criterion-referenced, and practitioner-based national (Canadian) online educational assessment and support resource called Passport for Life (PFL). It was developed to support the awareness and advancement of physical literacy among PE students and teachers. PFL consists of three assessments for each of the four components (active participation, fitness, movement, and living skills). The aim of this study was to uncover initial validation evidence for its current uses using four of the five broad guidelines (content, response processes, internal structure, relations with other variables) for establishing satisfactory score validity as established by the Standards for Educational and Psychological Testing. We conducted a pilot test with 860 students in Grades 4 and 5 in 2013–2014. We analyzed these data, along with data collected across 2 years for Grades 3 to 6 (n = 1,036 in 2013–2014 and 1,254 in 2014–2015) and Grades 7 to 9 (n = 1,793 in 2013–2014 and 1,151 in 2014–2015). A portion (15 to 25%) of these students completed some of the assessments a second time in each of these years. Validation evidence included the development of PFL by a number of domain experts, the nature and format of the components and scales relative to existing literature and evidence, the administrative procedures to guide teachers to implement the assessments, the alignment of items with each component construct and scale, teacher feedback, and positive and significant relations and temporal (predictive) consistency over the 2 years within and across scales and components. These results provide general support for the PFL and its intended use and highlight several cautions and recommendations. Subscribe to TPE</t>
+          <t>Physical educators play a key role in role modeling to students within the school context. Therefore, there is a need to understand whether current physical education teacher education (PETE) provides sufficient knowledge and practice to prepare preservice educators to be successful. Thirty PETE preservice teachers (23 males, 7 females, aged 19–26) participated in this study. Participants performed tests in physical fitness and motor performance and completed an online questionnaire about cognitive factors (e.g., knowledge and understanding). In addition, a 7-day walking step total was recorded as daily activity in accordance with the Canadian Assessment of Physical Literacy testing battery. Each participant's performance was compared with the achievement level of a 12-year-old child. Participants had significantly better performance in muscular strength (measured as handgrip test) and flexibility (measured as sit-and-reach test) than a 12-year-old. However, participants had significantly poorer performance in aerobic fitness (measured as PACER), motor performance (measured as obstacle course test), and muscular endurance (measured as plank test) than a 12-year-old. In addition, participants had significantly lower knowledge and understanding of health and physical activity than a 12-year-old. A positive relationship between physical competence (i.e., overall performance in physical fitness and motor performance) and cognitive factor was shown among participants. Growth and maturation may explain participants' better performance in muscular strength and flexibility. Excessive weight status and low level of knowledge may have contributed to their poor performance in the physical competence domain. The positive relationship may indicate that cognitive factors are a strong predictor of the performance of physical fitness and motor performance. Therefore, for physical educators to promote a healthy lifestyle in education settings, the current PETE curriculum needs to be reviewed and relevant information delivered to promote physical literacy in PETE preservice teachers.Subscribe to TPE</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>['Ken R. Lodewyk', 'James Mandigo']</t>
+          <t>['Chih‐Chia Chen', 'Megan E. Holmes', 'Katie Wood', 'Yonjoong Ryuh', 'Pamela Hodges Kulinna']</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>[['Brock University', 'https://ror.org/056am2717'], ['Brock University', 'https://ror.org/056am2717']]</t>
+          <t>[['Mississippi State University', 'https://ror.org/0432jq872'], ['Mississippi State University', 'https://ror.org/0432jq872'], ['Mississippi State University', 'https://ror.org/0432jq872'], ['Mississippi State University', 'https://ror.org/0432jq872'], ['Arizona State University', 'https://ror.org/03efmqc40']]</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="K30" t="b">
         <v>0</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>https://doi.org/10.18666/tpe-2017-v74-i3-7459</t>
+          <t>https://doi.org/10.18666/tpe-2020-v77-i1-8798</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2897980683</t>
+          <t>https://openalex.org/W2768220913</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://doi.org/10.7202/1057103ar</t>
+          <t>https://doi.org/10.1249/mss.0000000000001494</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Counsellor-in-Residence: Evaluation of a Residence-Based Initiative to Promote Student Mental Health</t>
+          <t>A Construct Validation Study of PLAYfun</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2019</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>cc-by-nc-nd</t>
-        </is>
-      </c>
+        <v>2017</v>
+      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Many universities have implemented campus-based initiatives addressing students’ mental health with the goal of promoting well-being. One such initiative is the newly developed Counsellor-in-Residence (CIR) program at the University of Calgary, which targets students’ mental health by providing residence-based counselling services and mental health programming. In this process evaluation, students completed three waves of data collection conducted over the academic year. Each wave measured students’ mental health literacy, using the Mental Health Literacy Scale (O’Connor &amp;amp; Casey, 2015), and resiliency, using the Connor-Davidson Resilience Scale-25 (Connor &amp;amp; Davidson, 2003). Males reported lower mental health literacy than females (p &amp;lt; .001), and international students reported lower mental health literacy than domestic students (p &amp;lt; .001). No differences in resilience levels were found between groups. These findings suggest that male and international students experience additional barriers to accessing campus-based mental health services. Implications for residence-based mental health programming that target male and international students are discussed.</t>
+          <t>Physical Literacy Assessment for Youth (PLAYfun) is a measure of motor competence, comprehension, and confidence which is part of a suite of scales used to assess physical literacy in children and youth; however, its measurement properties have not been reported in the published literature. The purpose of this study is to examine the factor structure of PLAYfun, in addition to variations in PLAYfun subscale results by age and sex.In this study, we use a sample of children and youth 7 to 14 yr of age (n = 215) to test a proposed factor structure for the motor competence component of PLAYfun and to examine age and sex differences in subscale and total scores. The initial (n = 128) and secondary (n = 98) samples were drawn from a stratified (by geographic region), random sample of 27 after-school programs from a larger pool of 400 programs across the province of Ontario. Seven research assistants were initially trained on the administration of PLAYfun and rated a small pilot sample of 10 children. These trained assessors then assessed the full sample.Interrater agreement was very good (intraclass correlation, 0.87). The hypothesized five-factor structure of the scale was found to have an acceptable fit to the data (root mean square error of approximation, 0.055; 90% confidence interval, 0.03-0.075; comparative fit index, 0.95; Tucker-Lewis Index, 0.94). In general, PLAYfun scores increased with age as developmentally expected. There were few sex differences across skills, but girls did not perform as well as boys on upper and lower body object control skills.The factor structure and patterns of results by age and sex support PLAYfun as a measure of motor competence. Continued evaluation of the tool and other subscales of PLAY is required.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>['Tiffany Beks', 'Sharon L. Cairns', 'Serena Smygwaty', 'Olga A.L. Miranda Osorio', 'Sheldon J Hill']</t>
+          <t>['John Cairney', 'Scott Veldhuizen', 'Jeffrey D. Graham', 'Christine Rodriguez', 'Chloe Bedard', 'Emily Bremer', 'Dean Kriellaars']</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>[['University of Calgary', 'https://ror.org/03yjb2x39'], ['University of Calgary', 'https://ror.org/03yjb2x39'], ['University of Calgary', 'https://ror.org/03yjb2x39'], ['University of Calgary', 'https://ror.org/03yjb2x39'], ['Université du Québec à Montréal', 'https://ror.org/002rjbv21'], ['Université de Montréal', 'https://ror.org/0161xgx34'], ['Université Laval', 'https://ror.org/04sjchr03'], ['University of Calgary', 'https://ror.org/03yjb2x39']]</t>
+          <t>[['McMaster University', 'https://ror.org/02fa3aq29'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['Impact', 'https://ror.org/05d9dsr70'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['University of Manitoba', 'https://ror.org/02gfys938']]</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="K31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>https://doi.org/10.7202/1057103ar</t>
+          <t>https://doi.org/10.1249/mss.0000000000001494</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2271312795</t>
+          <t>https://openalex.org/W4311236699</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1177/016146811511700102</t>
+          <t>https://doi.org/10.21083/partnership.v17i2.6808</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Cautions about Inferences from International Assessments: The Case of PISA 2009</t>
+          <t>Early Literacy Learning for Future Library Paraprofessionals: Authentic Learning in Library Education</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2015</v>
-      </c>
-      <c r="F32" t="inlineStr"/>
+        <v>2022</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>cc-by-nc-nd</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Background/Context Two key uses of international assessments of achievement have been (a) comparing country performances for identifying the countries with the best education systems and (b) generating insights about effective policy and practice strategies that are associated with higher learning outcomes. Do country rankings really reflect the quality of education in different countries? What are the fallacies of simply looking to higher performing countries to identify strategies for improving learning in our own countries? Purpose In this article we caution against (a) using country rankings as indicators of better education and (b) using correlates of higher performance in high ranking countries as a way of identifying strategies for improving education in our home countries. We elaborate on these cautions by discussing methodological limitations and by comparing five countries that scored very differently on the reading literacy scale of the 2009 PISA assessment. Population We use PISA 2009 reading assessment for five countries/jurisdictions as examples to elaborate on the problems with interpretation of international assessments: Canada, Shanghai-China, Germany, Turkey, and the US, i.e., countries from three continents that span the spectrum of high, average, and low ranking countries and jurisdictions. Research Design Using the five jurisdiction data in an exemplary fashion, our analyses focus on the interpretation of country rankings and correlates of reading performance within countries. We first examine the profiles of these jurisdictions with respect to high school graduation rates, school climate, student attitudes and disciplinary climate and how these variables are related to reading performance rankings. We then examine the extent to which two predictors of reading performance, reading enjoyment and out of school enrichment activities, may be responsible for higher performance levels. Conclusions This article highlights the importance of establishing comparability of test scores and data across jurisdictions as the first step in making international comparisons based on international assessments such as PISA. When it comes to interpreting jurisdiction rankings in international assessments, researchers need to be aware that there is a variegated and complex picture of the relations between reading achievement ranking and rankings on a number of factors that one might think to be related individually or in combination to quality of education. This makes it highly questionable to use reading score rankings as a criterion for adopting educational policies and practices of other jurisdictions. Furthermore, reading scores vary greatly for different student sub-populations within a jurisdiction – e.g., gender, language, and cultural groups – that are all part of the same education system in a given jurisdiction. Identifying effective strategies for improving education using correlates of achievement in high performing countries should be also done with caution. Our analyses present evidence that two factors, reading enjoyment and out of school enrichment activities, cannot be considered solely responsible for higher performance levels. The analyses suggests that the PISA 2009 results are variegated with regards to attitudes towards reading and out-of-school learning experience, rather than exhibiting clear differences that might explain the different performances among the five jurisdictions.</t>
+          <t>This article describes the professional learning around early literacy experienced by library paraprofessional students at a post-secondary institution in Canada. Students completed a survey to gauge their conceptions of early literacy at the beginning of a course on library services for children and young adults. These students then experienced hands-on, engaging course elements such as in-class discussions, guest speakers, and authentic assessments. At the conclusion of the course, students were again surveyed and were asked to identify course elements that contributed to their learning. Most students aligned with an emergent literacy approach to early literacy. While a comparison between the two surveys did not reveal a significant difference in terms of students’ conceptions of early literacy, multiple students identified the hands-on elements of the course as beneficial. The researchers conclude that providing authentic professional learning opportunities that include knowledge application reinforces learners’ conceptions about emergent literacy.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>['Kadriye Ercikan', 'Wolff‐Michael Roth', 'Mustafa Asıl']</t>
+          <t>['Alvina Mardhani-Bayne', 'Lisa Shamchuk']</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>[['University of British Columbia', 'https://ror.org/03rmrcq20'], ['University of Victoria', 'https://ror.org/04s5mat29'], ['University of Auckland', 'https://ror.org/03b94tp07'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['University of Victoria', 'https://ror.org/04s5mat29']]</t>
+          <t>[['MacEwan University', 'https://ror.org/003s89n44'], ['MacEwan University', 'https://ror.org/003s89n44']]</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="K32" t="b">
         <v>1</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1177/016146811511700102</t>
+          <t>https://doi.org/10.21083/partnership.v17i2.6808</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://openalex.org/W3004036534</t>
+          <t>https://openalex.org/W4283837859</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://doi.org/10.18666/tpe-2020-v77-i1-8798</t>
+          <t>https://doi.org/10.21083/partnership.v17i1.6574</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Are You Better Than a 12-Year-Old Student? A Pilot Study to Explore Physical Literacy in Preservice Physical Education Teachers</t>
+          <t>A Text Analysis of Four Levels of Librarian Involvement and Impact on Students in an Inquiry-Based Learning Course</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2020</v>
-      </c>
-      <c r="F33" t="inlineStr"/>
+        <v>2022</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>cc-by-nc-nd</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Physical educators play a key role in role modeling to students within the school context. Therefore, there is a need to understand whether current physical education teacher education (PETE) provides sufficient knowledge and practice to prepare preservice educators to be successful. Thirty PETE preservice teachers (23 males, 7 females, aged 19–26) participated in this study. Participants performed tests in physical fitness and motor performance and completed an online questionnaire about cognitive factors (e.g., knowledge and understanding). In addition, a 7-day walking step total was recorded as daily activity in accordance with the Canadian Assessment of Physical Literacy testing battery. Each participant's performance was compared with the achievement level of a 12-year-old child. Participants had significantly better performance in muscular strength (measured as handgrip test) and flexibility (measured as sit-and-reach test) than a 12-year-old. However, participants had significantly poorer performance in aerobic fitness (measured as PACER), motor performance (measured as obstacle course test), and muscular endurance (measured as plank test) than a 12-year-old. In addition, participants had significantly lower knowledge and understanding of health and physical activity than a 12-year-old. A positive relationship between physical competence (i.e., overall performance in physical fitness and motor performance) and cognitive factor was shown among participants. Growth and maturation may explain participants' better performance in muscular strength and flexibility. Excessive weight status and low level of knowledge may have contributed to their poor performance in the physical competence domain. The positive relationship may indicate that cognitive factors are a strong predictor of the performance of physical fitness and motor performance. Therefore, for physical educators to promote a healthy lifestyle in education settings, the current PETE curriculum needs to be reviewed and relevant information delivered to promote physical literacy in PETE preservice teachers.Subscribe to TPE</t>
+          <t>Librarians at the University of Calgary collaborated with instructors on an inquiry-based learning course with varying involvement across four course sections. This study uses text analysis of student assignments to assess information literacy (IL) skill development across four levels of course participation: librarian as instructor-of-record, two levels of embeddedness, and a single ‘one-shot’ session. The methodology included the tracking of keywords generated using the ACRL Framework for Information Literacy and text analysis of student reflection assignments in an inquiry-based, research-focused first-year undergraduate course. The results suggest that the benefit to student IL skills is not related to amount of librarian instruction, but rather to the level of instructor buy-in with regard to library services and the importance of IL skills. We argue that the most impactful librarian involvement is as an IL course consultant rather than a full-time embedded librarian (which is surprising given the literature on the efficacy of embeddedness). Although further research is needed, the study results have significant implications for academic librarian instructional practices and collaborations on course content with faculty members.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>['Chih‐Chia Chen', 'Megan E. Holmes', 'Katie Wood', 'Yonjoong Ryuh', 'Pamela Hodges Kulinna']</t>
+          <t>['Marc Stoeckle', 'James E. Murphy', 'Bartlomiej A. Lenart']</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>[['Mississippi State University', 'https://ror.org/0432jq872'], ['Mississippi State University', 'https://ror.org/0432jq872'], ['Mississippi State University', 'https://ror.org/0432jq872'], ['Mississippi State University', 'https://ror.org/0432jq872'], ['Arizona State University', 'https://ror.org/03efmqc40']]</t>
+          <t>[['University of Calgary', 'https://ror.org/03yjb2x39'], ['University of Calgary', 'https://ror.org/03yjb2x39'], ['University of Calgary', 'https://ror.org/03yjb2x39']]</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>https://doi.org/10.18666/tpe-2020-v77-i1-8798</t>
+          <t>https://doi.org/10.21083/partnership.v17i1.6574</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2612367365</t>
+          <t>https://openalex.org/W1917627399</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://doi.org/10.7202/1039633ar</t>
+          <t>https://doi.org/10.1186/s12889-015-2106-6</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>A/r/tography and Teacher Education in the 21st Century</t>
+          <t>The Canadian Assessment of Physical Literacy: methods for children in grades 4 to 6 (8 to 12 years)</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2017</v>
-      </c>
-      <c r="F34" t="inlineStr"/>
+        <v>2015</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>cc-by</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>In this article, we summarize research on Prince Edward Island where a Prince Edward Island teacher, identifying as an a/r/tographer, designed a digital and multiliteracies unit, as part of a directed studies course in her Master of Education program. Small in scope, this single participant case study was designed to give a fuller picture to three difficulties teachers often face when teaching new literacies. These are (1) applying multiliteracies theory, (2) thinking across literacies domains, and (3) assessing literacies holistically. Findings are derived from our six research conversations, and our discussion highlights the necessity of artistic ways of being and thinking for teacher education programs in the 21 st century.</t>
+          <t>Physical literacy is described as the motivation, confidence, physical competence, knowledge and understanding to value and engage in a physically active lifestyle. As such, it is expected that those who have greater physical literacy would be more likely to obtain the health benefits offered by habitual physical activity. A theoretical model and assessment battery, the Canadian Assessment of Physical Literacy (CAPL), for the assessment of childhood physical literacy had been proposed in theory but validity data were lacking. The purpose of this study was to explore validity evidence for the CAPL among children in grades 4 to 6.CAPL validity was evaluated through three analyses that utilized cross-sectional data obtained through local schools in Eastern Ontario, Canada. A confirmatory factor analysis compared the data to the theoretical model. Patterns of association between self-reported age and gender and the CAPL total and domain scores were examined using regression models. Teacher ratings of participants' knowledge, attitude and physical activity competence were compared to assessment results.The CAPL was completed by 963 children (55 % female) in grades 4, 5 and 6. Children were 8 to 12 years of age (mean 10.1 years), with 85 % of children approached agreeing to participate. A confirmatory factor analysis using data from 489 children with complete raw scores supported a model with four domains: engagement in physical activity (active and sedentary), physical competence (fitness and motor skill), motivation and confidence, and knowledge and understanding. Raw domain scores followed expected patterns for age and gender, providing evidence for their validity. Interpretive categories, developed from age and gender adjusted normative data, were not associated with age indicating that the CAPL is suitable for use across this age range. Children's gender was associated with the physical competence, motivation and engagement in physical activity domain scores, indicating that further research is required regarding the gender adjustment of the raw CAPL scores. CAPL domain and total scores were statistically significantly associated with teacher ratings of the child's motivation, attitudes, fitness, skill and overall physical activity.CAPL offers a comprehensive assessment of engagement in physical activity, physical competence, motivation and confidence, and knowledge and understanding as components of childhood (grades 4 to 6, 8 to 12 years) physical literacy. Monitoring of these measures enhances our understanding of children's physical literacy, and assists with the identification of areas where additional supports are required.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>['Sean Wiebe', 'Claire Caseley Smith']</t>
+          <t>['Patricia E. Longmuir', 'Charles P. Boyer', 'Meghann Lloyd', 'Yan Yang', 'Elena Boiarskaia', 'Weimo Zhu', 'Mark S. Tremblay']</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>[['University of Prince Edward Island', 'https://ror.org/02xh9x144']]</t>
+          <t>[["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Ontario Institute of Technology', 'https://ror.org/016zre027'], ['University of Illinois Urbana-Champaign', 'https://ror.org/047426m28'], ['University of Illinois Urbana-Champaign', 'https://ror.org/047426m28'], ['University of Illinois Urbana-Champaign', 'https://ror.org/047426m28'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Ottawa', 'https://ror.org/03c4mmv16']]</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>4</v>
+        <v>211</v>
       </c>
       <c r="K34" t="b">
         <v>1</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>https://doi.org/10.7202/1039633ar</t>
+          <t>https://doi.org/10.1186/s12889-015-2106-6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2612367365</t>
+          <t>https://openalex.org/W2030066779</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://doi.org/10.7202/1039633ar</t>
+          <t>https://doi.org/10.3138/cmlr.2346</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>A/r/tography and Teacher Education in the 21st Century</t>
+          <t>The Predictive Effects of L1 and L2 Early Literacy Indicators on Reading in French Immersion</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>In this article, we summarize research on Prince Edward Island where a Prince Edward Island teacher, identifying as an a/r/tographer, designed a digital and multiliteracies unit, as part of a directed studies course in her Master of Education program. Small in scope, this single participant case study was designed to give a fuller picture to three difficulties teachers often face when teaching new literacies. These are (1) applying multiliteracies theory, (2) thinking across literacies domains, and (3) assessing literacies holistically. Findings are derived from our six research conversations, and our discussion highlights the necessity of artistic ways of being and thinking for teacher education programs in the 21 st century.</t>
+          <t>Abstract: This study explored the predictive effects of within- and cross-language early literacy indicators with regard to second language (L2) reading achievement in a Grade 3 entry-point French immersion (FI) program. Kindergarten students (N = 83) in a regular English program were administered English early literacy measures. Three years later, once students entered the FI, 56 students from the original cohort were reassessed using French literacy measures. This allowed for an examination of the long-term connections between first language (L1) early literacy indicators and L2 reading outcomes. Regression analysis revealed that L1 early literacy skills relating to aspects of phonological awareness and, more importantly, alphabetic knowledge were significant predictors of L2 reading even when school-based L2 learning was delayed several years. With respect to the French literacy indicators, knowledge of the alphabet and related measures were again significant predictors of L2 reading performance. The predictive effects of French indicators were significant even in the first few months of FI. These results provide additional information about the predictive effects of within- and cross-language early literacy indicators and the extent to which they can be used to identify students who may be at risk for reading difficulties in their L2.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>['Sean Wiebe', 'Claire Caseley Smith']</t>
+          <t>['Renée Bourgoin']</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>[['University of Prince Edward Island', 'https://ror.org/02xh9x144']]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="K35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>https://doi.org/10.7202/1039633ar</t>
+          <t>https://doi.org/10.3138/cmlr.2346</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2612367365</t>
+          <t>https://openalex.org/W2067140869</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://doi.org/10.7202/1039633ar</t>
+          <t>https://doi.org/10.1016/j.jcjo.2014.08.002</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>A/r/tography and Teacher Education in the 21st Century</t>
+          <t>Patient-appropriate health literacy educational materials in ophthalmology</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>In this article, we summarize research on Prince Edward Island where a Prince Edward Island teacher, identifying as an a/r/tographer, designed a digital and multiliteracies unit, as part of a directed studies course in her Master of Education program. Small in scope, this single participant case study was designed to give a fuller picture to three difficulties teachers often face when teaching new literacies. These are (1) applying multiliteracies theory, (2) thinking across literacies domains, and (3) assessing literacies holistically. Findings are derived from our six research conversations, and our discussion highlights the necessity of artistic ways of being and thinking for teacher education programs in the 21 st century.</t>
-        </is>
-      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>['Sean Wiebe', 'Claire Caseley Smith']</t>
+          <t>['David Mikhail', 'Kari L. Visscher', 'Nancy Chen', 'Joy Wang', 'Barry Y. Emara', 'Cindy Hutnik']</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>[['University of Prince Edward Island', 'https://ror.org/02xh9x144']]</t>
+          <t>[['Western University', 'https://ror.org/02grkyz14'], ['Western University', 'https://ror.org/02grkyz14'], ['Western University', 'https://ror.org/02grkyz14'], ['Western University', 'https://ror.org/02grkyz14'], ['Western University', 'https://ror.org/02grkyz14'], ['Western University', 'https://ror.org/02grkyz14']]</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>https://doi.org/10.7202/1039633ar</t>
+          <t>https://doi.org/10.1016/j.jcjo.2014.08.002</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2612367365</t>
+          <t>https://openalex.org/W2754071577</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://doi.org/10.7202/1039633ar</t>
+          <t>https://doi.org/10.18848/2327-0136/cgp/v22i04/1-26</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>A/r/tography and Teacher Education in the 21st Century</t>
+          <t>Is Student Achievement on Standardized EQAO Testing Reflected in Their Annual Academic Performance? A Longitudinal Study</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>In this article, we summarize research on Prince Edward Island where a Prince Edward Island teacher, identifying as an a/r/tographer, designed a digital and multiliteracies unit, as part of a directed studies course in her Master of Education program. Small in scope, this single participant case study was designed to give a fuller picture to three difficulties teachers often face when teaching new literacies. These are (1) applying multiliteracies theory, (2) thinking across literacies domains, and (3) assessing literacies holistically. Findings are derived from our six research conversations, and our discussion highlights the necessity of artistic ways of being and thinking for teacher education programs in the 21 st century.</t>
-        </is>
-      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>['Sean Wiebe', 'Claire Caseley Smith']</t>
+          <t>['Roxanne Landry', 'Michèle Minor-Corriveau', 'Roxanne Bélanger']</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>[['University of Prince Edward Island', 'https://ror.org/02xh9x144']]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>https://doi.org/10.7202/1039633ar</t>
+          <t>https://doi.org/10.18848/2327-0136/cgp/v22i04/1-26</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2768220913</t>
+          <t>https://openalex.org/W2082979380</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1249/mss.0000000000001494</t>
+          <t>https://doi.org/10.1016/j.pec.2014.04.014</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>A Construct Validation Study of PLAYfun</t>
+          <t>Health literacy and its association with perception of teratogenic risks and health behavior during pregnancy</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Physical Literacy Assessment for Youth (PLAYfun) is a measure of motor competence, comprehension, and confidence which is part of a suite of scales used to assess physical literacy in children and youth; however, its measurement properties have not been reported in the published literature. The purpose of this study is to examine the factor structure of PLAYfun, in addition to variations in PLAYfun subscale results by age and sex.In this study, we use a sample of children and youth 7 to 14 yr of age (n = 215) to test a proposed factor structure for the motor competence component of PLAYfun and to examine age and sex differences in subscale and total scores. The initial (n = 128) and secondary (n = 98) samples were drawn from a stratified (by geographic region), random sample of 27 after-school programs from a larger pool of 400 programs across the province of Ontario. Seven research assistants were initially trained on the administration of PLAYfun and rated a small pilot sample of 10 children. These trained assessors then assessed the full sample.Interrater agreement was very good (intraclass correlation, 0.87). The hypothesized five-factor structure of the scale was found to have an acceptable fit to the data (root mean square error of approximation, 0.055; 90% confidence interval, 0.03-0.075; comparative fit index, 0.95; Tucker-Lewis Index, 0.94). In general, PLAYfun scores increased with age as developmentally expected. There were few sex differences across skills, but girls did not perform as well as boys on upper and lower body object control skills.The factor structure and patterns of results by age and sex support PLAYfun as a measure of motor competence. Continued evaluation of the tool and other subscales of PLAY is required.</t>
-        </is>
-      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>['John Cairney', 'Scott Veldhuizen', 'Jeffrey D. Graham', 'Christine Rodriguez', 'Chloe Bedard', 'Emily Bremer', 'Dean Kriellaars']</t>
+          <t>['Angela Lupattelli', 'Marta Picinardi', 'Adrienne Einarson', 'Hedvig Nordeng']</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>[['McMaster University', 'https://ror.org/02fa3aq29'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['Impact', 'https://ror.org/05d9dsr70'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['University of Manitoba', 'https://ror.org/02gfys938']]</t>
+          <t>[['University of Oslo', 'https://ror.org/01xtthb56'], ['University of Oslo', 'https://ror.org/01xtthb56'], ['Hospital for Sick Children', 'https://ror.org/057q4rt57'], ['SickKids Foundation', 'https://ror.org/04374qe70'], ['University of Oslo', 'https://ror.org/01xtthb56'], ['Norwegian Institute of Public Health', 'https://ror.org/046nvst19']]</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="K38" t="b">
         <v>0</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1249/mss.0000000000001494</t>
+          <t>https://doi.org/10.1016/j.pec.2014.04.014</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2768220913</t>
+          <t>https://openalex.org/W2211885666</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1249/mss.0000000000001494</t>
+          <t>https://doi.org/10.3899/jrheum.141509</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>A Construct Validation Study of PLAYfun</t>
+          <t>Health Literacy Rates in a Population of Patients with Rheumatoid Arthritis in Southwestern Ontario</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Physical Literacy Assessment for Youth (PLAYfun) is a measure of motor competence, comprehension, and confidence which is part of a suite of scales used to assess physical literacy in children and youth; however, its measurement properties have not been reported in the published literature. The purpose of this study is to examine the factor structure of PLAYfun, in addition to variations in PLAYfun subscale results by age and sex.In this study, we use a sample of children and youth 7 to 14 yr of age (n = 215) to test a proposed factor structure for the motor competence component of PLAYfun and to examine age and sex differences in subscale and total scores. The initial (n = 128) and secondary (n = 98) samples were drawn from a stratified (by geographic region), random sample of 27 after-school programs from a larger pool of 400 programs across the province of Ontario. Seven research assistants were initially trained on the administration of PLAYfun and rated a small pilot sample of 10 children. These trained assessors then assessed the full sample.Interrater agreement was very good (intraclass correlation, 0.87). The hypothesized five-factor structure of the scale was found to have an acceptable fit to the data (root mean square error of approximation, 0.055; 90% confidence interval, 0.03-0.075; comparative fit index, 0.95; Tucker-Lewis Index, 0.94). In general, PLAYfun scores increased with age as developmentally expected. There were few sex differences across skills, but girls did not perform as well as boys on upper and lower body object control skills.The factor structure and patterns of results by age and sex support PLAYfun as a measure of motor competence. Continued evaluation of the tool and other subscales of PLAY is required.</t>
+          <t>Objective. To determine the rate of low health literacy in the rheumatoid arthritis (RA) population in southwestern Ontario. Methods. For the study, 432 patients with RA were contacted, and 311 completed the assessment. The health literacy levels of the participants were estimated using 4 assessment tools administered in the following order: the Single Item Literacy Screener (SILS), the Medical Term Recognition Test (METER), the Rapid Estimate of Adult Literacy in Medicine (REALM), and the Shortened Test of Functional Health Literacy in Adults (STOFHLA). Results. The rates of low literacy as estimated by STOFHLA, REALM, METER, and SILS were 14.5%, 14.8%, 14.1%, and 18.6%, respectively. All 4 assessment tools were statistically significantly correlated. STOFHLA, REALM, and METER were strongly correlated with each other (r = 0.59–0.79), while SILS only demonstrated moderate correlations with the other assessment tools (r = 0.33–0.45). Multiple linear regression and binary logistic regression analyses revealed that low levels of education and a lack of daily reading activity were common predictors of low health literacy. Using a non-English primary language at home was found to be a strong predictor of low health literacy in STOFHLA, REALM, and METER. Male sex was found to be a significant predictor of poor performance in REALM and METER, but not STOFHLA. Conclusion. Low health literacy is an important issue in the southwestern Ontario RA population. About 1 in 7 patients with RA may not have the necessary skills to become involved in making decisions regarding their personal health. Rheumatologists should be aware of the low health literacy levels of patients with RA and should consider identifying patients at risk of low health literacy.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>['John Cairney', 'Scott Veldhuizen', 'Jeffrey D. Graham', 'Christine Rodriguez', 'Chloe Bedard', 'Emily Bremer', 'Dean Kriellaars']</t>
+          <t>['Zhaowei Gong', 'Sara Haig', 'Janet Pope', 'Sherry Rohekar', 'Gina Rohekar', 'Nicole G. H. LeRICHE', 'Andrew Thompson']</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>[['McMaster University', 'https://ror.org/02fa3aq29'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['Impact', 'https://ror.org/05d9dsr70'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['University of Manitoba', 'https://ror.org/02gfys938']]</t>
+          <t>[["St Joseph's Health Care", 'https://ror.org/05rj7xr73'], ['Western University', 'https://ror.org/02grkyz14'], ["St Joseph's Health Care", 'https://ror.org/05rj7xr73'], ['Western University', 'https://ror.org/02grkyz14'], ['Western University of Health Sciences', 'https://ror.org/05167c961'], ['Western University', 'https://ror.org/02grkyz14'], ["St Joseph's Health Care", 'https://ror.org/05rj7xr73'], ['Western University of Health Sciences', 'https://ror.org/05167c961'], ["St Joseph's Health Care", 'https://ror.org/05rj7xr73'], ['Western University', 'https://ror.org/02grkyz14'], ['Western University of Health Sciences', 'https://ror.org/05167c961'], ["St Joseph's Health Care", 'https://ror.org/05rj7xr73'], ['Western University', 'https://ror.org/02grkyz14'], ['Western University of Health Sciences', 'https://ror.org/05167c961'], ["St Joseph's Health Care", 'https://ror.org/05rj7xr73'], ['Western University', 'https://ror.org/02grkyz14'], ['Western University of Health Sciences', 'https://ror.org/05167c961'], ["St Joseph's Health Care", 'https://ror.org/05rj7xr73'], ['Western University', 'https://ror.org/02grkyz14'], ['Western University of Health Sciences', 'https://ror.org/05167c961']]</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="K39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1249/mss.0000000000001494</t>
+          <t>https://doi.org/10.3899/jrheum.141509</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2768220913</t>
+          <t>https://openalex.org/W1728407011</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1249/mss.0000000000001494</t>
+          <t>https://doi.org/10.1002/rrq.69</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>A Construct Validation Study of PLAYfun</t>
+          <t>The Role of Acculturation in Reading a Second Language: Its Relation to English Literacy Skills in Immigrant Chinese Adolescents</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Physical Literacy Assessment for Youth (PLAYfun) is a measure of motor competence, comprehension, and confidence which is part of a suite of scales used to assess physical literacy in children and youth; however, its measurement properties have not been reported in the published literature. The purpose of this study is to examine the factor structure of PLAYfun, in addition to variations in PLAYfun subscale results by age and sex.In this study, we use a sample of children and youth 7 to 14 yr of age (n = 215) to test a proposed factor structure for the motor competence component of PLAYfun and to examine age and sex differences in subscale and total scores. The initial (n = 128) and secondary (n = 98) samples were drawn from a stratified (by geographic region), random sample of 27 after-school programs from a larger pool of 400 programs across the province of Ontario. Seven research assistants were initially trained on the administration of PLAYfun and rated a small pilot sample of 10 children. These trained assessors then assessed the full sample.Interrater agreement was very good (intraclass correlation, 0.87). The hypothesized five-factor structure of the scale was found to have an acceptable fit to the data (root mean square error of approximation, 0.055; 90% confidence interval, 0.03-0.075; comparative fit index, 0.95; Tucker-Lewis Index, 0.94). In general, PLAYfun scores increased with age as developmentally expected. There were few sex differences across skills, but girls did not perform as well as boys on upper and lower body object control skills.The factor structure and patterns of results by age and sex support PLAYfun as a measure of motor competence. Continued evaluation of the tool and other subscales of PLAY is required.</t>
+          <t>The main purpose of this study was to bridge the gap between the literature on cognitive variables related to English literacy learning skills, as suggested by the simple view of reading, and the literature on sociocultural variables, specifically acculturation. The sample consisted of 94 Chinese immigrant adolescents from grades 7–12 in Waterloo Region in and the metropolitan Toronto area of Ontario, Canada. Acculturation was measured by a questionnaire. Literacy skills, including vocabulary, reading fluency, and reading comprehension, were assessed individually using standardized tests. Hierarchical regression analyses reveal that degrees of acculturation to Canadian culture positively predicted English literacy skills after controlling for length of residence in Canada. Interestingly, acculturation explained unique variance in reading beyond variables in the simple view of reading, suggesting the independent contribution of sociocultural factors to second-language reading in adolescent English learners. 本研究旨在弥合文献上两种变数之间的差距;其一是按简单阅读观所提出与英语读写技能相关的认知变数,其二是与社会文化,尤其与文化适应相关的变数。本研究样本取自加拿大安大略省多伦多市区和滑铁卢地区的7至12年级的94名中国移民青少年。研究者通过问卷调查衡量文化适应,并通过标准化单独测试评估读写技能,包括词汇、阅读流畅度和阅读理解能力。分层回归分析显示,加拿大文化适应程度,在控制了居住在加拿大时间的长短之后,能正面地预测英语读写技能。有趣的是,文化适应能解释简单阅读观之外的阅读变数的独特方差,这显示出社会文化因素对第二语言青少年英语学习者的阅读具有独特的作用。 El propósito principal de este estudio fue el de llenar el vacío entre la literatura sobre los variables cognitivos relacionados a las destrezas del aprendizaje del inglés, como sugerido por la perspectiva de simplemente leer, y la literatura sobre los variables socioculturales, específicamente aculturación. La muestra consistió de 94 inmigrantes chinos adolescentes entre el 7mo y 12mo grado en Waterloo Region y el área metropolitana de Toronto en Ontario, Canadá. Se midió la aculturación por medio de una encuesta. Las destrezas de aprendizaje, incluyendo vocabulario, la fluidez al leer, y la comprensión de la lectura, se midieron individualmente usando exámenes estandarizados. El análisis de regresión jerárquica muestra que el grado de aculturación a la cultura canadiense predecía de manera positiva las destrezas de aprendizaje del inglés, habiéndose controlado por la cantidad de tiempo que se había vivido en Canadá. Lo interesante es que la aculturación explicó variedades originales en la lectura más allá de las variables en la perspectiva simple de lectura, sugiriendo que hay una contribución independiente en los factores socioculturales a la lectura de un segundo idioma en adolescentes aprendiendo inglés. إن هدف هذه الدراسة الرئيسي هو سد الفجوة بين الأبحاث بشأن المتغيرات المتعلقة بمهارات تعلم القراءة والكتابة في الإنكليزية، كما يوجد في النظرة البسيطة للقراءة، والأبحاث بشأن المتغيرات الاجتماعية الثقافية وخصوصاً التأقلم. تألفت العينة من 94 مراهقاً مهاجراً صينياً من الصفوف 7-12 في منطقة واترلو وفي منطقة ترونتو العاصمية في أونتاريو كندا. لقد تم قياس التأقلم بواسطة استبيان. وقد تم تقييم مهارات القراءة والكتابة بما فيها المفردات وسلاسة القراءة واستيعاب القراءة على الانفراد باستخدام امتحانات قياسية. تكشف تحليلات الانحدار الهرمي أن درجات التأقلم مع الثقافة الكندية تكهنت مهارات القارءة والكتابة بالإنكليزية تكهناً إيجابياً بعد الأخذ بعين الاعتبار طول الإقامة في كندا. والجدير بالذكر إن التأقلم أوضح التباعد الفريد في القراءة ما وراء المتغيرات في النظرة البسيطة للقراءة، وذلك بالمساهمة المستقلة من قبل العوامل الاجتماعية الثقافية في قراءة لغة ثانية خاصة بمتعلمي الإنكليزية المراهقين. Aвтop paбoтaeт нa cтыкe иccлeдoвaний, пocвящeнныx кoгнитивным пepeмeнным, кoтopыe cвязaны c ycвoeниeм aнглийcкoгo языкa и cтaнoвлeниeм гpaмoтнocти – в cooтвeтcтвии c пpocтыми пpeдcтaвлeниями o пpoцecce чтeния, – и иccлeдoвaний, пocвящeнныx coциoкyльтypным пepeмeнным, в ocoбeннocти aккyльтypaции. Bыбopкa cocтoялa из 94 yчeникoв 7—12 клaccoв, вce oни pacтyт в ceмьяx китaйcкиx иммигpaнтoв и пpoживaют в Кaнaдe – гopoдкe Baтepлoo в пpoвинции Oнтapиo и в пpигopoдax Topoнтo. Cтeпeнь aккyльтypaции зaмepялacь aнкeтиpoвaниeм. Haвыки гpaмoтнocти – cлoвapный зaпac, бeглocть чтeния и пoнимaниe пpoчитaннoгo – oцeнивaлиcь индивидyaльнo нa ocнoвe тecтoв. Иepapxичecкий peгpeccиoнный aнaлиз пoкaзывaeт, чтo – нapядy c пpoдoлжитeльнocтью жизни в Кaнaдe – cтeпeнь aккyльтypaции пoвышaeт шaнcы oвлaдeть aнглийcким языкoм. Интepecнo, чтo cтeпeнь aккyльтypaции oбъяcняeт yникaльныe paзличия в нaвыкax чтeния пoмимo нaзвaнныx пepeмeнныx, чтo cвидeтeльcтвyeт o нeзaвиcимoм влиянии coциoкyльтypныx фaктopoв нa ocвoeниe пoдpocткaми втopoгo языкa. Le principal objectif de cette étude était de jeter un pont entre la littérature sur les variables cognitives liées aux compétences nécessaires à l'apprentissage de la lecture-écriture en anglais, telles que suggérées par la façon dont on se représente la lecture, et la littérature relative aux variables socioculturelles, plus précisément l'acculturation. L'échantillon est constitué de 94 adolescents immigrés de Chine, collégiens et lycéens de la région de Waterloo et de la région métropolitaine de Toronto dans l'Ontario, Canada. L'acculturation a été évaluée à l'aide d'un questionnaire. Les compétences en lecture, dont le vocabulaire, la lecture courante, et la compréhension de la lecture, ont été évaluées individuellement à l'aide de tests standardisés. L'analyse de régression hiérarchique révèle que les degrés d'acculturation à la culture canadienne permettent de prédire le degré de compétence en lecture-écriture après contrôle de la durée de la résidence au Canada. Il est intéressant de remarquer que l'acculturation permet à elle seule d'expliquer la variance en lecture, au-delà des variables de la façon dont on se représente la lecture, ce qui laisse penser que les facteurs socio-culturels contribuent de façon indépendante à l'apprentissage de la lecture dans une seconde langue des adolescents apprenant en anglais.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>['John Cairney', 'Scott Veldhuizen', 'Jeffrey D. Graham', 'Christine Rodriguez', 'Chloe Bedard', 'Emily Bremer', 'Dean Kriellaars']</t>
+          <t>['Fanli Jia', 'Alexandra Gottardo', 'Poh Wee Koh', 'Xi Chen', 'Adrian Pasquarella']</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>[['McMaster University', 'https://ror.org/02fa3aq29'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['Impact', 'https://ror.org/05d9dsr70'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['University of Manitoba', 'https://ror.org/02gfys938']]</t>
+          <t>[['Wilfrid Laurier University', 'https://ror.org/00fn7gb05'], ['Wilfrid Laurier University', 'https://ror.org/00fn7gb05'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['University of Delaware', 'https://ror.org/01sbq1a82']]</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="K40" t="b">
         <v>0</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1249/mss.0000000000001494</t>
+          <t>https://doi.org/10.1002/rrq.69</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2768220913</t>
+          <t>https://openalex.org/W2041761637</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1249/mss.0000000000001494</t>
+          <t>https://doi.org/10.1186/s12888-014-0379-4</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>A Construct Validation Study of PLAYfun</t>
+          <t>Sustained improvements in students’ mental health literacy with use of a mental health curriculum in Canadian schools</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2017</v>
-      </c>
-      <c r="F41" t="inlineStr"/>
+        <v>2014</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>cc-by</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Physical Literacy Assessment for Youth (PLAYfun) is a measure of motor competence, comprehension, and confidence which is part of a suite of scales used to assess physical literacy in children and youth; however, its measurement properties have not been reported in the published literature. The purpose of this study is to examine the factor structure of PLAYfun, in addition to variations in PLAYfun subscale results by age and sex.In this study, we use a sample of children and youth 7 to 14 yr of age (n = 215) to test a proposed factor structure for the motor competence component of PLAYfun and to examine age and sex differences in subscale and total scores. The initial (n = 128) and secondary (n = 98) samples were drawn from a stratified (by geographic region), random sample of 27 after-school programs from a larger pool of 400 programs across the province of Ontario. Seven research assistants were initially trained on the administration of PLAYfun and rated a small pilot sample of 10 children. These trained assessors then assessed the full sample.Interrater agreement was very good (intraclass correlation, 0.87). The hypothesized five-factor structure of the scale was found to have an acceptable fit to the data (root mean square error of approximation, 0.055; 90% confidence interval, 0.03-0.075; comparative fit index, 0.95; Tucker-Lewis Index, 0.94). In general, PLAYfun scores increased with age as developmentally expected. There were few sex differences across skills, but girls did not perform as well as boys on upper and lower body object control skills.The factor structure and patterns of results by age and sex support PLAYfun as a measure of motor competence. Continued evaluation of the tool and other subscales of PLAY is required.</t>
+          <t>Enhancement of mental health literacy for youth is a focus of increasing interest for mental health professionals and educators alike. Schools are an ideal site for addressing mental health literacy in young people. Currently, there is limited evidence regarding the impact of curriculum-based interventions within high school settings. We examined the effect of a high-school mental health curriculum (The Guide) in enhancing mental health literacy in Canadian schools. We conducted a secondary analysis on surveys of students who participated in a classroom mental health course taught by their usual teachers. Evaluation of students' mental health literacy (knowledge/attitudes) was completed before and after classroom implementation and at 2-month follow-up. We used paired-samples t-tests and Cohen's d value to determine the significance and impact of change. There were 265 students who completed all surveys. Students' knowledge significantly improved between pre- and post-tests (p &lt; 0.001; d = 0.90) and was maintained at follow-up (p &lt; 0.001; d = 0.73). Similarly, attitude significantly improved between pre- and post-tests (p &lt; 0.001; d = 0.25) and was significantly higher at follow-up than base-line (p &lt; 0.007; d = 0.18) The Guide, applied by usual teachers in usual classroom curriculum, may help improve student knowledge and attitudes regarding mental health. This is the first study to demonstrate the positive impact of a curriculum-based mental health literacy program in a Canadian high school population.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>['John Cairney', 'Scott Veldhuizen', 'Jeffrey D. Graham', 'Christine Rodriguez', 'Chloe Bedard', 'Emily Bremer', 'Dean Kriellaars']</t>
+          <t>['Alan McLuckie', 'Stan Kutcher', 'Yifeng Wei', 'Cynthia Weaver']</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>[['McMaster University', 'https://ror.org/02fa3aq29'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['Impact', 'https://ror.org/05d9dsr70'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['University of Manitoba', 'https://ror.org/02gfys938']]</t>
+          <t>[['University of Calgary', 'https://ror.org/03yjb2x39'], ['Izaak Walton Killam Health Centre', 'https://ror.org/0064zg438'], ['Dalhousie University', 'https://ror.org/01e6qks80'], ['Dalhousie University', 'https://ror.org/01e6qks80'], ['Izaak Walton Killam Health Centre', 'https://ror.org/0064zg438'], ['Ontario Shores Centre for Mental Health Sciences', 'https://ror.org/04mcqge53']]</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>58</v>
+        <v>213</v>
       </c>
       <c r="K41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1249/mss.0000000000001494</t>
+          <t>https://doi.org/10.1186/s12888-014-0379-4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://openalex.org/W4311236699</t>
+          <t>https://openalex.org/W2017521086</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://doi.org/10.21083/partnership.v17i2.6808</t>
+          <t>https://doi.org/10.1007/s13187-014-0744-5</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Early Literacy Learning for Future Library Paraprofessionals: Authentic Learning in Library Education</t>
+          <t>Predictors of High eHealth Literacy in Primary Lung Cancer Survivors</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2022</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>cc-by-nc-nd</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>This article describes the professional learning around early literacy experienced by library paraprofessional students at a post-secondary institution in Canada. Students completed a survey to gauge their conceptions of early literacy at the beginning of a course on library services for children and young adults. These students then experienced hands-on, engaging course elements such as in-class discussions, guest speakers, and authentic assessments. At the conclusion of the course, students were again surveyed and were asked to identify course elements that contributed to their learning. Most students aligned with an emergent literacy approach to early literacy. While a comparison between the two surveys did not reveal a significant difference in terms of students’ conceptions of early literacy, multiple students identified the hands-on elements of the course as beneficial. The researchers conclude that providing authentic professional learning opportunities that include knowledge application reinforces learners’ conceptions about emergent literacy.</t>
-        </is>
-      </c>
+        <v>2014</v>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>['Alvina Mardhani-Bayne', 'Lisa Shamchuk']</t>
+          <t>['Robin Milne', 'Martine Puts', 'Janet Papadakos', 'Lisa W. Le', 'Victoria Milne', 'Andrew Hope', 'Pamela Catton', 'Meredith Giuliani']</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>[['MacEwan University', 'https://ror.org/003s89n44'], ['MacEwan University', 'https://ror.org/003s89n44']]</t>
+          <t>[['Princess Margaret Cancer Centre', 'https://ror.org/03zayce58'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['Princess Margaret Cancer Centre', 'https://ror.org/03zayce58'], ['Princess Margaret Cancer Centre', 'https://ror.org/03zayce58'], ['Princess Margaret Cancer Centre', 'https://ror.org/03zayce58'], ['Princess Margaret Cancer Centre', 'https://ror.org/03zayce58'], ['Princess Margaret Cancer Centre', 'https://ror.org/03zayce58'], ['Princess Margaret Cancer Centre', 'https://ror.org/03zayce58']]</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>2</v>
+        <v>89</v>
       </c>
       <c r="K42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>https://doi.org/10.21083/partnership.v17i2.6808</t>
+          <t>https://doi.org/10.1007/s13187-014-0744-5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://openalex.org/W4283837859</t>
+          <t>https://openalex.org/W2518045192</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://doi.org/10.21083/partnership.v17i1.6574</t>
+          <t>https://doi.org/10.1093/ckj/sfw076</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>A Text Analysis of Four Levels of Librarian Involvement and Impact on Students in an Inquiry-Based Learning Course</t>
+          <t>An observational study of health literacy and medication adherence in adult kidney transplant recipients</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>cc-by-nc-nd</t>
+          <t>cc-by-nc</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Librarians at the University of Calgary collaborated with instructors on an inquiry-based learning course with varying involvement across four course sections. This study uses text analysis of student assignments to assess information literacy (IL) skill development across four levels of course participation: librarian as instructor-of-record, two levels of embeddedness, and a single ‘one-shot’ session. The methodology included the tracking of keywords generated using the ACRL Framework for Information Literacy and text analysis of student reflection assignments in an inquiry-based, research-focused first-year undergraduate course. The results suggest that the benefit to student IL skills is not related to amount of librarian instruction, but rather to the level of instructor buy-in with regard to library services and the importance of IL skills. We argue that the most impactful librarian involvement is as an IL course consultant rather than a full-time embedded librarian (which is surprising given the literature on the efficacy of embeddedness). Although further research is needed, the study results have significant implications for academic librarian instructional practices and collaborations on course content with faculty members.</t>
+          <t>There is a high prevalence of non-adherence to immunosuppressants in kidney transplant recipients. Although limited health literacy is common in kidney recipients and is linked to adverse outcomes in other medical populations, its effect on medication adherence in kidney transplant recipients remains poorly understood. The objective was to investigate the effect of lower health literacy on immunosuppressant adherence. Kidney recipients who were at least 6 months post-transplant and outpatients of Vancouver General Hospital in B.C., Canada were recruited through invitation letters. A total of 96 recipients completed the Health Literacy Questionnaire, which provides a multifactorial profile of self-reported health literacy and the Transplant Effects Questionnaire-Adherence subscale measuring self-reported immunosuppressant adherence. Hierarchical linear regression was used to analyze the association between health literacy and adherence after controlling for identified risk factors of non-adherence. Our sample was on average 53 years old, 56% male and 9 years post-transplant. Kidney recipients reported low levels of health literacy on scales measuring active health management and critical appraisal of information and 75% reported non-perfect adherence. Worse adherence was associated with poorer overall health literacy (ΔR2 = 0.08, P = 0.004) and lower scores on six of nine of the health literacy factors. Poorer health literacy is associated with lower immunosuppressant adherence in adult kidney transplant recipients suggesting the importance of considering a recipient's level of health literacy in research and clinical contexts. Medication adherence interventions can target the six factors of health literacy identified as being risk factors for lower medication adherence.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>['Marc Stoeckle', 'James E. Murphy', 'Bartlomiej A. Lenart']</t>
+          <t>['Maryam Demian', 'R. Jean Shapiro', 'Wendy Loken Thornton']</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>[['University of Calgary', 'https://ror.org/03yjb2x39'], ['University of Calgary', 'https://ror.org/03yjb2x39'], ['University of Calgary', 'https://ror.org/03yjb2x39']]</t>
+          <t>[['Simon Fraser University', 'https://ror.org/0213rcc28'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['Simon Fraser University', 'https://ror.org/0213rcc28']]</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="K43" t="b">
         <v>1</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>https://doi.org/10.21083/partnership.v17i1.6574</t>
+          <t>https://doi.org/10.1093/ckj/sfw076</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://openalex.org/W1917627399</t>
+          <t>https://openalex.org/W2291543154</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1186/s12889-015-2106-6</t>
+          <t>https://doi.org/10.1080/02701367.2016.1124722</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>The Canadian Assessment of Physical Literacy: methods for children in grades 4 to 6 (8 to 12 years)</t>
+          <t>Implications of Physical Literacy for Research and Practice: A Commentary</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2015</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>cc-by</t>
-        </is>
-      </c>
+        <v>2016</v>
+      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Physical literacy is described as the motivation, confidence, physical competence, knowledge and understanding to value and engage in a physically active lifestyle. As such, it is expected that those who have greater physical literacy would be more likely to obtain the health benefits offered by habitual physical activity. A theoretical model and assessment battery, the Canadian Assessment of Physical Literacy (CAPL), for the assessment of childhood physical literacy had been proposed in theory but validity data were lacking. The purpose of this study was to explore validity evidence for the CAPL among children in grades 4 to 6.CAPL validity was evaluated through three analyses that utilized cross-sectional data obtained through local schools in Eastern Ontario, Canada. A confirmatory factor analysis compared the data to the theoretical model. Patterns of association between self-reported age and gender and the CAPL total and domain scores were examined using regression models. Teacher ratings of participants' knowledge, attitude and physical activity competence were compared to assessment results.The CAPL was completed by 963 children (55 % female) in grades 4, 5 and 6. Children were 8 to 12 years of age (mean 10.1 years), with 85 % of children approached agreeing to participate. A confirmatory factor analysis using data from 489 children with complete raw scores supported a model with four domains: engagement in physical activity (active and sedentary), physical competence (fitness and motor skill), motivation and confidence, and knowledge and understanding. Raw domain scores followed expected patterns for age and gender, providing evidence for their validity. Interpretive categories, developed from age and gender adjusted normative data, were not associated with age indicating that the CAPL is suitable for use across this age range. Children's gender was associated with the physical competence, motivation and engagement in physical activity domain scores, indicating that further research is required regarding the gender adjustment of the raw CAPL scores. CAPL domain and total scores were statistically significantly associated with teacher ratings of the child's motivation, attitudes, fitness, skill and overall physical activity.CAPL offers a comprehensive assessment of engagement in physical activity, physical competence, motivation and confidence, and knowledge and understanding as components of childhood (grades 4 to 6, 8 to 12 years) physical literacy. Monitoring of these measures enhances our understanding of children's physical literacy, and assists with the identification of areas where additional supports are required.</t>
+          <t>Physical literacy is a term that has increasingly gained popularity in recent years. A variety of individuals and organizations have promoted the use of the term internationally, and a variety of claims have been made for the benefits of using the term. A historical overview allows the reader to consider physical literacy as one of many terms that have gained popularity in the field and describes divergent views as well as areas of agreement concerning the term physical literacy. Three North American institutional approaches to physical literacy are discussed. Other issues are also discussed, including assessment and other literacy types (e.g., health, sports). The article is designed to provoke thought among professionals and representatives of institutions concerning physical literacy.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>['Patricia E. Longmuir', 'Charles P. Boyer', 'Meghann Lloyd', 'Yan Yang', 'Elena Boiarskaia', 'Weimo Zhu', 'Mark S. Tremblay']</t>
+          <t>['Charles B. Corbin']</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>[["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Ontario Institute of Technology', 'https://ror.org/016zre027'], ['University of Illinois Urbana-Champaign', 'https://ror.org/047426m28'], ['University of Illinois Urbana-Champaign', 'https://ror.org/047426m28'], ['University of Illinois Urbana-Champaign', 'https://ror.org/047426m28'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Ottawa', 'https://ror.org/03c4mmv16']]</t>
+          <t>[['Arizona State University', 'https://ror.org/03efmqc40']]</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>211</v>
+        <v>144</v>
       </c>
       <c r="K44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1186/s12889-015-2106-6</t>
+          <t>https://doi.org/10.1080/02701367.2016.1124722</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2030066779</t>
+          <t>https://openalex.org/W2921451314</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3138/cmlr.2346</t>
+          <t>https://doi.org/10.1016/j.psychres.2019.03.009</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>The Predictive Effects of L1 and L2 Early Literacy Indicators on Reading in French Immersion</t>
+          <t>Establishment and validation of a mental health literacy measurement in Canadian educators</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Abstract: This study explored the predictive effects of within- and cross-language early literacy indicators with regard to second language (L2) reading achievement in a Grade 3 entry-point French immersion (FI) program. Kindergarten students (N = 83) in a regular English program were administered English early literacy measures. Three years later, once students entered the FI, 56 students from the original cohort were reassessed using French literacy measures. This allowed for an examination of the long-term connections between first language (L1) early literacy indicators and L2 reading outcomes. Regression analysis revealed that L1 early literacy skills relating to aspects of phonological awareness and, more importantly, alphabetic knowledge were significant predictors of L2 reading even when school-based L2 learning was delayed several years. With respect to the French literacy indicators, knowledge of the alphabet and related measures were again significant predictors of L2 reading performance. The predictive effects of French indicators were significant even in the first few months of FI. These results provide additional information about the predictive effects of within- and cross-language early literacy indicators and the extent to which they can be used to identify students who may be at risk for reading difficulties in their L2.</t>
-        </is>
-      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>['Renée Bourgoin']</t>
+          <t>['Yifeng Wei', 'Andrew Baxter', 'Stan Kutcher']</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[['Izaak Walton Killam Health Centre', 'https://ror.org/0064zg438'], ['Dalhousie University', 'https://ror.org/01e6qks80'], ['Alberta Health Services', 'https://ror.org/02nt5es71'], ['Izaak Walton Killam Health Centre', 'https://ror.org/0064zg438'], ['Dalhousie University', 'https://ror.org/01e6qks80']]</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="K45" t="b">
         <v>0</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3138/cmlr.2346</t>
+          <t>https://doi.org/10.1016/j.psychres.2019.03.009</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2067140869</t>
+          <t>https://openalex.org/W2624920485</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.jcjo.2014.08.002</t>
+          <t>https://doi.org/10.1016/j.ijmedinf.2017.06.001</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Patient-appropriate health literacy educational materials in ophthalmology</t>
+          <t>Barriers to technology use among older heart failure individuals in managing their symptoms after hospital discharge</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>['David Mikhail', 'Kari L. Visscher', 'Nancy Chen', 'Joy Wang', 'Barry Y. Emara', 'Cindy Hutnik']</t>
+          <t>['Linda Nguyen', 'Karim Keshavjee', 'Norm Archer', 'Christopher Patterson', 'Femida Gwadry‐Sridhar', 'Catherine Demers']</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>[['Western University', 'https://ror.org/02grkyz14'], ['Western University', 'https://ror.org/02grkyz14'], ['Western University', 'https://ror.org/02grkyz14'], ['Western University', 'https://ror.org/02grkyz14'], ['Western University', 'https://ror.org/02grkyz14'], ['Western University', 'https://ror.org/02grkyz14']]</t>
+          <t>[['McMaster University', 'https://ror.org/02fa3aq29'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['Western University', 'https://ror.org/02grkyz14'], ['McMaster University', 'https://ror.org/02fa3aq29']]</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="K46" t="b">
         <v>0</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.jcjo.2014.08.002</t>
+          <t>https://doi.org/10.1016/j.ijmedinf.2017.06.001</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2754071577</t>
+          <t>https://openalex.org/W2755779874</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://doi.org/10.18848/2327-0136/cgp/v22i04/1-26</t>
+          <t>https://doi.org/10.24095/hpcdp.37.9.06</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Is Student Achievement on Standardized EQAO Testing Reflected in Their Annual Academic Performance? A Longitudinal Study</t>
+          <t>The Ontario Food and Nutrition Strategy: identifying indicators of food access and food literacy for early monitoring of the food environment</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2015</v>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
+        <v>2017</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>cc-by</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>To address challenges Canadians face within their food environments, a comprehensive, multistakeholder, intergovernmental approach to policy development is essential. Food environment indicators are needed to assess population status and change. The Ontario Food and Nutrition Strategy (OFNS) integrates the food, agriculture and nutrition sectors, and aims to improve the health of Ontarians through actions that promote healthy food systems and environments. This report describes the process of identifying indicators for 11 OFNS action areas in two strategic directions (SDs): Healthy Food Access, and Food Literacy and Skills.The OFNS Indicators Advisory Group used a five-step process to select indicators: (1) potential indicators from national and provincial data sources were identified; (2) indicators were organized by SD, action area and data type; (3) selection criteria were identified, pilot tested and finalized; (4) final criteria were applied to refine the indicator list; and (5) indicators were prioritized after reapplication of selection criteria.Sixty-nine potential indicators were initially identified; however, many were individual-level rather than system-level measures. After final application of the selection criteria, one individual-level indicator and six system-level indicators were prioritized in five action areas; for six of the action areas, no indicators were available.Data limitations suggest that available data may not measure important aspects of the food environment, highlighting the need for action and resources to improve system-level indicators and support monitoring of the food environment and health in Ontario and across Canada.Une approche intergouvernementale multilatérale globale en matière d’élaboration de politiques est essentielle pour permettre aux Canadiens et aux Canadiennes de faire face aux défis que pose leur environnement alimentaire. Des indicateurs de l’environnement alimentaire sont nécessaires pour évaluer l’état et l’évolution de la population. La Stratégie sur l’alimentation et la nutrition de l’Ontario (SANO), qui regroupe les secteurs de l’alimentation, de l’agriculture et de la nutrition, vise à améliorer la santé de la population ontarienne par des interventions favorisant des systèmes et des environnements alimentaires sains. Cet article décrit le processus d’établissement d'indicateurs pour 11 secteurs d’intervention de la SANO dans deux orientations stratégiques : l’accès à des aliments sains et l’alphabétisme et les compétences alimentaires.Le groupe consultatif sur les indicateurs de la SANO a suivi un processus en cinq étapes pour choisir les indicateurs : 1) choix des indicateurs potentiels dans les sources de données provinciales et nationales, 2) catégorisation des indicateurs par orientation stratégique, par secteur d’intervention et par type de données, 3) établissement, essai pilote et finalisation des critères de sélection, 4) application des critères finaux pour améliorer la liste des indicateurs et 5) établissement des indicateurs prioritaires après cette application finale des critères de sélection.Soixante-neuf indicateurs potentiels ont été recensés au départ, mais un grand nombre d’entre eux offraient des mesures individuelles et non collectives. Après l’application finale des critères de sélection, ont été jugés prioritaires un indicateur individuel et six indicateurs collectifs associés à cinq secteurs d’intervention, aucun indicateur n’étant disponible pour les six autres secteurs d’intervention.Les limites des données existantes laissent penser qu’on ne peut sans doute pas qualifier certaines caractéristiques importantes de l’environnement alimentaire, d’où l’importance de prendre des mesures et d’allouer des ressources pour améliorer les indicateurs collectifs et d’appuyer le suivi de l’environnement alimentaire et de la santé alimentaire tant en Ontario que dans le reste du Canada.</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>['Roxanne Landry', 'Michèle Minor-Corriveau', 'Roxanne Bélanger']</t>
+          <t>['Beatrice A. Boucher', 'Elizabeth Manafò', 'Meaghan R. Boddy', 'Lynn Roblin', 'Rebecca Truscott']</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[['Cancer Care Ontario', 'https://ror.org/029n6xw55'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['Toronto Metropolitan University', 'https://ror.org/05g13zd79'], ['Cancer Care Ontario', 'https://ror.org/029n6xw55'], ['Cancer Care Ontario', 'https://ror.org/029n6xw55']]</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>https://doi.org/10.18848/2327-0136/cgp/v22i04/1-26</t>
+          <t>https://doi.org/10.24095/hpcdp.37.9.06</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2082979380</t>
+          <t>https://openalex.org/W2801027355</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.pec.2014.04.014</t>
+          <t>https://doi.org/10.3389/fped.2018.00138</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Health literacy and its association with perception of teratogenic risks and health behavior during pregnancy</t>
+          <t>The Preschool Physical Literacy Assessment Tool: Testing a New Physical Literacy Tool for the Early Years</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2014</v>
-      </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
+        <v>2018</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>cc-by</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Background: Physical literacy is essential to physical activity across the lifespan. While there is an emerging body of research on physical literacy in school-aged children, the preschool years have largely been ignored. We tested the psychometric properties of new tool, the Preschool Physical Literacy Assessment Tool (Pre-PLAY) designed to address this gap. Methods: We recruted 78 children (aged 19 to 49 months) across 5 childcare centers in Hamilton, Ontario. Two Early Childhood Educators (ECE) completed the Pre-PLAY for each child at two points in time to assess inter-rater reliability and test-retest reliability. We assessed the agreement between the Pre-PLAY tool with gross motor skills and the ability of the PPLAy to predict physical activity. Results: Results indicated Pre-PLAY is related to gross motor skills and predictive of physical activity for females, but not males. Inter-rater and intra-rater reliability was at least adequate for all but the co-orindated movements items and scale for females, but ECEs showed poor agreement for males. Conclusions: These results suggest initial support for the Pre-PLAY tool as a measure of physical literacy during the early years. However, some modification to the items and training are required to address the gender-specific effects found in this sample.</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>['Angela Lupattelli', 'Marta Picinardi', 'Adrienne Einarson', 'Hedvig Nordeng']</t>
+          <t>['John Cairney', 'Heather J. Clark', 'Maeghan E. James', 'Drew Mitchell', 'Dean Dudley', 'Dean Kriellaars']</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>[['University of Oslo', 'https://ror.org/01xtthb56'], ['University of Oslo', 'https://ror.org/01xtthb56'], ['Hospital for Sick Children', 'https://ror.org/057q4rt57'], ['SickKids Foundation', 'https://ror.org/04374qe70'], ['University of Oslo', 'https://ror.org/01xtthb56'], ['Norwegian Institute of Public Health', 'https://ror.org/046nvst19']]</t>
+          <t>[['University of Toronto', 'https://ror.org/03dbr7087'], ['Friends For Life', 'https://ror.org/042n1mt30'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['Friends For Life', 'https://ror.org/042n1mt30'], ['Macquarie University', 'https://ror.org/01sf06y89'], ['Friends For Life', 'https://ror.org/042n1mt30'], ['Friends For Life', 'https://ror.org/042n1mt30'], ['University of Manitoba', 'https://ror.org/02gfys938']]</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>91</v>
+        <v>27</v>
       </c>
       <c r="K48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.pec.2014.04.014</t>
+          <t>https://doi.org/10.3389/fped.2018.00138</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2211885666</t>
+          <t>https://openalex.org/W2894925006</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3899/jrheum.141509</t>
+          <t>https://doi.org/10.1186/s12889-018-5902-y</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Health Literacy Rates in a Population of Patients with Rheumatoid Arthritis in Southwestern Ontario</t>
+          <t>Canadian Assessment of Physical Literacy Second Edition: a streamlined assessment of the capacity for physical activity among children 8 to 12 years of age</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2015</v>
-      </c>
-      <c r="F49" t="inlineStr"/>
+        <v>2018</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>cc-by</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Objective. To determine the rate of low health literacy in the rheumatoid arthritis (RA) population in southwestern Ontario. Methods. For the study, 432 patients with RA were contacted, and 311 completed the assessment. The health literacy levels of the participants were estimated using 4 assessment tools administered in the following order: the Single Item Literacy Screener (SILS), the Medical Term Recognition Test (METER), the Rapid Estimate of Adult Literacy in Medicine (REALM), and the Shortened Test of Functional Health Literacy in Adults (STOFHLA). Results. The rates of low literacy as estimated by STOFHLA, REALM, METER, and SILS were 14.5%, 14.8%, 14.1%, and 18.6%, respectively. All 4 assessment tools were statistically significantly correlated. STOFHLA, REALM, and METER were strongly correlated with each other (r = 0.59–0.79), while SILS only demonstrated moderate correlations with the other assessment tools (r = 0.33–0.45). Multiple linear regression and binary logistic regression analyses revealed that low levels of education and a lack of daily reading activity were common predictors of low health literacy. Using a non-English primary language at home was found to be a strong predictor of low health literacy in STOFHLA, REALM, and METER. Male sex was found to be a significant predictor of poor performance in REALM and METER, but not STOFHLA. Conclusion. Low health literacy is an important issue in the southwestern Ontario RA population. About 1 in 7 patients with RA may not have the necessary skills to become involved in making decisions regarding their personal health. Rheumatologists should be aware of the low health literacy levels of patients with RA and should consider identifying patients at risk of low health literacy.</t>
+          <t>The Canadian Assessment of Physical Literacy (CAPL) assesses the capacity of children to lead a physically active lifestyle. It is comprised of a battery of standardized assessment protocols that reflect the Canadian consensus definition of physical literacy. The Royal Bank of Canada Learn to Play - Canadian Assessment of Physical Literacy study implemented the CAPL with 10,034 Canadian children (50.1% female), 8 to 12 years of age. Feedback during data collection, necessary changes identified by the coordinating centre, and recent data analyses suggested that a streamlined, second edition of the CAPL was required. The purpose of this paper is to describe the methods used to develop the CAPL second edition (CAPL-2).The larger dataset created through the RBC-Learn to Play CAPL study enabled the re-examination of the CAPL model through factor analyses specific to Canadian children 8 to 12 years of age from across Canada. This comprehensive database was also used to examine the CAPL protocols for redundancy or variables that did not contribute significantly to the overall assessment. Removing redundancy had been identified as a priority in order to reduce the high examiner and participant burden. The "lessons learned" from such a large national surveillance project were reviewed for additional information regarding the changes that would be required to optimize the assessment of children's physical literacy. In addition, administrative changes, improvements, and corrections were identified as necessary to improve the quality and accuracy of the CAPL manual and training materials.For each domain of the CAPL, recommended changes based on the factor analyses, qualitative feedback and theoretical considerations significantly reduced the number of protocols. Specific protocol combinations were then evaluated for model fit within the overarching concept of physical literacy. The CAPL-2 continues to reflect the four components of the Canadian consensus definition of physical literacy: Motivation and Confidence, Physical Competence, Knowledge and Understanding, and engagement in Physical Activity Behaviour. The CAPL-2 is comprised of three Physical Competence protocols (plank, Progressive Aerobic Cardiovascular Endurance Run [PACER], Canadian Agility and Movement Skill Assessment [CAMSA]), two Daily Behaviour protocol (pedometer steps, self-reported physical activity), and a 22-item questionnaire assessing the physical literacy domains of Motivation and Confidence, and Knowledge and Understanding. Detailed information about the CAPL-2 is available online ( www.capl-eclp.ca ).The CAPL-2 dramatically reduces examiner and participant burden (three Physical Competence protocols, two Daily Behaviour protocols, and a 22-response questionnaire; versus eight Physical Competence protocols, three Daily Behaviour protocols and a 72-response questionnaire for the original CAPL), while continuing to be a comprehensive assessment of all aspects of children's physical literacy using the Canadian consensus definition of this term. Like the original, the CAPL-2 continues to offer maximum flexibility to practitioners, who can choose to complete the entire CAPL-2 assessment, only one or more domains, or select individual protocols. Regardless of the assessment selected, scores are available to interpret the performance of each child relative to Canadian children of the same age and sex. All of the protocols included in the CAPL-2 have published reports of validity and reliability for this age group (8 to 12 years). The detailed manual for CAPL-2 administration, along with training materials and other resources, are available free of charge on the CAPL-2 website ( www.capl-eclp.ca ). All CAPL-2 materials and resources, including the website, are available in both English and French.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>['Zhaowei Gong', 'Sara Haig', 'Janet Pope', 'Sherry Rohekar', 'Gina Rohekar', 'Nicole G. H. LeRICHE', 'Andrew Thompson']</t>
+          <t>['Patricia E. Longmuir', 'Katie E. Gunnell', 'Joel D. Barnes', 'Kevin Belanger', 'Geneviève Leduc', 'Sarah J. Woodruff', 'Mark S. Tremblay']</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>[["St Joseph's Health Care", 'https://ror.org/05rj7xr73'], ['Western University', 'https://ror.org/02grkyz14'], ["St Joseph's Health Care", 'https://ror.org/05rj7xr73'], ['Western University', 'https://ror.org/02grkyz14'], ['Western University of Health Sciences', 'https://ror.org/05167c961'], ['Western University', 'https://ror.org/02grkyz14'], ["St Joseph's Health Care", 'https://ror.org/05rj7xr73'], ['Western University of Health Sciences', 'https://ror.org/05167c961'], ["St Joseph's Health Care", 'https://ror.org/05rj7xr73'], ['Western University', 'https://ror.org/02grkyz14'], ['Western University of Health Sciences', 'https://ror.org/05167c961'], ["St Joseph's Health Care", 'https://ror.org/05rj7xr73'], ['Western University', 'https://ror.org/02grkyz14'], ['Western University of Health Sciences', 'https://ror.org/05167c961'], ["St Joseph's Health Care", 'https://ror.org/05rj7xr73'], ['Western University', 'https://ror.org/02grkyz14'], ['Western University of Health Sciences', 'https://ror.org/05167c961'], ["St Joseph's Health Care", 'https://ror.org/05rj7xr73'], ['Western University', 'https://ror.org/02grkyz14'], ['Western University of Health Sciences', 'https://ror.org/05167c961']]</t>
+          <t>[["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['Carleton University', 'https://ror.org/02qtvee93'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Windsor', 'https://ror.org/01gw3d370'], ['University of Ottawa', 'https://ror.org/03c4mmv16']]</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>8</v>
+        <v>113</v>
       </c>
       <c r="K49" t="b">
         <v>1</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3899/jrheum.141509</t>
+          <t>https://doi.org/10.1186/s12889-018-5902-y</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://openalex.org/W1728407011</t>
+          <t>https://openalex.org/W2894914095</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/rrq.69</t>
+          <t>https://doi.org/10.1186/s12889-018-5898-3</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>The Role of Acculturation in Reading a Second Language: Its Relation to English Literacy Skills in Immigrant Chinese Adolescents</t>
+          <t>Associations between domains of physical literacy by weight status in 8- to 12-year-old Canadian children</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2014</v>
-      </c>
-      <c r="F50" t="inlineStr"/>
+        <v>2018</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>cc-by</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>The main purpose of this study was to bridge the gap between the literature on cognitive variables related to English literacy learning skills, as suggested by the simple view of reading, and the literature on sociocultural variables, specifically acculturation. The sample consisted of 94 Chinese immigrant adolescents from grades 7–12 in Waterloo Region in and the metropolitan Toronto area of Ontario, Canada. Acculturation was measured by a questionnaire. Literacy skills, including vocabulary, reading fluency, and reading comprehension, were assessed individually using standardized tests. Hierarchical regression analyses reveal that degrees of acculturation to Canadian culture positively predicted English literacy skills after controlling for length of residence in Canada. Interestingly, acculturation explained unique variance in reading beyond variables in the simple view of reading, suggesting the independent contribution of sociocultural factors to second-language reading in adolescent English learners. 本研究旨在弥合文献上两种变数之间的差距;其一是按简单阅读观所提出与英语读写技能相关的认知变数,其二是与社会文化,尤其与文化适应相关的变数。本研究样本取自加拿大安大略省多伦多市区和滑铁卢地区的7至12年级的94名中国移民青少年。研究者通过问卷调查衡量文化适应,并通过标准化单独测试评估读写技能,包括词汇、阅读流畅度和阅读理解能力。分层回归分析显示,加拿大文化适应程度,在控制了居住在加拿大时间的长短之后,能正面地预测英语读写技能。有趣的是,文化适应能解释简单阅读观之外的阅读变数的独特方差,这显示出社会文化因素对第二语言青少年英语学习者的阅读具有独特的作用。 El propósito principal de este estudio fue el de llenar el vacío entre la literatura sobre los variables cognitivos relacionados a las destrezas del aprendizaje del inglés, como sugerido por la perspectiva de simplemente leer, y la literatura sobre los variables socioculturales, específicamente aculturación. La muestra consistió de 94 inmigrantes chinos adolescentes entre el 7mo y 12mo grado en Waterloo Region y el área metropolitana de Toronto en Ontario, Canadá. Se midió la aculturación por medio de una encuesta. Las destrezas de aprendizaje, incluyendo vocabulario, la fluidez al leer, y la comprensión de la lectura, se midieron individualmente usando exámenes estandarizados. El análisis de regresión jerárquica muestra que el grado de aculturación a la cultura canadiense predecía de manera positiva las destrezas de aprendizaje del inglés, habiéndose controlado por la cantidad de tiempo que se había vivido en Canadá. Lo interesante es que la aculturación explicó variedades originales en la lectura más allá de las variables en la perspectiva simple de lectura, sugiriendo que hay una contribución independiente en los factores socioculturales a la lectura de un segundo idioma en adolescentes aprendiendo inglés. إن هدف هذه الدراسة الرئيسي هو سد الفجوة بين الأبحاث بشأن المتغيرات المتعلقة بمهارات تعلم القراءة والكتابة في الإنكليزية، كما يوجد في النظرة البسيطة للقراءة، والأبحاث بشأن المتغيرات الاجتماعية الثقافية وخصوصاً التأقلم. تألفت العينة من 94 مراهقاً مهاجراً صينياً من الصفوف 7-12 في منطقة واترلو وفي منطقة ترونتو العاصمية في أونتاريو كندا. لقد تم قياس التأقلم بواسطة استبيان. وقد تم تقييم مهارات القراءة والكتابة بما فيها المفردات وسلاسة القراءة واستيعاب القراءة على الانفراد باستخدام امتحانات قياسية. تكشف تحليلات الانحدار الهرمي أن درجات التأقلم مع الثقافة الكندية تكهنت مهارات القارءة والكتابة بالإنكليزية تكهناً إيجابياً بعد الأخذ بعين الاعتبار طول الإقامة في كندا. والجدير بالذكر إن التأقلم أوضح التباعد الفريد في القراءة ما وراء المتغيرات في النظرة البسيطة للقراءة، وذلك بالمساهمة المستقلة من قبل العوامل الاجتماعية الثقافية في قراءة لغة ثانية خاصة بمتعلمي الإنكليزية المراهقين. Aвтop paбoтaeт нa cтыкe иccлeдoвaний, пocвящeнныx кoгнитивным пepeмeнным, кoтopыe cвязaны c ycвoeниeм aнглийcкoгo языкa и cтaнoвлeниeм гpaмoтнocти – в cooтвeтcтвии c пpocтыми пpeдcтaвлeниями o пpoцecce чтeния, – и иccлeдoвaний, пocвящeнныx coциoкyльтypным пepeмeнным, в ocoбeннocти aккyльтypaции. Bыбopкa cocтoялa из 94 yчeникoв 7—12 клaccoв, вce oни pacтyт в ceмьяx китaйcкиx иммигpaнтoв и пpoживaют в Кaнaдe – гopoдкe Baтepлoo в пpoвинции Oнтapиo и в пpигopoдax Topoнтo. Cтeпeнь aккyльтypaции зaмepялacь aнкeтиpoвaниeм. Haвыки гpaмoтнocти – cлoвapный зaпac, бeглocть чтeния и пoнимaниe пpoчитaннoгo – oцeнивaлиcь индивидyaльнo нa ocнoвe тecтoв. Иepapxичecкий peгpeccиoнный aнaлиз пoкaзывaeт, чтo – нapядy c пpoдoлжитeльнocтью жизни в Кaнaдe – cтeпeнь aккyльтypaции пoвышaeт шaнcы oвлaдeть aнглийcким языкoм. Интepecнo, чтo cтeпeнь aккyльтypaции oбъяcняeт yникaльныe paзличия в нaвыкax чтeния пoмимo нaзвaнныx пepeмeнныx, чтo cвидeтeльcтвyeт o нeзaвиcимoм влиянии coциoкyльтypныx фaктopoв нa ocвoeниe пoдpocткaми втopoгo языкa. Le principal objectif de cette étude était de jeter un pont entre la littérature sur les variables cognitives liées aux compétences nécessaires à l'apprentissage de la lecture-écriture en anglais, telles que suggérées par la façon dont on se représente la lecture, et la littérature relative aux variables socioculturelles, plus précisément l'acculturation. L'échantillon est constitué de 94 adolescents immigrés de Chine, collégiens et lycéens de la région de Waterloo et de la région métropolitaine de Toronto dans l'Ontario, Canada. L'acculturation a été évaluée à l'aide d'un questionnaire. Les compétences en lecture, dont le vocabulaire, la lecture courante, et la compréhension de la lecture, ont été évaluées individuellement à l'aide de tests standardisés. L'analyse de régression hiérarchique révèle que les degrés d'acculturation à la culture canadienne permettent de prédire le degré de compétence en lecture-écriture après contrôle de la durée de la résidence au Canada. Il est intéressant de remarquer que l'acculturation permet à elle seule d'expliquer la variance en lecture, au-delà des variables de la façon dont on se représente la lecture, ce qui laisse penser que les facteurs socio-culturels contribuent de façon indépendante à l'apprentissage de la lecture dans une seconde langue des adolescents apprenant en anglais.</t>
+          <t>The Canadian Assessment of Physical Literacy (CAPL) is divided into four domains (Physical Competence, Daily Behaviour, Motivation and Confidence, and Knowledge and Understanding) and provides a robust and comprehensive assessment of physical literacy. As weight status is known to influence health-related behaviours such as physical fitness and activity, it is important to investigate whether the associations between the domains of physical literacy vary among children of different weight status. The aim of this study was to determine the associations among the four domains of physical literacy stratified by weight status.Canadian children aged 8 to 12 years (n = 8343, 63.6% healthy-weight) completed the CAPL. Differences in domain scores and overall physical literacy score by weight status (children of healthy weight versus children with overweight/obese) were assessed using MANOVA (multivariate analysis of variance). Partial correlations between the four domains were calculated, adjusting for gender and age, and correlation coefficients of both weight status groups were compared using the Steiger test.For all four domains as well as overall physical literacy, healthy-weight children had higher scores than their overweight/obese peers (Cohen's d ranged from 0.05 to 0.44). Weak to moderate correlations were found between all of the domains for both groups. Correlation coefficients for Physical Competence and Daily Behaviour as well as for Physical Competence and Knowledge and Understanding were generally stronger in the healthy-weight children (r = 0.29 and 0.22, respectively) compared with the overweight/obese children (r = 0.23 and 0.17, respectively).All of the domains of the CAPL correlate positively with each other regardless of weight status, with a trend for these correlation coefficients to be slightly stronger in the healthy-weight children. The overall weak to moderate correlations between the domains in both groups suggest that the CAPL domains are not measuring the same constructs, thus providing support for CAPL's psychometric architecture in both healthy-weight and overweight/obese children.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>['Fanli Jia', 'Alexandra Gottardo', 'Poh Wee Koh', 'Xi Chen', 'Adrian Pasquarella']</t>
+          <t>['Christine Delisle Nyström', 'Gregory Traversy', 'Joel D. Barnes', 'Jean‐Philippe Chaput', 'Patricia E. Longmuir', 'Mark S. Tremblay']</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>[['Wilfrid Laurier University', 'https://ror.org/00fn7gb05'], ['Wilfrid Laurier University', 'https://ror.org/00fn7gb05'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['University of Delaware', 'https://ror.org/01sbq1a82']]</t>
+          <t>[["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27']]</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="K50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/rrq.69</t>
+          <t>https://doi.org/10.1186/s12889-018-5898-3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2041761637</t>
+          <t>https://openalex.org/W2895509011</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1186/s12888-014-0379-4</t>
+          <t>https://doi.org/10.1186/s12889-018-5891-x</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Sustained improvements in students’ mental health literacy with use of a mental health curriculum in Canadian schools</t>
+          <t>Physical literacy levels of Canadian children aged 8–12 years: descriptive and normative results from the RBC Learn to Play–CAPL project</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2014</v>
+        <v>2018</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2892,94 +2904,98 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Enhancement of mental health literacy for youth is a focus of increasing interest for mental health professionals and educators alike. Schools are an ideal site for addressing mental health literacy in young people. Currently, there is limited evidence regarding the impact of curriculum-based interventions within high school settings. We examined the effect of a high-school mental health curriculum (The Guide) in enhancing mental health literacy in Canadian schools. We conducted a secondary analysis on surveys of students who participated in a classroom mental health course taught by their usual teachers. Evaluation of students' mental health literacy (knowledge/attitudes) was completed before and after classroom implementation and at 2-month follow-up. We used paired-samples t-tests and Cohen's d value to determine the significance and impact of change. There were 265 students who completed all surveys. Students' knowledge significantly improved between pre- and post-tests (p &lt; 0.001; d = 0.90) and was maintained at follow-up (p &lt; 0.001; d = 0.73). Similarly, attitude significantly improved between pre- and post-tests (p &lt; 0.001; d = 0.25) and was significantly higher at follow-up than base-line (p &lt; 0.007; d = 0.18) The Guide, applied by usual teachers in usual classroom curriculum, may help improve student knowledge and attitudes regarding mental health. This is the first study to demonstrate the positive impact of a curriculum-based mental health literacy program in a Canadian high school population.</t>
+          <t>The current physical literacy level of Canadian children is unknown. The Royal Bank of Canada (RBC) Learn to Play - Canadian Assessment of Physical Literacy (CAPL) project, which is anchored in the Canadian consensus statement definition of physical literacy, aimed to help establish the current physical literacy level of Canadian children.The CAPL was used to assess the physical literacy (and component domains: Daily Behaviour, Physical Competence, Knowledge and Understanding, and Motivation and Confidence) of Canadian children aged 8-12 years. Data were collected from 11 sites across Canada, yielding a sample of 10,034 participants (5030 girls). Descriptive statistics by age and gender were calculated and percentile distributions of physical literacy scores, including each domain and individual measure, were derived.The mean age of participants was 10.1 ± 1.2 years. Total physical literacy scores (out of 100) were on average 63.1 ± 13.0 for boys and 62.2 ± 11.3 for girls. For boys and girls respectively, domain scores were 19.9 ± 4.7 and 19.3 ± 4.1 (out of 32) for Physical Competence; 18.6 ± 7.9 and 18.5 ± 7.4 (out of 32) for Daily Behaviour; 12.7 ± 2.8 and 12.2 ± 2.6 (out of 18) for Motivation and Confidence; and 11.8 ± 2.8 and 12.2 ± 2.6 (out of 18) for Knowledge and Understanding. Physical Competence measures were on average 28.1 ± 8.4 cm (sit-and-reach flexibility), 33.5 ± 9.4 kg (grip strength, right + left), 23.4 ± 14.1 laps (Progressive Aerobic Cardiovascular Endurance Run [PACER] shuttle run), 61.8 ± 43.8 s (isometric plank), 19.0 ± 3.8 kg/m2 (body mass index), 67.3 ± 10.8 cm (waist circumference), and 20.6 ± 3.9 out of 28 points for the Canadian Agility and Movement Skill Assessment (CAMSA), with scores for boys higher than girls and older children higher than younger children for grip strength, PACER, plank, and CAMSA score. Girls and younger children had better scores on the sit-and-reach flexibility than boys and older children. Daily pedometer step counts were higher in boys than girls (12,355 ± 4252 vs. 10,779 ± 3624), and decreased with age.These results provide the largest and most comprehensive assessment of physical literacy of Canadian children to date, providing a "state of the nation" baseline, and can be used to monitor changes and inform intervention strategies going forward.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>['Alan McLuckie', 'Stan Kutcher', 'Yifeng Wei', 'Cynthia Weaver']</t>
+          <t>['Mark S. Tremblay', 'Patricia E. Longmuir', 'Joel D. Barnes', 'Kevin Belanger', 'Kristal D. Anderson', 'Brenda Bruner', 'Jennifer L. Copeland', 'Christine Delisle Nyström', 'Melanie Gregg', 'Nathan Hall', 'Angela M. Kolen', 'Kirstin N. Lane', 'Barbi Law', 'Dany J. MacDonald', 'Luc J. Martin', 'Travis J. Saunders', 'Dwayne P. Sheehan', 'Michelle Stone', 'Sarah J. Woodruff']</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>[['University of Calgary', 'https://ror.org/03yjb2x39'], ['Izaak Walton Killam Health Centre', 'https://ror.org/0064zg438'], ['Dalhousie University', 'https://ror.org/01e6qks80'], ['Dalhousie University', 'https://ror.org/01e6qks80'], ['Izaak Walton Killam Health Centre', 'https://ror.org/0064zg438'], ['Ontario Shores Centre for Mental Health Sciences', 'https://ror.org/04mcqge53']]</t>
+          <t>[["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['Camosun College', 'https://ror.org/02v6aqf52'], ['Nipissing University', 'https://ror.org/05k14ba46'], ['University of Lethbridge', 'https://ror.org/044j76961'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Winnipeg', 'https://ror.org/02gdzyx04'], ['University of Winnipeg', 'https://ror.org/02gdzyx04'], ['St. Francis Xavier University', 'https://ror.org/01wcaxs37'], ['Camosun College', 'https://ror.org/02v6aqf52'], ['Nipissing University', 'https://ror.org/05k14ba46'], ['University of Prince Edward Island', 'https://ror.org/02xh9x144'], ["Queen's University", 'https://ror.org/02y72wh86'], ['University of Prince Edward Island', 'https://ror.org/02xh9x144'], ['Mount Royal University', 'https://ror.org/04evsam41'], ['Dalhousie University', 'https://ror.org/01e6qks80'], ['University of Windsor', 'https://ror.org/01gw3d370']]</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>213</v>
+        <v>91</v>
       </c>
       <c r="K51" t="b">
         <v>1</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1186/s12888-014-0379-4</t>
+          <t>https://doi.org/10.1186/s12889-018-5891-x</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2017521086</t>
+          <t>https://openalex.org/W2966612541</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1007/s13187-014-0744-5</t>
+          <t>https://doi.org/10.3390/nu11081763</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Predictors of High eHealth Literacy in Primary Lung Cancer Survivors</t>
+          <t>Using Food Models to Enhance Sugar Literacy among Older Adolescents: Evaluation of a Brief Experiential Nutrition Education Intervention</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Adolescent diets high in sugar are a public health concern. Sugar literacy interventions have changed intake but focused more on children, adults, and early adolescents and on sugar sweetened beverages rather than total sugar consumption. Food models are an efficacious experiential learning strategy with children. This study assessed the impact of two 45 min nutrition lessons using food models on adolescents’ sugar literacy. Classes (n = 16) were randomized to intervention or control with knowledge, label reading skills, intentions to limit sugar consumption measured at baseline and follow-up. Two hundred and three students aged 14 to 19 from six schools on Vancouver Island, BC, Canada participated in the study. Adolescents’ knowledge of added sugar in foods and beverages and servings per food group in a healthy diet was limited at baseline but improved significantly in the intervention condition (F(1, 201) = 104.84, p &amp;lt; 0.001) compared to controls. Intention to consume less added sugar increased significantly after intervention (F(1, 201) = 4.93, p = 0.03) as did label reading confidence (F(1, 200) = 14.94, p &amp;lt; 0.001). A brief experiential learning intervention using food models was efficacious for changing student’s knowledge about sugar guidelines and sugar in food, label reading confidence, and intention to change sugar consumption.</t>
+        </is>
+      </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>['Robin Milne', 'Martine Puts', 'Janet Papadakos', 'Lisa W. Le', 'Victoria Milne', 'Andrew Hope', 'Pamela Catton', 'Meredith Giuliani']</t>
+          <t>['María Isabel Santaló', 'Sandra L. Gibbons', 'Patti‐Jean Naylor']</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>[['Princess Margaret Cancer Centre', 'https://ror.org/03zayce58'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['Princess Margaret Cancer Centre', 'https://ror.org/03zayce58'], ['Princess Margaret Cancer Centre', 'https://ror.org/03zayce58'], ['Princess Margaret Cancer Centre', 'https://ror.org/03zayce58'], ['Princess Margaret Cancer Centre', 'https://ror.org/03zayce58'], ['Princess Margaret Cancer Centre', 'https://ror.org/03zayce58'], ['Princess Margaret Cancer Centre', 'https://ror.org/03zayce58']]</t>
+          <t>[['University of Victoria', 'https://ror.org/04s5mat29'], ['University of Victoria', 'https://ror.org/04s5mat29'], ['University of Victoria', 'https://ror.org/04s5mat29']]</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>89</v>
+        <v>16</v>
       </c>
       <c r="K52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1007/s13187-014-0744-5</t>
+          <t>https://doi.org/10.3390/nu11081763</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2518045192</t>
+          <t>https://openalex.org/W2474144775</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1093/ckj/sfw076</t>
+          <t>https://doi.org/10.1186/s13104-016-2141-0</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>An observational study of health literacy and medication adherence in adult kidney transplant recipients</t>
+          <t>Health literacy in pregnant women facing prenatal screening may explain their intention to use a patient decision aid: a short report</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -2987,249 +3003,253 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>cc-by-nc</t>
+          <t>cc-by</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>There is a high prevalence of non-adherence to immunosuppressants in kidney transplant recipients. Although limited health literacy is common in kidney recipients and is linked to adverse outcomes in other medical populations, its effect on medication adherence in kidney transplant recipients remains poorly understood. The objective was to investigate the effect of lower health literacy on immunosuppressant adherence. Kidney recipients who were at least 6 months post-transplant and outpatients of Vancouver General Hospital in B.C., Canada were recruited through invitation letters. A total of 96 recipients completed the Health Literacy Questionnaire, which provides a multifactorial profile of self-reported health literacy and the Transplant Effects Questionnaire-Adherence subscale measuring self-reported immunosuppressant adherence. Hierarchical linear regression was used to analyze the association between health literacy and adherence after controlling for identified risk factors of non-adherence. Our sample was on average 53 years old, 56% male and 9 years post-transplant. Kidney recipients reported low levels of health literacy on scales measuring active health management and critical appraisal of information and 75% reported non-perfect adherence. Worse adherence was associated with poorer overall health literacy (ΔR2 = 0.08, P = 0.004) and lower scores on six of nine of the health literacy factors. Poorer health literacy is associated with lower immunosuppressant adherence in adult kidney transplant recipients suggesting the importance of considering a recipient's level of health literacy in research and clinical contexts. Medication adherence interventions can target the six factors of health literacy identified as being risk factors for lower medication adherence.</t>
+          <t>It has been suggested that health literacy may impact the use of decision aids (DAs) among patients facing difficult decisions. Embedded in the pilot test of a questionnaire, this study aimed to measure the association between health literacy and pregnant women's intention to use a DA to decide about prenatal screening. We recruited a convenience sample of 45 pregnant women in three clinical sites (family practice teaching unit, birthing center and obstetrical ambulatory care clinic). We asked participating women to complete a self-administered questionnaire assessing their intention to use a DA to decide about prenatal screening and assessed their health literacy levels using one subjective and two objective scales. Two of the three scales discriminated between levels of health literacy (three numeracy questions and three health literacy questions). We found a positive correlation between pregnant women's intention to use a DA and subjective health literacy (Spearman coefficient, Rho 0.32, P = 0.04) but not objective health literacy (Spearman coefficient, Rho 0.07, P = 0.65). Hence subjective health literacy may affect the intention to use a DA among pregnant women facing a decision about prenatal screening. Special attention should be given to pregnant women with lower health literacy levels to increase their intention to use a DA and ensure that every pregnant women can give informed and value-based consent to prenatal screening.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>['Maryam Demian', 'R. Jean Shapiro', 'Wendy Loken Thornton']</t>
+          <t>['Agathe Delanoë', 'Johanie Lépine', 'Maria Esther Leiva Portocarrero', 'Hubert Robitaille', 'Stéphane Turcotte', 'Isabelle Lévesque', 'Brenda J. Wilson', 'Anik Giguère', 'France Légaré']</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>[['Simon Fraser University', 'https://ror.org/0213rcc28'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['Simon Fraser University', 'https://ror.org/0213rcc28']]</t>
+          <t>[["Hôpital Saint-François d'Assise", 'https://ror.org/02r1pzn16'], ['Centre hospitalier universitaire de Québec', 'https://ror.org/006a7pj43'], ["Hôpital Saint-François d'Assise", 'https://ror.org/02r1pzn16'], ['Centre hospitalier universitaire de Québec', 'https://ror.org/006a7pj43'], ["Hôpital Saint-François d'Assise", 'https://ror.org/02r1pzn16'], ['Centre hospitalier universitaire de Québec', 'https://ror.org/006a7pj43'], ["Hôpital Saint-François d'Assise", 'https://ror.org/02r1pzn16'], ['Centre hospitalier universitaire de Québec', 'https://ror.org/006a7pj43'], ["Hôpital Saint-François d'Assise", 'https://ror.org/02r1pzn16'], ['Centre hospitalier universitaire de Québec', 'https://ror.org/006a7pj43'], ['Université Laval', 'https://ror.org/04sjchr03'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ['Quebec Research and Development Centre', 'https://ror.org/01xgv8v73'], ['Université Laval', 'https://ror.org/04sjchr03']]</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="K53" t="b">
         <v>1</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1093/ckj/sfw076</t>
+          <t>https://doi.org/10.1186/s13104-016-2141-0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2291543154</t>
+          <t>https://openalex.org/W2794438485</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/02701367.2016.1124722</t>
+          <t>https://doi.org/10.17269/s41997-018-0034-9</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Implications of Physical Literacy for Research and Practice: A Commentary</t>
+          <t>Primary care intervention to address cardiovascular disease medication health literacy among Indigenous peoples: Canadian results of a pre-post-design study</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2016</v>
-      </c>
-      <c r="F54" t="inlineStr"/>
+        <v>2018</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>cc-by</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Physical literacy is a term that has increasingly gained popularity in recent years. A variety of individuals and organizations have promoted the use of the term internationally, and a variety of claims have been made for the benefits of using the term. A historical overview allows the reader to consider physical literacy as one of many terms that have gained popularity in the field and describes divergent views as well as areas of agreement concerning the term physical literacy. Three North American institutional approaches to physical literacy are discussed. Other issues are also discussed, including assessment and other literacy types (e.g., health, sports). The article is designed to provoke thought among professionals and representatives of institutions concerning physical literacy.</t>
+          <t>Cardiovascular diseases (CVD) are a leading cause of illness and death for Indigenous people in Canada and globally. Appropriate medication can significantly improve health outcomes for persons diagnosed with CVD or for those at high risk of CVD. Poor health literacy has been identified as a major barrier that interferes with client understanding and taking of CVD medication. Strengthening health literacy within health services is particularly relevant in Indigenous contexts, where there are systemic barriers to accessing literacy skills.The aim of this study is to test the effect of a customized, structured health literacy educational program addressing CVD medications.Pre-post-design involves health providers and Indigenous clients at the De dwa da dehs nye&gt;s Aboriginal Health Centre (DAHC) in Ontario, Canada. Forty-seven Indigenous clients with or at high risk of CVD received three educational sessions delivered by a trained Indigenous nurse over a 4- to 7-week period. A tablet application, pill card and booklet supported the sessions. Primary outcomes were knowledge of CVD medications and health literacy practices, which were assessed before and after the programe.Following the program compared to before, mean medication knowledge scores were 3.3 to 6.1 times higher for the four included CVD medications. Participants were also more likely to refer to the customized pill card and booklet for information and answer questions from others regarding CVD.This customized education program was highly effective in increasing medication knowledge and health literacy practice among Indigenous people with CVD or at risk of CVD attending the program at an urban Indigenous health centre.</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>['Charles B. Corbin']</t>
+          <t>['Janet Smylie', 'Kristen O’Brien', 'Chloé G. Xavier', 'Marcia Anderson', 'Constance McKnight', 'Bernice Downey', 'Margaret Kelaher']</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>[['Arizona State University', 'https://ror.org/03efmqc40']]</t>
+          <t>[["St. Michael's Hospital", 'https://ror.org/04skqfp25'], ["St. Michael's Hospital", 'https://ror.org/04skqfp25'], ["St. Michael's Hospital", 'https://ror.org/04skqfp25'], ['University of Manitoba', 'https://ror.org/02gfys938'], ['Aboriginal Affairs Northern Dev Canada', 'https://ror.org/05pgxdd43'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['The University of Melbourne', 'https://ror.org/01ej9dk98']]</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>144</v>
+        <v>19</v>
       </c>
       <c r="K54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/02701367.2016.1124722</t>
+          <t>https://doi.org/10.17269/s41997-018-0034-9</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2921451314</t>
+          <t>https://openalex.org/W2894753606</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.psychres.2019.03.009</t>
+          <t>https://doi.org/10.1186/s12889-018-5900-0</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Establishment and validation of a mental health literacy measurement in Canadian educators</t>
+          <t>Revising the motivation and confidence domain of the Canadian assessment of physical literacy</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2019</v>
-      </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
+        <v>2018</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>cc-by</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>The Motivation and Confidence domain questionnaire in the Canadian Assessment of Physical Literacy (CAPL) was lengthy (36 single items that aggregate to five subscales), and thus burdensome to both participants and practitioners. The purpose of this study was to use factor analysis to refine the Motivation and Confidence domain to be used in the CAPL-Second Edition (CAPL-2).Children, primarily recruited through free-of-charge summer day camps (n = 205, Mage = 9.50 years, SD = 1.14, 50.7% girls), completed the CAPL-2 protocol, and two survey versions of the Motivation and Confidence questionnaire. Survey 1 contained the Motivation and Confidence questionnaire items from the original CAPL, whereas Survey 2 contained a battery of items informed by self-determination theory to assess motivation and confidence. First, factor analyses were performed on individual questionnaires to examine validity evidence (i.e., internal structure) and score reliability (i.e., coefficient H and omega total). Second, factor analyses were performed on different combinations of questionnaires to establish the least burdensome yet well-fitted and theoretically aligned model.The assessment of adequacy and predilection, based on 16 single items as originally conceptualized within the CAPL, was not a good fit to the data. Therefore, a revised and shorter version of these scales was proposed, based on exploratory factor analysis. The self-determination theory items provided a good fit to the data; however, identified, introjected, and external regulation had low score reliability. Overall, a model comprising three single items for each of the following subscales was proposed for use within the CAPL-2: adequacy, predilection, intrinsic motivation, and perceived competence satisfaction. This revised domain fit well within the overall CAPL-2 model specifying a higher-order physical literacy factor (MLRχ2(63) = 81.45, p = 0.06, CFI = 0.908, RMSEA = 0.038, 90% CI (0.00, 0.060)).The revised and much shorter questionnaire of 12 items that aggregate to four subscales within the domain of Motivation and Confidence is recommended for use in the CAPL-2. The revised domain is aligned with the definition of motivation and confidence within physical literacy and has clearer instructions for completion.</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>['Yifeng Wei', 'Andrew Baxter', 'Stan Kutcher']</t>
+          <t>['Katie E. Gunnell', 'Patricia E. Longmuir', 'Sarah J. Woodruff', 'Joel D. Barnes', 'Kevin Belanger', 'Mark S. Tremblay']</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>[['Izaak Walton Killam Health Centre', 'https://ror.org/0064zg438'], ['Dalhousie University', 'https://ror.org/01e6qks80'], ['Alberta Health Services', 'https://ror.org/02nt5es71'], ['Izaak Walton Killam Health Centre', 'https://ror.org/0064zg438'], ['Dalhousie University', 'https://ror.org/01e6qks80']]</t>
+          <t>[['Carleton University', 'https://ror.org/02qtvee93'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Windsor', 'https://ror.org/01gw3d370'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27']]</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="K55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.psychres.2019.03.009</t>
+          <t>https://doi.org/10.1186/s12889-018-5900-0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2624920485</t>
+          <t>https://openalex.org/W2183435816</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.ijmedinf.2017.06.001</t>
+          <t>https://doi.org/10.1007/s11092-015-9233-6</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Barriers to technology use among older heart failure individuals in managing their symptoms after hospital discharge</t>
+          <t>Teacher assessment literacy: a review of international standards and measures</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>['Linda Nguyen', 'Karim Keshavjee', 'Norm Archer', 'Christopher Patterson', 'Femida Gwadry‐Sridhar', 'Catherine Demers']</t>
+          <t>['Christopher DeLuca', 'Danielle LaPointe-McEwan', 'Ulemu Luhanga']</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>[['McMaster University', 'https://ror.org/02fa3aq29'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['Western University', 'https://ror.org/02grkyz14'], ['McMaster University', 'https://ror.org/02fa3aq29']]</t>
+          <t>[["Queen's University", 'https://ror.org/02y72wh86'], ["Queen's University", 'https://ror.org/02y72wh86'], ["Queen's University", 'https://ror.org/02y72wh86']]</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>19</v>
+        <v>199</v>
       </c>
       <c r="K56" t="b">
         <v>0</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.ijmedinf.2017.06.001</t>
+          <t>https://doi.org/10.1007/s11092-015-9233-6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2755779874</t>
+          <t>https://openalex.org/W2581724875</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.24095/hpcdp.37.9.06</t>
+          <t>https://doi.org/10.1007/s11136-016-1495-z</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>The Ontario Food and Nutrition Strategy: identifying indicators of food access and food literacy for early monitoring of the food environment</t>
+          <t>Health literacy and logical inconsistencies in valuations of hypothetical health states: results from the Canadian EQ-5D-5L valuation study</t>
         </is>
       </c>
       <c r="E57" t="n">
         <v>2017</v>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>cc-by</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>To address challenges Canadians face within their food environments, a comprehensive, multistakeholder, intergovernmental approach to policy development is essential. Food environment indicators are needed to assess population status and change. The Ontario Food and Nutrition Strategy (OFNS) integrates the food, agriculture and nutrition sectors, and aims to improve the health of Ontarians through actions that promote healthy food systems and environments. This report describes the process of identifying indicators for 11 OFNS action areas in two strategic directions (SDs): Healthy Food Access, and Food Literacy and Skills.The OFNS Indicators Advisory Group used a five-step process to select indicators: (1) potential indicators from national and provincial data sources were identified; (2) indicators were organized by SD, action area and data type; (3) selection criteria were identified, pilot tested and finalized; (4) final criteria were applied to refine the indicator list; and (5) indicators were prioritized after reapplication of selection criteria.Sixty-nine potential indicators were initially identified; however, many were individual-level rather than system-level measures. After final application of the selection criteria, one individual-level indicator and six system-level indicators were prioritized in five action areas; for six of the action areas, no indicators were available.Data limitations suggest that available data may not measure important aspects of the food environment, highlighting the need for action and resources to improve system-level indicators and support monitoring of the food environment and health in Ontario and across Canada.Une approche intergouvernementale multilatérale globale en matière d’élaboration de politiques est essentielle pour permettre aux Canadiens et aux Canadiennes de faire face aux défis que pose leur environnement alimentaire. Des indicateurs de l’environnement alimentaire sont nécessaires pour évaluer l’état et l’évolution de la population. La Stratégie sur l’alimentation et la nutrition de l’Ontario (SANO), qui regroupe les secteurs de l’alimentation, de l’agriculture et de la nutrition, vise à améliorer la santé de la population ontarienne par des interventions favorisant des systèmes et des environnements alimentaires sains. Cet article décrit le processus d’établissement d'indicateurs pour 11 secteurs d’intervention de la SANO dans deux orientations stratégiques : l’accès à des aliments sains et l’alphabétisme et les compétences alimentaires.Le groupe consultatif sur les indicateurs de la SANO a suivi un processus en cinq étapes pour choisir les indicateurs : 1) choix des indicateurs potentiels dans les sources de données provinciales et nationales, 2) catégorisation des indicateurs par orientation stratégique, par secteur d’intervention et par type de données, 3) établissement, essai pilote et finalisation des critères de sélection, 4) application des critères finaux pour améliorer la liste des indicateurs et 5) établissement des indicateurs prioritaires après cette application finale des critères de sélection.Soixante-neuf indicateurs potentiels ont été recensés au départ, mais un grand nombre d’entre eux offraient des mesures individuelles et non collectives. Après l’application finale des critères de sélection, ont été jugés prioritaires un indicateur individuel et six indicateurs collectifs associés à cinq secteurs d’intervention, aucun indicateur n’étant disponible pour les six autres secteurs d’intervention.Les limites des données existantes laissent penser qu’on ne peut sans doute pas qualifier certaines caractéristiques importantes de l’environnement alimentaire, d’où l’importance de prendre des mesures et d’allouer des ressources pour améliorer les indicateurs collectifs et d’appuyer le suivi de l’environnement alimentaire et de la santé alimentaire tant en Ontario que dans le reste du Canada.</t>
-        </is>
-      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>['Beatrice A. Boucher', 'Elizabeth Manafò', 'Meaghan R. Boddy', 'Lynn Roblin', 'Rebecca Truscott']</t>
+          <t>['Fatima Al Sayah', 'Jeffrey Johnson', 'Arto Öhinmaa', 'Feng Xie', 'Nick Bansback']</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>[['Cancer Care Ontario', 'https://ror.org/029n6xw55'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['Toronto Metropolitan University', 'https://ror.org/05g13zd79'], ['Cancer Care Ontario', 'https://ror.org/029n6xw55'], ['Cancer Care Ontario', 'https://ror.org/029n6xw55']]</t>
+          <t>[['University of Alberta', 'https://ror.org/0160cpw27'], ['University of Alberta', 'https://ror.org/0160cpw27'], ['University of Alberta', 'https://ror.org/0160cpw27'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['St. Joseph’s Healthcare Hamilton', 'https://ror.org/009z39p97'], ['University of British Columbia', 'https://ror.org/03rmrcq20']]</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="K57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>https://doi.org/10.24095/hpcdp.37.9.06</t>
+          <t>https://doi.org/10.1007/s11136-016-1495-z</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2801027355</t>
+          <t>https://openalex.org/W2895198122</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3389/fped.2018.00138</t>
+          <t>https://doi.org/10.1186/s12889-018-5901-z</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>The Preschool Physical Literacy Assessment Tool: Testing a New Physical Literacy Tool for the Early Years</t>
+          <t>An exploratory analysis of missing data from the Royal Bank of Canada (RBC) Learn to Play – Canadian Assessment of Physical Literacy (CAPL) project</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -3242,198 +3262,198 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Background: Physical literacy is essential to physical activity across the lifespan. While there is an emerging body of research on physical literacy in school-aged children, the preschool years have largely been ignored. We tested the psychometric properties of new tool, the Preschool Physical Literacy Assessment Tool (Pre-PLAY) designed to address this gap. Methods: We recruted 78 children (aged 19 to 49 months) across 5 childcare centers in Hamilton, Ontario. Two Early Childhood Educators (ECE) completed the Pre-PLAY for each child at two points in time to assess inter-rater reliability and test-retest reliability. We assessed the agreement between the Pre-PLAY tool with gross motor skills and the ability of the PPLAy to predict physical activity. Results: Results indicated Pre-PLAY is related to gross motor skills and predictive of physical activity for females, but not males. Inter-rater and intra-rater reliability was at least adequate for all but the co-orindated movements items and scale for females, but ECEs showed poor agreement for males. Conclusions: These results suggest initial support for the Pre-PLAY tool as a measure of physical literacy during the early years. However, some modification to the items and training are required to address the gender-specific effects found in this sample.</t>
+          <t>Physical literacy comprises a range of tests over four domains (Physical Competence, Daily Behaviour, Motivation and Confidence, and Knowledge and Understanding). The patterns of missing data in large field test batteries such as those for physical literacy are largely unknown. Therefore, the aim of this paper was to explore the patterns and possible reasons for missing data in the Royal Bank of Canada Learn to Play-Canadian Assessment of Physical Literacy (RBC Learn to Play-CAPL) project.A total of 10,034 Canadian children aged 8 to 12 years participated in the RBC Learn to Play-CAPL project. A 32-variable subset from the larger CAPL dataset was used for these analyses. Several R packages ("Hmisc", "mice", "VIM") were used to generate matrices and plots of missing data, and to perform multiple imputations.Overall, the proportion of missing data for individual measures and domains ranged from 0.0 to 33.8%, with the average proportion of missing data being 4.0%. The largest proportion of missing data in CAPL was the pedometer step counts, followed by the components of the Physical Competence domain and the Children's Self-Perception of Adequacy in and Predilection for Physical Activity subscales. When domain scores were regressed on five imputed subsets with the original subset as the reference, there were small and statistically detectable differences in the Daily Behaviour score (β = - 1.6 to - 1.7, p &lt; 0.001). However, for the other domain scores the differences were negligible and statistically undetectable (β = - 0.01 to - 0.06, p &gt; 0.05).This study has implications for other researchers or educators who are creating or using large field-based assessment measures in the areas of physical literacy, physical activity, or physical fitness, as this study demonstrates where problems in data collection can arise and how missing data can be avoided. When large proportions of missing data are present, imputation techniques, correction factors, or other treatment options may be required.</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>['John Cairney', 'Heather J. Clark', 'Maeghan E. James', 'Drew Mitchell', 'Dean Dudley', 'Dean Kriellaars']</t>
+          <t>['Christine Delisle Nyström', 'Joel D. Barnes', 'Mark S. Tremblay']</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>[['University of Toronto', 'https://ror.org/03dbr7087'], ['Friends For Life', 'https://ror.org/042n1mt30'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['Friends For Life', 'https://ror.org/042n1mt30'], ['Macquarie University', 'https://ror.org/01sf06y89'], ['Friends For Life', 'https://ror.org/042n1mt30'], ['Friends For Life', 'https://ror.org/042n1mt30'], ['University of Manitoba', 'https://ror.org/02gfys938']]</t>
+          <t>[["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27']]</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="K58" t="b">
         <v>1</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3389/fped.2018.00138</t>
+          <t>https://doi.org/10.1186/s12889-018-5901-z</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2768220913</t>
+          <t>https://openalex.org/W2898919684</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1249/mss.0000000000001494</t>
+          <t>https://doi.org/10.1123/jtpe.2018-0028</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>A Construct Validation Study of PLAYfun</t>
+          <t>Examining the Impact of a Teaching Games for Understanding Approach on the Development of Physical Literacy Using the Passport for Life Assessment Tool</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Physical Literacy Assessment for Youth (PLAYfun) is a measure of motor competence, comprehension, and confidence which is part of a suite of scales used to assess physical literacy in children and youth; however, its measurement properties have not been reported in the published literature. The purpose of this study is to examine the factor structure of PLAYfun, in addition to variations in PLAYfun subscale results by age and sex.In this study, we use a sample of children and youth 7 to 14 yr of age (n = 215) to test a proposed factor structure for the motor competence component of PLAYfun and to examine age and sex differences in subscale and total scores. The initial (n = 128) and secondary (n = 98) samples were drawn from a stratified (by geographic region), random sample of 27 after-school programs from a larger pool of 400 programs across the province of Ontario. Seven research assistants were initially trained on the administration of PLAYfun and rated a small pilot sample of 10 children. These trained assessors then assessed the full sample.Interrater agreement was very good (intraclass correlation, 0.87). The hypothesized five-factor structure of the scale was found to have an acceptable fit to the data (root mean square error of approximation, 0.055; 90% confidence interval, 0.03-0.075; comparative fit index, 0.95; Tucker-Lewis Index, 0.94). In general, PLAYfun scores increased with age as developmentally expected. There were few sex differences across skills, but girls did not perform as well as boys on upper and lower body object control skills.The factor structure and patterns of results by age and sex support PLAYfun as a measure of motor competence. Continued evaluation of the tool and other subscales of PLAY is required.</t>
+          <t>Purpose: The purpose of this study was to investigate the impact of an 8-week after-school intramural program that adopted a Teaching Games for Understanding (TGfU) approach to facilitate the development of elementary-school-aged children physical literacy. Methods: Using Physical and Health Education Canada's Passport for Life tool, 22 participants took part in a battery of assessments consistent with characteristics of physical literacy. These measures were (a) active participation, (b) living skills, (c) fitness skills, and (d) movement skills. Each category of assessment included three submeasures for a total of 12 indicators of physical literacy. Participants were assessed at the beginning of the PlaySport Intramural Program and then 8 weeks later following participation in a series of after-school TGfU lessons designed using the PlaySport program. Results: Of the 12 indicators of physical literacy, the majority of participants reported higher scores at the end program for 10 of the indicators. Significant (p &lt; .004) improvements were seen in balance and stability skills, cardiovascular endurance, participation in diverse environments, and interest in participating in diverse activities. No improvements were seen in kicking skills and interacting with others. Discussion/Conclusion: These results provide support for the hypothesis that the use of pedagogical approaches such as TGfU can be effective at facilitating certain components of children's development of physical literacy.</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>['John Cairney', 'Scott Veldhuizen', 'Jeffrey D. Graham', 'Christine Rodriguez', 'Chloe Bedard', 'Emily Bremer', 'Dean Kriellaars']</t>
+          <t>['James Mandigo', 'Ken R. Lodewyk', 'Jay Tredway']</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>[['McMaster University', 'https://ror.org/02fa3aq29'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['Impact', 'https://ror.org/05d9dsr70'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['University of Manitoba', 'https://ror.org/02gfys938']]</t>
+          <t>[['Brock University', 'https://ror.org/056am2717'], ['Brock University', 'https://ror.org/056am2717'], ['Ridley College', 'https://ror.org/02gdmq314']]</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="K59" t="b">
         <v>0</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1249/mss.0000000000001494</t>
+          <t>https://doi.org/10.1123/jtpe.2018-0028</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2768220913</t>
+          <t>https://openalex.org/W2793868721</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1249/mss.0000000000001494</t>
+          <t>https://doi.org/10.1186/s12889-018-5892-9</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>A Construct Validation Study of PLAYfun</t>
+          <t>The relationship between sedentary behaviour and physical literacy in Canadian children: a cross-sectional analysis from the RBC-CAPL Learn to Play study</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2017</v>
-      </c>
-      <c r="F60" t="inlineStr"/>
+        <v>2018</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>cc-by</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Physical Literacy Assessment for Youth (PLAYfun) is a measure of motor competence, comprehension, and confidence which is part of a suite of scales used to assess physical literacy in children and youth; however, its measurement properties have not been reported in the published literature. The purpose of this study is to examine the factor structure of PLAYfun, in addition to variations in PLAYfun subscale results by age and sex.In this study, we use a sample of children and youth 7 to 14 yr of age (n = 215) to test a proposed factor structure for the motor competence component of PLAYfun and to examine age and sex differences in subscale and total scores. The initial (n = 128) and secondary (n = 98) samples were drawn from a stratified (by geographic region), random sample of 27 after-school programs from a larger pool of 400 programs across the province of Ontario. Seven research assistants were initially trained on the administration of PLAYfun and rated a small pilot sample of 10 children. These trained assessors then assessed the full sample.Interrater agreement was very good (intraclass correlation, 0.87). The hypothesized five-factor structure of the scale was found to have an acceptable fit to the data (root mean square error of approximation, 0.055; 90% confidence interval, 0.03-0.075; comparative fit index, 0.95; Tucker-Lewis Index, 0.94). In general, PLAYfun scores increased with age as developmentally expected. There were few sex differences across skills, but girls did not perform as well as boys on upper and lower body object control skills.The factor structure and patterns of results by age and sex support PLAYfun as a measure of motor competence. Continued evaluation of the tool and other subscales of PLAY is required.</t>
+          <t>Physical literacy is the foundation of a physically active lifestyle. Sedentary behaviour displays deleterious associations with important health indicators in children. However, the association between sedentary behaviour and physical literacy is unknown. The purpose of this study was to identify the aspects of physical literacy that are associated with key modes of sedentary behaviour among Canadian children participating in the RBC-CAPL Learn to Play study.A total of 8,307 children aged 8.0-12.9 years were included in the present analysis. Physical literacy was assessed using the Canadian Assessment of Physical Literacy, which measures four domains (Physical Competence, Daily Behaviour, Motivation and Confidence, Knowledge and Understanding). Screen-based sedentary behaviours (TV viewing, computer and video game use), non-screen sedentary behaviours (reading, doing homework, sitting and talking to friends, drawing, etc.) and total sedentary behaviour were assessed via self-report questionnaire. Linear regression models were used to determine significant (p&lt;0.05) correlates of each mode of sedentary behaviour.In comparison to girls, boys reported more screen time (2.7±2.0 vs 2.2±1.8 hours/day, Cohen's d=0.29), and total sedentary behaviour (4.3±2.6 vs 3.9±2.4 hours/day, Cohen's d=0.19), but lower non-screen-based sedentary behaviour (1.6±1.3 vs 1.7±1.3 hours/day, Cohen's d=0.08) (all p&lt; 0.05). Physical Competence (standardized β's: -0.100 to -0.036, all p&lt;0.05) and Motivation and Confidence (standardized β's: -0.274 to -0.083, all p&lt;0.05) were negatively associated with all modes of sedentary behaviour in fully adjusted models. Knowledge and Understanding was negatively associated with screen-based modes of sedentary behaviour (standardized β's: -0.039 to -0.032, all p&lt;0.05), and positively associated with non-screen sedentary behaviour (standardized β: 0.098, p&lt;0.05). Progressive Aerobic Cardiovascular Endurance Run score and log-transformed plank score were negatively associated with all screen-based modes of sedentary behaviour, while the Canadian Agility and Movement Skill Assessment score was negatively associated with all modes of sedentary behaviour other than TV viewing (all p&lt;0.05).These results highlight differences in the ways that screen and non-screen sedentary behaviours relate to physical literacy. Public health interventions should continue to target screen-based sedentary behaviours, given their potentially harmful associations with important aspects of physical literacy.</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>['John Cairney', 'Scott Veldhuizen', 'Jeffrey D. Graham', 'Christine Rodriguez', 'Chloe Bedard', 'Emily Bremer', 'Dean Kriellaars']</t>
+          <t>['Travis J. Saunders', 'Dany J. MacDonald', 'Jennifer L. Copeland', 'Patricia E. Longmuir', 'Joel D. Barnes', 'Kevin Belanger', 'Brenda Bruner', 'Melanie Gregg', 'Nathan Hall', 'Angela M. Kolen', 'Barbi Law', 'Luc J. Martin', 'Dwayne P. Sheehan', 'Michelle Stone', 'Sarah J. Woodruff', 'Mark S. Tremblay']</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>[['McMaster University', 'https://ror.org/02fa3aq29'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['Impact', 'https://ror.org/05d9dsr70'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['University of Manitoba', 'https://ror.org/02gfys938']]</t>
+          <t>[['University of Prince Edward Island', 'https://ror.org/02xh9x144'], ['University of Prince Edward Island', 'https://ror.org/02xh9x144'], ['University of Lethbridge', 'https://ror.org/044j76961'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['Nipissing University', 'https://ror.org/05k14ba46'], ['University of Winnipeg', 'https://ror.org/02gdzyx04'], ['University of Winnipeg', 'https://ror.org/02gdzyx04'], ['St. Francis Xavier University', 'https://ror.org/01wcaxs37'], ['Nipissing University', 'https://ror.org/05k14ba46'], ["Queen's University", 'https://ror.org/02y72wh86'], ['Mount Royal University', 'https://ror.org/04evsam41'], ['Dalhousie University', 'https://ror.org/01e6qks80'], ['University of Windsor', 'https://ror.org/01gw3d370'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27']]</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="K60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1249/mss.0000000000001494</t>
+          <t>https://doi.org/10.1186/s12889-018-5892-9</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2768220913</t>
+          <t>https://openalex.org/W2012525493</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1249/mss.0000000000001494</t>
+          <t>https://doi.org/10.1016/j.jmathb.2015.01.004</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>A Construct Validation Study of PLAYfun</t>
+          <t>The assessment of mathematical literacy of linguistic minority students: Results of a multi-method investigation</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Physical Literacy Assessment for Youth (PLAYfun) is a measure of motor competence, comprehension, and confidence which is part of a suite of scales used to assess physical literacy in children and youth; however, its measurement properties have not been reported in the published literature. The purpose of this study is to examine the factor structure of PLAYfun, in addition to variations in PLAYfun subscale results by age and sex.In this study, we use a sample of children and youth 7 to 14 yr of age (n = 215) to test a proposed factor structure for the motor competence component of PLAYfun and to examine age and sex differences in subscale and total scores. The initial (n = 128) and secondary (n = 98) samples were drawn from a stratified (by geographic region), random sample of 27 after-school programs from a larger pool of 400 programs across the province of Ontario. Seven research assistants were initially trained on the administration of PLAYfun and rated a small pilot sample of 10 children. These trained assessors then assessed the full sample.Interrater agreement was very good (intraclass correlation, 0.87). The hypothesized five-factor structure of the scale was found to have an acceptable fit to the data (root mean square error of approximation, 0.055; 90% confidence interval, 0.03-0.075; comparative fit index, 0.95; Tucker-Lewis Index, 0.94). In general, PLAYfun scores increased with age as developmentally expected. There were few sex differences across skills, but girls did not perform as well as boys on upper and lower body object control skills.The factor structure and patterns of results by age and sex support PLAYfun as a measure of motor competence. Continued evaluation of the tool and other subscales of PLAY is required.</t>
-        </is>
-      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>['John Cairney', 'Scott Veldhuizen', 'Jeffrey D. Graham', 'Christine Rodriguez', 'Chloe Bedard', 'Emily Bremer', 'Dean Kriellaars']</t>
+          <t>['Wolff‐Michael Roth', 'Kadriye Ercikan', 'Marielle Simon', 'Romeo Fola']</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>[['McMaster University', 'https://ror.org/02fa3aq29'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['Impact', 'https://ror.org/05d9dsr70'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['University of Manitoba', 'https://ror.org/02gfys938']]</t>
+          <t>[['University of Victoria', 'https://ror.org/04s5mat29'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ['University of Ottawa', 'https://ror.org/03c4mmv16']]</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="K61" t="b">
         <v>0</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1249/mss.0000000000001494</t>
+          <t>https://doi.org/10.1016/j.jmathb.2015.01.004</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2768220913</t>
+          <t>https://openalex.org/W2588450759</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1249/mss.0000000000001494</t>
+          <t>https://doi.org/10.1542/peds.2016-1961</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>A Construct Validation Study of PLAYfun</t>
+          <t>Parental Health Literacy and Outcomes of Childhood Nephrotic Syndrome</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -3442,156 +3462,148 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Physical Literacy Assessment for Youth (PLAYfun) is a measure of motor competence, comprehension, and confidence which is part of a suite of scales used to assess physical literacy in children and youth; however, its measurement properties have not been reported in the published literature. The purpose of this study is to examine the factor structure of PLAYfun, in addition to variations in PLAYfun subscale results by age and sex.In this study, we use a sample of children and youth 7 to 14 yr of age (n = 215) to test a proposed factor structure for the motor competence component of PLAYfun and to examine age and sex differences in subscale and total scores. The initial (n = 128) and secondary (n = 98) samples were drawn from a stratified (by geographic region), random sample of 27 after-school programs from a larger pool of 400 programs across the province of Ontario. Seven research assistants were initially trained on the administration of PLAYfun and rated a small pilot sample of 10 children. These trained assessors then assessed the full sample.Interrater agreement was very good (intraclass correlation, 0.87). The hypothesized five-factor structure of the scale was found to have an acceptable fit to the data (root mean square error of approximation, 0.055; 90% confidence interval, 0.03-0.075; comparative fit index, 0.95; Tucker-Lewis Index, 0.94). In general, PLAYfun scores increased with age as developmentally expected. There were few sex differences across skills, but girls did not perform as well as boys on upper and lower body object control skills.The factor structure and patterns of results by age and sex support PLAYfun as a measure of motor competence. Continued evaluation of the tool and other subscales of PLAY is required.</t>
+          <t>Determine the association of parental health literacy with treatment response among children with nephrotic syndrome.This was a cohort study of children aged 1-18 with nephrotic syndrome and their parent. Health literacy was measured using the validated Short Test of Functional Health Literacy in Adults assessing reading comprehension and numeracy. Outcomes included initial relapse-free period, frequently relapsing disease, relapse rate, second-line medication use, and complete remission after therapy.Of 190 parents, 80% had adequate health literacy (score &gt;67 of 100), and higher scores were not correlated with higher education. Almost all achieved perfect numeracy scores (&gt;86%); numeracy was not associated with outcomes. After adjusting for immigration, education, and income, higher reading comprehension scores (tertile 3) compared with lower scores (tertile 1) were significantly associated with lower risk of first relapse (hazard ratio 0.67, 95% confidence interval [CI] 0.48-0.94, P trend = .02), lower odds of frequently relapsing disease (odds ratio [OR] 0.38, 95% CI 0.21-0.70, P trend = .002), lower relapse rate (rate ratio 0.77, 95% CI 0.73-0.80, P trend &lt; .001), and higher odds of complete remission after both initial steroids and cyclophosphamide (OR 2.07, 95% CI 1.36-3.16, P trend = .003; OR 5.97, 95% CI 2.42-14.7, P trend &lt; .001).Lower parental health literacy, specifically reading comprehension, is associated with higher relapse rates among children with nephrotic syndrome and fewer achieving complete remission. This underscores the importance of assessing and targeting health literacy for chronic management of childhood-onset diseases.</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>['John Cairney', 'Scott Veldhuizen', 'Jeffrey D. Graham', 'Christine Rodriguez', 'Chloe Bedard', 'Emily Bremer', 'Dean Kriellaars']</t>
+          <t>['Karlota Borges', 'Cathryn Sibbald', 'Neesha Hussain‐Shamsy', 'Jovanka Vasilevska‐Ristovska', 'Tonny Banh', 'Viral Patel', 'Josefina Brooke', 'Monica Piekut', 'Michele Reddon', 'Kimberly Aitken-Menezes', 'Ashley McNaughton', 'Rachel Pearl', 'Valérie S. Langlois', 'Seetha Radhakrishnan', 'Christoph Licht', 'Tino D. Piscione', 'Leo Levin', 'Damien Noone', 'Diane Hébert', 'Rulan S. Parekh']</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>[['McMaster University', 'https://ror.org/02fa3aq29'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['Impact', 'https://ror.org/05d9dsr70'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['University of Manitoba', 'https://ror.org/02gfys938']]</t>
+          <t>[['Institute for Clinical Evaluative Sciences', 'https://ror.org/05p6rhy72'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['Institute for Clinical Evaluative Sciences', 'https://ror.org/05p6rhy72'], ['Institute for Clinical Evaluative Sciences', 'https://ror.org/05p6rhy72'], ['Institute for Clinical Evaluative Sciences', 'https://ror.org/05p6rhy72'], ['Institute for Clinical Evaluative Sciences', 'https://ror.org/05p6rhy72'], ['Pediatric Nephrology of Alabama', 'https://ror.org/00zsny525'], ['Pediatric Nephrology of Alabama', 'https://ror.org/00zsny525'], ['Pediatric Nephrology of Alabama', 'https://ror.org/00zsny525'], ['Pediatric Nephrology of Alabama', 'https://ror.org/00zsny525'], ['Pediatric Nephrology of Alabama', 'https://ror.org/00zsny525'], ['Institute for Clinical Evaluative Sciences', 'https://ror.org/05p6rhy72'], ['Pediatric Nephrology of Alabama', 'https://ror.org/00zsny525'], ['Brampton Civic Hospital', 'https://ror.org/01q9kjc87'], ['William Osler Health System', 'https://ror.org/03d1xjg58'], ['Pediatric Nephrology of Alabama', 'https://ror.org/00zsny525'], ['Institute for Clinical Evaluative Sciences', 'https://ror.org/05p6rhy72'], ['Pediatric Nephrology of Alabama', 'https://ror.org/00zsny525'], ['Hospital for Sick Children', 'https://ror.org/057q4rt57'], ['Institute for Clinical Evaluative Sciences', 'https://ror.org/05p6rhy72'], ['Pediatric Nephrology of Alabama', 'https://ror.org/00zsny525'], ['Institute for Clinical Evaluative Sciences', 'https://ror.org/05p6rhy72'], ['Pediatric Nephrology of Alabama', 'https://ror.org/00zsny525'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['Institute for Clinical Evaluative Sciences', 'https://ror.org/05p6rhy72'], ['Pediatric Nephrology of Alabama', 'https://ror.org/00zsny525'], ['Institute for Clinical Evaluative Sciences', 'https://ror.org/05p6rhy72'], ['Pediatric Nephrology of Alabama', 'https://ror.org/00zsny525'], ['Institute for Clinical Evaluative Sciences', 'https://ror.org/05p6rhy72'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['Pediatric Nephrology of Alabama', 'https://ror.org/00zsny525'], ['University Health Network', 'https://ror.org/042xt5161'], ['Public Health Ontario', 'https://ror.org/025z8ah66']]</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="K62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1249/mss.0000000000001494</t>
+          <t>https://doi.org/10.1542/peds.2016-1961</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2894925006</t>
+          <t>https://openalex.org/W2890722669</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1186/s12889-018-5902-y</t>
+          <t>https://doi.org/10.7870/cjcmh-2018-002</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Canadian Assessment of Physical Literacy Second Edition: a streamlined assessment of the capacity for physical activity among children 8 to 12 years of age</t>
+          <t>Improving Mental Health Literacy in Post-Secondary Students: Field Testing the Feasibility and Potential Outcomes of a Peer-Led Approach</t>
         </is>
       </c>
       <c r="E63" t="n">
         <v>2018</v>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>cc-by</t>
-        </is>
-      </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>The Canadian Assessment of Physical Literacy (CAPL) assesses the capacity of children to lead a physically active lifestyle. It is comprised of a battery of standardized assessment protocols that reflect the Canadian consensus definition of physical literacy. The Royal Bank of Canada Learn to Play - Canadian Assessment of Physical Literacy study implemented the CAPL with 10,034 Canadian children (50.1% female), 8 to 12 years of age. Feedback during data collection, necessary changes identified by the coordinating centre, and recent data analyses suggested that a streamlined, second edition of the CAPL was required. The purpose of this paper is to describe the methods used to develop the CAPL second edition (CAPL-2).The larger dataset created through the RBC-Learn to Play CAPL study enabled the re-examination of the CAPL model through factor analyses specific to Canadian children 8 to 12 years of age from across Canada. This comprehensive database was also used to examine the CAPL protocols for redundancy or variables that did not contribute significantly to the overall assessment. Removing redundancy had been identified as a priority in order to reduce the high examiner and participant burden. The "lessons learned" from such a large national surveillance project were reviewed for additional information regarding the changes that would be required to optimize the assessment of children's physical literacy. In addition, administrative changes, improvements, and corrections were identified as necessary to improve the quality and accuracy of the CAPL manual and training materials.For each domain of the CAPL, recommended changes based on the factor analyses, qualitative feedback and theoretical considerations significantly reduced the number of protocols. Specific protocol combinations were then evaluated for model fit within the overarching concept of physical literacy. The CAPL-2 continues to reflect the four components of the Canadian consensus definition of physical literacy: Motivation and Confidence, Physical Competence, Knowledge and Understanding, and engagement in Physical Activity Behaviour. The CAPL-2 is comprised of three Physical Competence protocols (plank, Progressive Aerobic Cardiovascular Endurance Run [PACER], Canadian Agility and Movement Skill Assessment [CAMSA]), two Daily Behaviour protocol (pedometer steps, self-reported physical activity), and a 22-item questionnaire assessing the physical literacy domains of Motivation and Confidence, and Knowledge and Understanding. Detailed information about the CAPL-2 is available online ( www.capl-eclp.ca ).The CAPL-2 dramatically reduces examiner and participant burden (three Physical Competence protocols, two Daily Behaviour protocols, and a 22-response questionnaire; versus eight Physical Competence protocols, three Daily Behaviour protocols and a 72-response questionnaire for the original CAPL), while continuing to be a comprehensive assessment of all aspects of children's physical literacy using the Canadian consensus definition of this term. Like the original, the CAPL-2 continues to offer maximum flexibility to practitioners, who can choose to complete the entire CAPL-2 assessment, only one or more domains, or select individual protocols. Regardless of the assessment selected, scores are available to interpret the performance of each child relative to Canadian children of the same age and sex. All of the protocols included in the CAPL-2 have published reports of validity and reliability for this age group (8 to 12 years). The detailed manual for CAPL-2 administration, along with training materials and other resources, are available free of charge on the CAPL-2 website ( www.capl-eclp.ca ). All CAPL-2 materials and resources, including the website, are available in both English and French.</t>
+          <t>Transitions (2nd edition) is an evidence-based life-skills resource designed to help post-secondary students transition from high school to college or university. This study was an on-campus evaluation of peer-led seminars of the mental health content from Transitions. A cross-sectional survey was conducted to assess the mental health literacy of three groups of students: master trainers, student trainers, and seminar participants. Post-seminar, there were significant improvements in mental health knowledge and help-seeking, two key components of participants’ mental health literacy. This peer-led approach is a feasible option with the potential to improve student mental health literacy within a short time frame.</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>['Patricia E. Longmuir', 'Katie E. Gunnell', 'Joel D. Barnes', 'Kevin Belanger', 'Geneviève Leduc', 'Sarah J. Woodruff', 'Mark S. Tremblay']</t>
+          <t>['Chris Gilham', 'Erin L. Austen', 'Yifeng Wei', 'Stan Kutcher']</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>[["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['Carleton University', 'https://ror.org/02qtvee93'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Windsor', 'https://ror.org/01gw3d370'], ['University of Ottawa', 'https://ror.org/03c4mmv16']]</t>
+          <t>[['St. Francis Xavier University', 'https://ror.org/01wcaxs37'], ['Dalhousie University', 'https://ror.org/01e6qks80'], ['Izaak Walton Killam Health Centre', 'https://ror.org/0064zg438'], ['Bridge University', 'https://ror.org/00cbm0437'], ['Bridge University', 'https://ror.org/00cbm0437'], ['Dalhousie University', 'https://ror.org/01e6qks80'], ['St. Francis Xavier University', 'https://ror.org/01wcaxs37'], ['Izaak Walton Killam Health Centre', 'https://ror.org/0064zg438'], ['St. Francis Xavier University', 'https://ror.org/01wcaxs37'], ['Dalhousie University', 'https://ror.org/01e6qks80'], ['Bridge University', 'https://ror.org/00cbm0437'], ['Izaak Walton Killam Health Centre', 'https://ror.org/0064zg438'], ['Dalhousie University', 'https://ror.org/01e6qks80'], ['Bridge University', 'https://ror.org/00cbm0437'], ['St. Francis Xavier University', 'https://ror.org/01wcaxs37'], ['Izaak Walton Killam Health Centre', 'https://ror.org/0064zg438']]</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>113</v>
+        <v>14</v>
       </c>
       <c r="K63" t="b">
         <v>1</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1186/s12889-018-5902-y</t>
+          <t>https://doi.org/10.7870/cjcmh-2018-002</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2894914095</t>
+          <t>https://openalex.org/W2737442553</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1186/s12889-018-5898-3</t>
+          <t>https://doi.org/10.3138/cmlr.3665</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Associations between domains of physical literacy by weight status in 8- to 12-year-old Canadian children</t>
+          <t>Literacy Outcomes of a Chinese/English Bilingual Program in Ontario</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2018</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>cc-by</t>
-        </is>
-      </c>
+        <v>2017</v>
+      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>The Canadian Assessment of Physical Literacy (CAPL) is divided into four domains (Physical Competence, Daily Behaviour, Motivation and Confidence, and Knowledge and Understanding) and provides a robust and comprehensive assessment of physical literacy. As weight status is known to influence health-related behaviours such as physical fitness and activity, it is important to investigate whether the associations between the domains of physical literacy vary among children of different weight status. The aim of this study was to determine the associations among the four domains of physical literacy stratified by weight status.Canadian children aged 8 to 12 years (n = 8343, 63.6% healthy-weight) completed the CAPL. Differences in domain scores and overall physical literacy score by weight status (children of healthy weight versus children with overweight/obese) were assessed using MANOVA (multivariate analysis of variance). Partial correlations between the four domains were calculated, adjusting for gender and age, and correlation coefficients of both weight status groups were compared using the Steiger test.For all four domains as well as overall physical literacy, healthy-weight children had higher scores than their overweight/obese peers (Cohen's d ranged from 0.05 to 0.44). Weak to moderate correlations were found between all of the domains for both groups. Correlation coefficients for Physical Competence and Daily Behaviour as well as for Physical Competence and Knowledge and Understanding were generally stronger in the healthy-weight children (r = 0.29 and 0.22, respectively) compared with the overweight/obese children (r = 0.23 and 0.17, respectively).All of the domains of the CAPL correlate positively with each other regardless of weight status, with a trend for these correlation coefficients to be slightly stronger in the healthy-weight children. The overall weak to moderate correlations between the domains in both groups suggest that the CAPL domains are not measuring the same constructs, thus providing support for CAPL's psychometric architecture in both healthy-weight and overweight/obese children.</t>
+          <t>This study examined the performance of Mandarin-speaking students in a K–Grade 4 50/50 Chinese/English bilingual program. The program was intended to facilitate students’ learning of English and their adjustment to English-medium instruction within the school context. The bilingual-program students were compared to students from Mandarin-speaking backgrounds whose school instruction was conducted totally in English but who attended a weekly 2.5-hour Chinese language class conducted outside of the regular school day through the International Languages Program funded by the Ontario government. Students’ abilities in phonological awareness, vocabulary knowledge, morphological awareness, and word reading were measured. Results showed that students in the bilingual program who received less English instruction overall performed comparably in all English measures to their peers in the English-only programs. Some differences in favour of the bilingual-program students were observed in Chinese language and literacy measures, specifically in character recognition. Students in the bilingual program performed above grade norms on standardized measures of English literacy skills and in the Grade 3 provincial standardized testing of English reading and writing abilities.</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>['Christine Delisle Nyström', 'Gregory Traversy', 'Joel D. Barnes', 'Jean‐Philippe Chaput', 'Patricia E. Longmuir', 'Mark S. Tremblay']</t>
+          <t>['Poh Wee Koh', 'Xi Chen', 'James Cummins', 'Jia Li']</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>[["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27']]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="K64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1186/s12889-018-5898-3</t>
+          <t>https://doi.org/10.3138/cmlr.3665</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2895509011</t>
+          <t>https://openalex.org/W2895270365</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1186/s12889-018-5891-x</t>
+          <t>https://doi.org/10.1186/s12889-018-5896-5</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Physical literacy levels of Canadian children aged 8–12 years: descriptive and normative results from the RBC Learn to Play–CAPL project</t>
+          <t>Cardiorespiratory fitness is associated with physical literacy in a large sample of Canadian children aged 8 to 12 years</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -3604,152 +3616,144 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>The current physical literacy level of Canadian children is unknown. The Royal Bank of Canada (RBC) Learn to Play - Canadian Assessment of Physical Literacy (CAPL) project, which is anchored in the Canadian consensus statement definition of physical literacy, aimed to help establish the current physical literacy level of Canadian children.The CAPL was used to assess the physical literacy (and component domains: Daily Behaviour, Physical Competence, Knowledge and Understanding, and Motivation and Confidence) of Canadian children aged 8-12 years. Data were collected from 11 sites across Canada, yielding a sample of 10,034 participants (5030 girls). Descriptive statistics by age and gender were calculated and percentile distributions of physical literacy scores, including each domain and individual measure, were derived.The mean age of participants was 10.1 ± 1.2 years. Total physical literacy scores (out of 100) were on average 63.1 ± 13.0 for boys and 62.2 ± 11.3 for girls. For boys and girls respectively, domain scores were 19.9 ± 4.7 and 19.3 ± 4.1 (out of 32) for Physical Competence; 18.6 ± 7.9 and 18.5 ± 7.4 (out of 32) for Daily Behaviour; 12.7 ± 2.8 and 12.2 ± 2.6 (out of 18) for Motivation and Confidence; and 11.8 ± 2.8 and 12.2 ± 2.6 (out of 18) for Knowledge and Understanding. Physical Competence measures were on average 28.1 ± 8.4 cm (sit-and-reach flexibility), 33.5 ± 9.4 kg (grip strength, right + left), 23.4 ± 14.1 laps (Progressive Aerobic Cardiovascular Endurance Run [PACER] shuttle run), 61.8 ± 43.8 s (isometric plank), 19.0 ± 3.8 kg/m2 (body mass index), 67.3 ± 10.8 cm (waist circumference), and 20.6 ± 3.9 out of 28 points for the Canadian Agility and Movement Skill Assessment (CAMSA), with scores for boys higher than girls and older children higher than younger children for grip strength, PACER, plank, and CAMSA score. Girls and younger children had better scores on the sit-and-reach flexibility than boys and older children. Daily pedometer step counts were higher in boys than girls (12,355 ± 4252 vs. 10,779 ± 3624), and decreased with age.These results provide the largest and most comprehensive assessment of physical literacy of Canadian children to date, providing a "state of the nation" baseline, and can be used to monitor changes and inform intervention strategies going forward.</t>
+          <t>The associations between cardiorespiratory fitness (CRF) and physical literacy in children are largely unknown. The aim of this study was to assess the relationships between CRF, measured using the 20-m shuttle run test (20mSRT), and components of physical literacy among Canadian children aged 8-12 years.A total of 9393 (49.9% girls) children, with a mean (SD) age of 10.1 (±1.2) years, from a cross-sectional surveillance study were included for this analysis. The SRT was evaluated using a standardized 15 m or 20 m protocol. All 15 m SRTs were converted to 20mSRT values using a standardized formula. The four domains of physical literacy (Physical Competence, Daily Behaviour, Motivation and Confidence, and Knowledge and Understanding) were measured using the Canadian Assessment of Physical Literacy. Tertiles were identified for 20mSRT laps, representing low, medium, and high CRF for each age and gender group. Cohen's d was used to calculate the effect size between the low and high CRF groups.CRF was strongly and favourably associated with all components of physical literacy among school-aged Canadian children. The effect size between low and high CRF tertile groups was large for the Physical Competence domain (Cohen's d range: 1.11-1.94) across age and gender groups, followed by moderate to large effect sizes for Motivation and Confidence (Cohen's d range: 0.54-1.18), small to moderate effect sizes for Daily Behaviour (Cohen's d range: 0.25-0.81), and marginal to moderate effect sizes for Knowledge and Understanding (Cohen's d range: 0.08-0.70).This study identified strong favourable associations between CRF and physical literacy and its constituent components in children aged 8-12 years. Future research should investigate the sensitivity and specificity of the 20mSRT in screening those with low physical literacy levels.</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>['Mark S. Tremblay', 'Patricia E. Longmuir', 'Joel D. Barnes', 'Kevin Belanger', 'Kristal D. Anderson', 'Brenda Bruner', 'Jennifer L. Copeland', 'Christine Delisle Nyström', 'Melanie Gregg', 'Nathan Hall', 'Angela M. Kolen', 'Kirstin N. Lane', 'Barbi Law', 'Dany J. MacDonald', 'Luc J. Martin', 'Travis J. Saunders', 'Dwayne P. Sheehan', 'Michelle Stone', 'Sarah J. Woodruff']</t>
+          <t>['Justin J. Lang', 'Jean‐Philippe Chaput', 'Patricia E. Longmuir', 'Joel D. Barnes', 'Kevin Belanger', 'Grant R. Tomkinson', 'Kristal D. Anderson', 'Brenda Bruner', 'Jennifer L. Copeland', 'Melanie Gregg', 'Nathan Hall', 'Angela M. Kolen', 'Kirstin N. Lane', 'Barbi Law', 'Dany J. MacDonald', 'Luc J. Martin', 'Travis J. Saunders', 'Dwayne P. Sheehan', 'Michelle Stone', 'Sarah J. Woodruff', 'Mark S. Tremblay']</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>[["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['Camosun College', 'https://ror.org/02v6aqf52'], ['Nipissing University', 'https://ror.org/05k14ba46'], ['University of Lethbridge', 'https://ror.org/044j76961'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Winnipeg', 'https://ror.org/02gdzyx04'], ['University of Winnipeg', 'https://ror.org/02gdzyx04'], ['St. Francis Xavier University', 'https://ror.org/01wcaxs37'], ['Camosun College', 'https://ror.org/02v6aqf52'], ['Nipissing University', 'https://ror.org/05k14ba46'], ['University of Prince Edward Island', 'https://ror.org/02xh9x144'], ["Queen's University", 'https://ror.org/02y72wh86'], ['University of Prince Edward Island', 'https://ror.org/02xh9x144'], ['Mount Royal University', 'https://ror.org/04evsam41'], ['Dalhousie University', 'https://ror.org/01e6qks80'], ['University of Windsor', 'https://ror.org/01gw3d370']]</t>
+          <t>[['Agricultural Research Institute of Ontario', 'https://ror.org/011n4tk56'], ['Agricultural Research Institute of Ontario', 'https://ror.org/011n4tk56'], ['Agricultural Research Institute of Ontario', 'https://ror.org/011n4tk56'], ['Agricultural Research Institute of Ontario', 'https://ror.org/011n4tk56'], ['Agricultural Research Institute of Ontario', 'https://ror.org/011n4tk56'], ['University of South Australia', 'https://ror.org/01p93h210'], ['University of North Dakota', 'https://ror.org/04a5szx83'], ['Camosun College', 'https://ror.org/02v6aqf52'], ['Nipissing University', 'https://ror.org/05k14ba46'], ['University of Lethbridge', 'https://ror.org/044j76961'], ['University of Winnipeg', 'https://ror.org/02gdzyx04'], ['University of Winnipeg', 'https://ror.org/02gdzyx04'], ['St. Francis Xavier University', 'https://ror.org/01wcaxs37'], ['Camosun College', 'https://ror.org/02v6aqf52'], ['Nipissing University', 'https://ror.org/05k14ba46'], ['University of Prince Edward Island', 'https://ror.org/02xh9x144'], ["Queen's University", 'https://ror.org/02y72wh86'], ['University of Prince Edward Island', 'https://ror.org/02xh9x144'], ['Mount Royal University', 'https://ror.org/04evsam41'], ['Dalhousie University', 'https://ror.org/01e6qks80'], ['University of Windsor', 'https://ror.org/01gw3d370'], ['Agricultural Research Institute of Ontario', 'https://ror.org/011n4tk56']]</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>91</v>
+        <v>45</v>
       </c>
       <c r="K65" t="b">
         <v>1</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1186/s12889-018-5891-x</t>
+          <t>https://doi.org/10.1186/s12889-018-5896-5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2966612541</t>
+          <t>https://openalex.org/W2462681362</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/nu11081763</t>
+          <t>https://doi.org/10.1111/jppi.12160</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Using Food Models to Enhance Sugar Literacy among Older Adolescents: Evaluation of a Brief Experiential Nutrition Education Intervention</t>
+          <t>An Early Literacy Program for Young Children with Down Syndrome: Changes Observed over One Year</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Adolescent diets high in sugar are a public health concern. Sugar literacy interventions have changed intake but focused more on children, adults, and early adolescents and on sugar sweetened beverages rather than total sugar consumption. Food models are an efficacious experiential learning strategy with children. This study assessed the impact of two 45 min nutrition lessons using food models on adolescents’ sugar literacy. Classes (n = 16) were randomized to intervention or control with knowledge, label reading skills, intentions to limit sugar consumption measured at baseline and follow-up. Two hundred and three students aged 14 to 19 from six schools on Vancouver Island, BC, Canada participated in the study. Adolescents’ knowledge of added sugar in foods and beverages and servings per food group in a healthy diet was limited at baseline but improved significantly in the intervention condition (F(1, 201) = 104.84, p &amp;lt; 0.001) compared to controls. Intention to consume less added sugar increased significantly after intervention (F(1, 201) = 4.93, p = 0.03) as did label reading confidence (F(1, 200) = 14.94, p &amp;lt; 0.001). A brief experiential learning intervention using food models was efficacious for changing student’s knowledge about sugar guidelines and sugar in food, label reading confidence, and intention to change sugar consumption.</t>
+          <t>Although much individual variability exists, most persons with Down syndrome (DS) experience marked expressive language delays and challenges with speech production, hearing, and verbal memory that may negatively affect literacy development. There is, however, a paucity of research with respect to early intervention literacy programs with this population. The authors describe an early intervention literacy program that used a hybrid approach to reading instruction combining whole-word (i.e., visual) and analytic (i.e., phonic or sound-based) reading strategies. They also detail the changes observed in the literacy and language abilities of the participants over 1 year. The participants were 15 English speaking Canadian students with DS aged 3–6 years (M age 4;11, pretreatment) who took part in a 45-week program. Weekly individual sessions with a certified teacher were augmented by regular homework. Each student's literacy and language abilities were assessed immediately pretreatment and posttreatment. Measures of letter name identification, letter sound identification, print concepts, and identification of taught sight words showed statistically significant changes. Letter name identification, letter sound identification, and number of sight words read pretreatment were all positively and significantly correlated with gains in word identification. There was also a clear difference regarding how many new sight words students were able to read posttreatment depending on whether they used abstract symbols to communicate (i.e., unprompted spoken words or signs) pretreatment. The authors note that this study provides support for literacy interventions that combine phonological awareness, word analysis, sight word training, and shared book reading with children with DS as young as 3 years of age with varying levels of language development.</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>['María Isabel Santaló', 'Sandra L. Gibbons', 'Patti‐Jean Naylor']</t>
+          <t>['Paola Colozzo', 'Leah McKeil', 'Jill Petersen', 'Amanda N. Szabo‐Reed']</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>[['University of Victoria', 'https://ror.org/04s5mat29'], ['University of Victoria', 'https://ror.org/04s5mat29'], ['University of Victoria', 'https://ror.org/04s5mat29']]</t>
+          <t>[['University of British Columbia', 'https://ror.org/03rmrcq20'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['Down Syndrome Research Foundation', 'https://ror.org/04xayvx70'], ['Down Syndrome Research Foundation', 'https://ror.org/04xayvx70']]</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/nu11081763</t>
+          <t>https://doi.org/10.1111/jppi.12160</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2474144775</t>
+          <t>https://openalex.org/W2800995841</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1186/s13104-016-2141-0</t>
+          <t>https://doi.org/10.17269/s41997-018-0048-3</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Health literacy in pregnant women facing prenatal screening may explain their intention to use a patient decision aid: a short report</t>
+          <t>Assessing health literacy among older adults living in subsidized housing: a cross-sectional study</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2016</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>cc-by</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>It has been suggested that health literacy may impact the use of decision aids (DAs) among patients facing difficult decisions. Embedded in the pilot test of a questionnaire, this study aimed to measure the association between health literacy and pregnant women's intention to use a DA to decide about prenatal screening. We recruited a convenience sample of 45 pregnant women in three clinical sites (family practice teaching unit, birthing center and obstetrical ambulatory care clinic). We asked participating women to complete a self-administered questionnaire assessing their intention to use a DA to decide about prenatal screening and assessed their health literacy levels using one subjective and two objective scales. Two of the three scales discriminated between levels of health literacy (three numeracy questions and three health literacy questions). We found a positive correlation between pregnant women's intention to use a DA and subjective health literacy (Spearman coefficient, Rho 0.32, P = 0.04) but not objective health literacy (Spearman coefficient, Rho 0.07, P = 0.65). Hence subjective health literacy may affect the intention to use a DA among pregnant women facing a decision about prenatal screening. Special attention should be given to pregnant women with lower health literacy levels to increase their intention to use a DA and ensure that every pregnant women can give informed and value-based consent to prenatal screening.</t>
-        </is>
-      </c>
+        <v>2018</v>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>['Agathe Delanoë', 'Johanie Lépine', 'Maria Esther Leiva Portocarrero', 'Hubert Robitaille', 'Stéphane Turcotte', 'Isabelle Lévesque', 'Brenda J. Wilson', 'Anik Giguère', 'France Légaré']</t>
+          <t>['Gina Agarwal', 'Kendra Habing', 'Melissa Pirrie', 'Ric Angeles', 'Francine Marzanek', 'Jenna Parascandalo']</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>[["Hôpital Saint-François d'Assise", 'https://ror.org/02r1pzn16'], ['Centre hospitalier universitaire de Québec', 'https://ror.org/006a7pj43'], ["Hôpital Saint-François d'Assise", 'https://ror.org/02r1pzn16'], ['Centre hospitalier universitaire de Québec', 'https://ror.org/006a7pj43'], ["Hôpital Saint-François d'Assise", 'https://ror.org/02r1pzn16'], ['Centre hospitalier universitaire de Québec', 'https://ror.org/006a7pj43'], ["Hôpital Saint-François d'Assise", 'https://ror.org/02r1pzn16'], ['Centre hospitalier universitaire de Québec', 'https://ror.org/006a7pj43'], ["Hôpital Saint-François d'Assise", 'https://ror.org/02r1pzn16'], ['Centre hospitalier universitaire de Québec', 'https://ror.org/006a7pj43'], ['Université Laval', 'https://ror.org/04sjchr03'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ['Quebec Research and Development Centre', 'https://ror.org/01xgv8v73'], ['Université Laval', 'https://ror.org/04sjchr03']]</t>
+          <t>[['Impact', 'https://ror.org/05d9dsr70'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['McMaster University', 'https://ror.org/02fa3aq29']]</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="K67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1186/s13104-016-2141-0</t>
+          <t>https://doi.org/10.17269/s41997-018-0048-3</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2794438485</t>
+          <t>https://openalex.org/W2894683557</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://doi.org/10.17269/s41997-018-0034-9</t>
+          <t>https://doi.org/10.1186/s12889-018-5899-2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Primary care intervention to address cardiovascular disease medication health literacy among Indigenous peoples: Canadian results of a pre-post-design study</t>
+          <t>Refining the Canadian Assessment of Physical Literacy based on theory and factor analyses</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -3762,52 +3766,52 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cardiovascular diseases (CVD) are a leading cause of illness and death for Indigenous people in Canada and globally. Appropriate medication can significantly improve health outcomes for persons diagnosed with CVD or for those at high risk of CVD. Poor health literacy has been identified as a major barrier that interferes with client understanding and taking of CVD medication. Strengthening health literacy within health services is particularly relevant in Indigenous contexts, where there are systemic barriers to accessing literacy skills.The aim of this study is to test the effect of a customized, structured health literacy educational program addressing CVD medications.Pre-post-design involves health providers and Indigenous clients at the De dwa da dehs nye&gt;s Aboriginal Health Centre (DAHC) in Ontario, Canada. Forty-seven Indigenous clients with or at high risk of CVD received three educational sessions delivered by a trained Indigenous nurse over a 4- to 7-week period. A tablet application, pill card and booklet supported the sessions. Primary outcomes were knowledge of CVD medications and health literacy practices, which were assessed before and after the programe.Following the program compared to before, mean medication knowledge scores were 3.3 to 6.1 times higher for the four included CVD medications. Participants were also more likely to refer to the customized pill card and booklet for information and answer questions from others regarding CVD.This customized education program was highly effective in increasing medication knowledge and health literacy practice among Indigenous people with CVD or at risk of CVD attending the program at an urban Indigenous health centre.</t>
+          <t>The Canadian Assessment of Physical Literacy (CAPL) is a 25-indicator assessment tool comprising four domains of physical literacy: (1) Physical Competence, (2) Daily Behaviour, (3) Motivation and Confidence, and (4) Knowledge and Understanding. The purpose of this study was to re-examine the factor structure of CAPL scores and the relative weight of each domain for an overall physical literacy factor. Our goal was to maximize content representation, and reduce construct irrelevant variance and participant burden, to inform the development of CAPL-2 (a revised, shorter, and theoretically stronger version of CAPL).Canadian children (n = 10,034; Mage = 10.6, SD = 1.2; 50.1% girls) completed CAPL testing at one time point. Confirmatory factor analysis was used.Based on weak factor loadings (λs &lt; 0.32) and conceptual alignment, we removed body mass index, waist circumference, sit-and-reach flexibility, and grip strength as indicators of Physical Competence. Based on the factor loading (λ &lt; 0.35) and conceptual alignment, we removed screen time as an indicator of Daily Behaviour. To reduce redundancy, we removed children's activity compared to other children as an indicator of Motivation and Confidence. Based on low factor loadings (λs &lt; 0.35) and conceptual alignment, we removed knowledge of screen time guidelines, what it means to be healthy, how to improve fitness, activity preferences, and physical activity safety gear indicators from the Knowledge and Understanding domain. The final refined CAPL model was comprised of 14 indicators, and the four-factor correlated model fit the data well (r ranged from 0.08 to 0.76), albeit with an unexpected cross-loading from Daily Behaviour to knowledge of physical activity guidelines (mean- and variance-adjusted weighted least square [WLSMV] χ2(70) = 1221.29, p &lt; 0.001, Comparative Fit Index [CFI] = 0.947, root mean square error of approximation [RMSEA] = 0.041[0.039, 0.043]). Finally, our higher-order model with Physical Literacy as a factor with indicators of Physical Competence (λ = 0.68), Daily Behaviour (λ = 0.91), Motivation and Confidence (λ = 0.80), and Knowledge and Understanding (λ = 0.21) fit the data well.The scores from the revised and much shorter 14-indicator model of CAPL can be used to assess the four correlated domains of physical literacy and/or a higher-order aggregate physical literacy factor. The results of this investigation will inform the development of CAPL-2.</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>['Janet Smylie', 'Kristen O’Brien', 'Chloé G. Xavier', 'Marcia Anderson', 'Constance McKnight', 'Bernice Downey', 'Margaret Kelaher']</t>
+          <t>['Katie E. Gunnell', 'Patricia E. Longmuir', 'Joel D. Barnes', 'Kevin Belanger', 'Mark S. Tremblay']</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>[["St. Michael's Hospital", 'https://ror.org/04skqfp25'], ["St. Michael's Hospital", 'https://ror.org/04skqfp25'], ["St. Michael's Hospital", 'https://ror.org/04skqfp25'], ['University of Manitoba', 'https://ror.org/02gfys938'], ['Aboriginal Affairs Northern Dev Canada', 'https://ror.org/05pgxdd43'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['The University of Melbourne', 'https://ror.org/01ej9dk98']]</t>
+          <t>[["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27']]</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="K68" t="b">
         <v>1</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>https://doi.org/10.17269/s41997-018-0034-9</t>
+          <t>https://doi.org/10.1186/s12889-018-5899-2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2894753606</t>
+          <t>https://openalex.org/W2725011375</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1186/s12889-018-5900-0</t>
+          <t>https://doi.org/10.1186/s12955-017-0716-7</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Revising the motivation and confidence domain of the Canadian assessment of physical literacy</t>
+          <t>The relationship between health literacy and quality of life among frequent users of health care services: a cross-sectional study</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -3816,248 +3820,256 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>The Motivation and Confidence domain questionnaire in the Canadian Assessment of Physical Literacy (CAPL) was lengthy (36 single items that aggregate to five subscales), and thus burdensome to both participants and practitioners. The purpose of this study was to use factor analysis to refine the Motivation and Confidence domain to be used in the CAPL-Second Edition (CAPL-2).Children, primarily recruited through free-of-charge summer day camps (n = 205, Mage = 9.50 years, SD = 1.14, 50.7% girls), completed the CAPL-2 protocol, and two survey versions of the Motivation and Confidence questionnaire. Survey 1 contained the Motivation and Confidence questionnaire items from the original CAPL, whereas Survey 2 contained a battery of items informed by self-determination theory to assess motivation and confidence. First, factor analyses were performed on individual questionnaires to examine validity evidence (i.e., internal structure) and score reliability (i.e., coefficient H and omega total). Second, factor analyses were performed on different combinations of questionnaires to establish the least burdensome yet well-fitted and theoretically aligned model.The assessment of adequacy and predilection, based on 16 single items as originally conceptualized within the CAPL, was not a good fit to the data. Therefore, a revised and shorter version of these scales was proposed, based on exploratory factor analysis. The self-determination theory items provided a good fit to the data; however, identified, introjected, and external regulation had low score reliability. Overall, a model comprising three single items for each of the following subscales was proposed for use within the CAPL-2: adequacy, predilection, intrinsic motivation, and perceived competence satisfaction. This revised domain fit well within the overall CAPL-2 model specifying a higher-order physical literacy factor (MLRχ2(63) = 81.45, p = 0.06, CFI = 0.908, RMSEA = 0.038, 90% CI (0.00, 0.060)).The revised and much shorter questionnaire of 12 items that aggregate to four subscales within the domain of Motivation and Confidence is recommended for use in the CAPL-2. The revised domain is aligned with the definition of motivation and confidence within physical literacy and has clearer instructions for completion.</t>
+          <t>Although health literacy and quality of life are important concepts in health care, the link between them is unclear, especially for a population of frequent users of health care services with chronic diseases. Low health literacy is a common problem that has been linked to several negative health outcomes. Quality of life is an important health outcome in patient-centered care. Frequent users of health care services are a vulnerable population that deserves attention due to high costs and negative outcomes such as lower quality of life and higher mortality. The objective of this study was to examine the relationship between health literacy and the physical and mental components of quality of life among frequent users of health care services with chronic diseases. This study presents the cross-sectional analysis of data collected through the V1SAGES project, a randomized controlled trial on the effectiveness of a case management intervention in primary care in Quebec, Canada. Participants (n = 247) were frequent users of health care services presenting at least one chronic condition. Health literacy was measured by the Newest Vital Sign (NVS), and the physical and mental components of quality of life were evaluated by the Short Form Health Survey Version 2 (SF-12v2). The association between health literacy (independent variable) and the physical and mental components of quality of life was examined using biserial correlation. No association was found between health literacy and quality of life (physical component: r = 0.108, ρ = 0.11; mental component: r = 0.147, ρ = 0.15). This study suggests that there is no relationship between health literacy and the physical and mental components of quality of life among frequent users of health care services. NCT01719991 . Registered October 25, 2012.</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>['Katie E. Gunnell', 'Patricia E. Longmuir', 'Sarah J. Woodruff', 'Joel D. Barnes', 'Kevin Belanger', 'Mark S. Tremblay']</t>
+          <t>['Éva Marjorie Couture', 'Maud‐Christine Chouinard', 'Martin Fortin', 'Catherine Hudon']</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>[['Carleton University', 'https://ror.org/02qtvee93'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Windsor', 'https://ror.org/01gw3d370'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27']]</t>
+          <t>[['Université de Sherbrooke', 'https://ror.org/00kybxq39'], ['Université du Québec à Chicoutimi', 'https://ror.org/00y3hzd62'], ['Université de Sherbrooke', 'https://ror.org/00kybxq39'], ['Centre Hospitalier Universitaire de Sherbrooke', 'https://ror.org/020r51985']]</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="K69" t="b">
         <v>1</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1186/s12889-018-5900-0</t>
+          <t>https://doi.org/10.1186/s12955-017-0716-7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2183435816</t>
+          <t>https://openalex.org/W2895497822</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1007/s11092-015-9233-6</t>
+          <t>https://doi.org/10.1186/s12889-018-5897-4</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Teacher assessment literacy: a review of international standards and measures</t>
+          <t>The relationship between physical literacy scores and adherence to Canadian physical activity and sedentary behaviour guidelines</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2015</v>
-      </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
+        <v>2018</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>cc-by</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Physical literacy is an emerging construct in children's health promotion, and may impact their lifelong physical activity habits. However, recent data reveal that only a small portion of Canadian children are regularly physically active and/or meet sedentary behaviour guidelines. To our knowledge, no study has investigated the association between physical literacy and movement behaviour guidelines. Therefore, the purpose of this study was to examine the relationship between physical literacy scores in Canadian children who meet or do not meet physical activity and sedentary behaviour guidelines.Children (n = 2956; 56.6% girls) aged 8-12 years from 10 Canadian cities had their physical literacy levels measured using the Canadian Assessment of Physical Literacy, which consists of four domains (Physical Competence; Daily Behaviour; Knowledge and Understanding; and Motivation and Confidence) that are aggregated to provide a composite physical literacy score. Physical activity levels were measured by pedometers, and sedentary behaviour was assessed through self-report questionnaire. Analyses were conducted separately for each guideline, comparing participants meeting versus those not meeting the guidelines. Comparisons were performed using MANOVA and logistic regression to control for age, gender, and seasonality.Participants meeting physical activity guidelines or sedentary behaviour guidelines had higher physical literacy domain scores for Physical Competence and for Motivation and Confidence compared to those not meeting either guideline (both p &lt; 0.0001). Participants had increased odds of meeting physical activity guidelines and sedentary behaviour guidelines if they met the minimum recommended level of the Physical Competence and Motivation and Confidence domains. Significant age (OR 0.9; 95% CI: 0.8, 0.9), gender (OR 0.4; 95% CI: 0.3, 0.5) and seasonality effects (OR 1.6; 95% CI: 1.2, 2.2 spring and OR 1.7; 95% CI: 1.2, 2.5 summer, reference winter) were seen for physical activity guidelines, and age (OR 0.8; 95% CI: 0.7, 0.8) and gender effects (OR 1.7; 95% CI: 1.4, 2.0) for sedentary behaviour guidelines. Knowledge and Understanding of physical activity principles was not related to guideline adherence in either model.These cross-sectional findings demonstrate important associations between physical literacy and guideline adherence for physical activity and sedentary behaviour. Future research should explore the causality of these associations.</t>
+        </is>
+      </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>['Christopher DeLuca', 'Danielle LaPointe-McEwan', 'Ulemu Luhanga']</t>
+          <t>['Kevin Belanger', 'Joel D. Barnes', 'Patricia E. Longmuir', 'Kristal D. Anderson', 'Brenda Bruner', 'Jennifer L. Copeland', 'Melanie Gregg', 'Nathan Hall', 'Angela M. Kolen', 'Kirstin N. Lane', 'Barbi Law', 'Dany J. MacDonald', 'Luc J. Martin', 'Travis J. Saunders', 'Dwayne P. Sheehan', 'Michelle Stone', 'Sarah J. Woodruff', 'Mark S. Tremblay']</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>[["Queen's University", 'https://ror.org/02y72wh86'], ["Queen's University", 'https://ror.org/02y72wh86'], ["Queen's University", 'https://ror.org/02y72wh86']]</t>
+          <t>[["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['Camosun College', 'https://ror.org/02v6aqf52'], ['Nipissing University', 'https://ror.org/05k14ba46'], ['University of Lethbridge', 'https://ror.org/044j76961'], ['University of Winnipeg', 'https://ror.org/02gdzyx04'], ['University of Winnipeg', 'https://ror.org/02gdzyx04'], ['St. Francis Xavier University', 'https://ror.org/01wcaxs37'], ['Camosun College', 'https://ror.org/02v6aqf52'], ['Nipissing University', 'https://ror.org/05k14ba46'], ['University of Prince Edward Island', 'https://ror.org/02xh9x144'], ["Queen's University", 'https://ror.org/02y72wh86'], ['University of Prince Edward Island', 'https://ror.org/02xh9x144'], ['Mount Royal University', 'https://ror.org/04evsam41'], ['Dalhousie University', 'https://ror.org/01e6qks80'], ['University of Windsor', 'https://ror.org/01gw3d370'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27']]</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>199</v>
+        <v>137</v>
       </c>
       <c r="K70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1007/s11092-015-9233-6</t>
+          <t>https://doi.org/10.1186/s12889-018-5897-4</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2581724875</t>
+          <t>https://openalex.org/W3110689777</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1007/s11136-016-1495-z</t>
+          <t>https://doi.org/10.1080/02660830.2020.1855870</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Health literacy and logical inconsistencies in valuations of hypothetical health states: results from the Canadian EQ-5D-5L valuation study</t>
+          <t>The automated literacies of e-recruitment and online services</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Online technologies have entered almost all spheres of life, introducing new challenges to how literacies are theorised, defined and taken up in adult literacy education settings. This process has accelerated during the COVID-19 pandemic and on a global scale, as more services, resources and information move online. An important, if under-studied example of this trend is e-recruitment. Job seekers increasingly rely upon automated platforms to find and apply for jobs, and their fate in these selection processes are often automated. Drawing on data from the German LEO study and ethnographic interviews with job seekers in community-based digital literacy classes in Canada, this article explores how adult job seekers experience e-recruitment platforms, examining promises of efficiency, convenience and fairness in light of embedded inequalities within algorithmic agencies. Located within constructs of digital inequality, new literacy studies and sociomaterial literacies, findings suggest the need to reconfigure skills discourses, literacy measurement projects, and literacies education to account for automated intelligences as new actors in the literacies landscape.</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>['Fatima Al Sayah', 'Jeffrey Johnson', 'Arto Öhinmaa', 'Feng Xie', 'Nick Bansback']</t>
+          <t>['Suzanne Smythe', 'Anke Grotlüschen', 'Klaus Buddeberg']</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>[['University of Alberta', 'https://ror.org/0160cpw27'], ['University of Alberta', 'https://ror.org/0160cpw27'], ['University of Alberta', 'https://ror.org/0160cpw27'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['St. Joseph’s Healthcare Hamilton', 'https://ror.org/009z39p97'], ['University of British Columbia', 'https://ror.org/03rmrcq20']]</t>
+          <t>[['Simon Fraser University', 'https://ror.org/0213rcc28'], ['Universität Hamburg', 'https://ror.org/00g30e956'], ['Universität Hamburg', 'https://ror.org/00g30e956']]</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="K71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1007/s11136-016-1495-z</t>
+          <t>https://doi.org/10.1080/02660830.2020.1855870</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2895198122</t>
+          <t>https://openalex.org/W2916608537</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1186/s12889-018-5901-z</t>
+          <t>https://doi.org/10.1177/1524839919827576</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>An exploratory analysis of missing data from the Royal Bank of Canada (RBC) Learn to Play – Canadian Assessment of Physical Literacy (CAPL) project</t>
+          <t>Health Literacy Among Canadian Men Experiencing Prostate Cancer</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2018</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>cc-by</t>
-        </is>
-      </c>
+        <v>2019</v>
+      </c>
+      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Physical literacy comprises a range of tests over four domains (Physical Competence, Daily Behaviour, Motivation and Confidence, and Knowledge and Understanding). The patterns of missing data in large field test batteries such as those for physical literacy are largely unknown. Therefore, the aim of this paper was to explore the patterns and possible reasons for missing data in the Royal Bank of Canada Learn to Play-Canadian Assessment of Physical Literacy (RBC Learn to Play-CAPL) project.A total of 10,034 Canadian children aged 8 to 12 years participated in the RBC Learn to Play-CAPL project. A 32-variable subset from the larger CAPL dataset was used for these analyses. Several R packages ("Hmisc", "mice", "VIM") were used to generate matrices and plots of missing data, and to perform multiple imputations.Overall, the proportion of missing data for individual measures and domains ranged from 0.0 to 33.8%, with the average proportion of missing data being 4.0%. The largest proportion of missing data in CAPL was the pedometer step counts, followed by the components of the Physical Competence domain and the Children's Self-Perception of Adequacy in and Predilection for Physical Activity subscales. When domain scores were regressed on five imputed subsets with the original subset as the reference, there were small and statistically detectable differences in the Daily Behaviour score (β = - 1.6 to - 1.7, p &lt; 0.001). However, for the other domain scores the differences were negligible and statistically undetectable (β = - 0.01 to - 0.06, p &gt; 0.05).This study has implications for other researchers or educators who are creating or using large field-based assessment measures in the areas of physical literacy, physical activity, or physical fitness, as this study demonstrates where problems in data collection can arise and how missing data can be avoided. When large proportions of missing data are present, imputation techniques, correction factors, or other treatment options may be required.</t>
+          <t>The objective was to describe the health literacy of a sample of Canadian men with prostate cancer and explore whether sociodemographic and health factors were related to men’s health literacy scores. A sample of 213 Canadian men ( M age = 68.71 years, SD = 7.44) diagnosed with prostate cancer were recruited from an online prostate cancer support website. The men completed the Health Literacy Questionnaire along with demographic, comorbidity, and prostate cancer treatment–related questions online. Of the 5-point scales, men’s health literacy scores were highest for “Understanding health information enough to know what to do” ( M = 4.04, SD = 0.48) and lowest for “Navigating the health care system” ( M = 3.80, SD = 0.58). Of the 4-point scales, men’s scores were highest for “Feeling understood and supported by health care professionals” ( M = 3.20, SD = 0.52) and lowest for “Having sufficient information to manage my health” ( M = 2.97, SD = 0.46). Regression analyses indicated that level of education was positively associated with health literacy scores, and men without comorbidities had higher health literacy scores. Age and years since diagnosis were unrelated to health literacy. Support in health system navigation and self-management of health may be important targets for intervention.</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>['Christine Delisle Nyström', 'Joel D. Barnes', 'Mark S. Tremblay']</t>
+          <t>['Cherisse L. Seaton', 'John L. Oliffe', 'Simon Rice', 'Joan L. Bottorff', 'Steven T. Johnson', 'Susan Gordon', 'Suzanne K. Chambers']</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>[["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27']]</t>
+          <t>[['Kelowna General Hospital', 'https://ror.org/01j25h453'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['Kelowna General Hospital', 'https://ror.org/01j25h453'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['Orygen Youth Health', 'https://ror.org/00ej70p06'], ['The University of Melbourne', 'https://ror.org/01ej9dk98'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['Kelowna General Hospital', 'https://ror.org/01j25h453'], ['Athabasca University', 'https://ror.org/01y3xgc52'], ['Flinders University', 'https://ror.org/01kpzv902'], ['University of Technology Sydney', 'https://ror.org/03f0f6041'], ['Griffith University', 'https://ror.org/02sc3r913']]</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1186/s12889-018-5901-z</t>
+          <t>https://doi.org/10.1177/1524839919827576</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2898919684</t>
+          <t>https://openalex.org/W3193745980</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1123/jtpe.2018-0028</t>
+          <t>https://doi.org/10.3390/ijerph18168646</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Examining the Impact of a Teaching Games for Understanding Approach on the Development of Physical Literacy Using the Passport for Life Assessment Tool</t>
+          <t>An Integrated Framework to Conceptualize and Develop the Vancouver Airways Health Literacy Tool (VAHLT)</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Purpose: The purpose of this study was to investigate the impact of an 8-week after-school intramural program that adopted a Teaching Games for Understanding (TGfU) approach to facilitate the development of elementary-school-aged children physical literacy. Methods: Using Physical and Health Education Canada's Passport for Life tool, 22 participants took part in a battery of assessments consistent with characteristics of physical literacy. These measures were (a) active participation, (b) living skills, (c) fitness skills, and (d) movement skills. Each category of assessment included three submeasures for a total of 12 indicators of physical literacy. Participants were assessed at the beginning of the PlaySport Intramural Program and then 8 weeks later following participation in a series of after-school TGfU lessons designed using the PlaySport program. Results: Of the 12 indicators of physical literacy, the majority of participants reported higher scores at the end program for 10 of the indicators. Significant (p &lt; .004) improvements were seen in balance and stability skills, cardiovascular endurance, participation in diverse environments, and interest in participating in diverse activities. No improvements were seen in kicking skills and interacting with others. Discussion/Conclusion: These results provide support for the hypothesis that the use of pedagogical approaches such as TGfU can be effective at facilitating certain components of children's development of physical literacy.</t>
+          <t>There is currently no comprehensive tool to assess the functional health literacy (HL) skills of chronic airway disease (CAD) patients. The purpose of this article is to describe the development of a new HL measure, the Vancouver Airways Health Literacy Tool (VAHLT). The tool was developed through the following phases: (1) Tool conceptualization, consisting of: (A) a systematic review (SR), (B) focus group sessions with CAD patients to understand barriers and facilitators to CAD management, (C) a survey with key-informants to obtain strategies to mitigate self-management barriers and validate patient-derived topics, and (D) respiratory physicians’ review of the topics; (2) Scenario and item development; and (3) Tool testing and content validation. The SR identified the lack of a valid HL measurement tool for CAD patients. Patients provided an initial shortlist of disease-related self-care topics. Key-informants helped to finalize topics for inclusion. Respiratory physicians and patients contributed to the development of a scenario-based questionnaire, which was refined during three rounds of testing to develop a 44-item instrument comprising nine self-management passages. We highlight the holistic process of integrating information from the literature with knowledge gained from key stakeholders into our tool framework. Our approach to stakeholder engagement may be of interest to researchers developing similar tools, and could facilitate the development and testing of HL-based interventions to ultimately improve patient outcomes and reduce the burden on the healthcare system.</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>['James Mandigo', 'Ken R. Lodewyk', 'Jay Tredway']</t>
+          <t>['Iraj Poureslami', 'Jacek A. Kopec', 'Noah Tregobov', 'Jessica Shum', 'Richard Sawatzky', 'Richard E. Hohn', 'J. Mark FitzGerald']</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>[['Brock University', 'https://ror.org/056am2717'], ['Brock University', 'https://ror.org/056am2717'], ['Ridley College', 'https://ror.org/02gdmq314']]</t>
+          <t>[['University of British Columbia', 'https://ror.org/03rmrcq20'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['Western University', 'https://ror.org/02grkyz14'], ['Trinity Western University', 'https://ror.org/01j2kd606'], ['Simon Fraser University', 'https://ror.org/0213rcc28'], ['University of British Columbia', 'https://ror.org/03rmrcq20']]</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>74</v>
+        <v>7</v>
       </c>
       <c r="K73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1123/jtpe.2018-0028</t>
+          <t>https://doi.org/10.3390/ijerph18168646</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2793868721</t>
+          <t>https://openalex.org/W2991461979</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1186/s12889-018-5892-9</t>
+          <t>https://doi.org/10.3389/fpubh.2019.00346</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>The relationship between sedentary behaviour and physical literacy in Canadian children: a cross-sectional analysis from the RBC-CAPL Learn to Play study</t>
+          <t>Physical Literacy and Resilience in Children and Youth</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -4066,398 +4078,410 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Physical literacy is the foundation of a physically active lifestyle. Sedentary behaviour displays deleterious associations with important health indicators in children. However, the association between sedentary behaviour and physical literacy is unknown. The purpose of this study was to identify the aspects of physical literacy that are associated with key modes of sedentary behaviour among Canadian children participating in the RBC-CAPL Learn to Play study.A total of 8,307 children aged 8.0-12.9 years were included in the present analysis. Physical literacy was assessed using the Canadian Assessment of Physical Literacy, which measures four domains (Physical Competence, Daily Behaviour, Motivation and Confidence, Knowledge and Understanding). Screen-based sedentary behaviours (TV viewing, computer and video game use), non-screen sedentary behaviours (reading, doing homework, sitting and talking to friends, drawing, etc.) and total sedentary behaviour were assessed via self-report questionnaire. Linear regression models were used to determine significant (p&lt;0.05) correlates of each mode of sedentary behaviour.In comparison to girls, boys reported more screen time (2.7±2.0 vs 2.2±1.8 hours/day, Cohen's d=0.29), and total sedentary behaviour (4.3±2.6 vs 3.9±2.4 hours/day, Cohen's d=0.19), but lower non-screen-based sedentary behaviour (1.6±1.3 vs 1.7±1.3 hours/day, Cohen's d=0.08) (all p&lt; 0.05). Physical Competence (standardized β's: -0.100 to -0.036, all p&lt;0.05) and Motivation and Confidence (standardized β's: -0.274 to -0.083, all p&lt;0.05) were negatively associated with all modes of sedentary behaviour in fully adjusted models. Knowledge and Understanding was negatively associated with screen-based modes of sedentary behaviour (standardized β's: -0.039 to -0.032, all p&lt;0.05), and positively associated with non-screen sedentary behaviour (standardized β: 0.098, p&lt;0.05). Progressive Aerobic Cardiovascular Endurance Run score and log-transformed plank score were negatively associated with all screen-based modes of sedentary behaviour, while the Canadian Agility and Movement Skill Assessment score was negatively associated with all modes of sedentary behaviour other than TV viewing (all p&lt;0.05).These results highlight differences in the ways that screen and non-screen sedentary behaviours relate to physical literacy. Public health interventions should continue to target screen-based sedentary behaviours, given their potentially harmful associations with important aspects of physical literacy.</t>
+          <t>Background There is growing interest in the relationship between physical and psychosocial factors related to resilience to better understand the antecedents of health and successful adaptation to challenges in and out of school, and across the lifespan. To further this understanding, a trans-disciplinary approach was used to investigate the association between the multidimensional constructs of physical literacy and resilience in children at a key stage in their development. Methods Cross-sectional data were collected from 227 school children aged 9-12 years old from five schools in [blinded]. Resilience was measured using the Child and Youth Resilience Measure, and physical literacy through the Physical Literacy Assessment for Youth tools. Data were provided by self-report, surrogate assessors of the child (physical education teachers and parents), and trained assessors for movement skills. These data were analysed using correlation and logistic regression. Results Resilience was significantly correlated with numerous indicators of physical literacy, including movement capacity, confidence, and competence, environmental engagement, and overall perceptions of physical literacy. Regressions indicated that resilience could be predicted by movement confidence and competence, environmental engagement, and overall physical literacy. Conclusions The findings of this study, using a constellation of sources, provide foundational evidence for the link between resilience and physical literacy among children, encouraging the importance of physical literacy development in schools. Longitudinal studies are required to further examine this relationship and how these previously unrelated fields may work together for a richer understanding of the interplay between the physical and psychological determinants of well-being.</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>['Travis J. Saunders', 'Dany J. MacDonald', 'Jennifer L. Copeland', 'Patricia E. Longmuir', 'Joel D. Barnes', 'Kevin Belanger', 'Brenda Bruner', 'Melanie Gregg', 'Nathan Hall', 'Angela M. Kolen', 'Barbi Law', 'Luc J. Martin', 'Dwayne P. Sheehan', 'Michelle Stone', 'Sarah J. Woodruff', 'Mark S. Tremblay']</t>
+          <t>['Philip Jefferies', 'Michael Ungar', 'Patrice Aubertin', 'Dean Kriellaars']</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>[['University of Prince Edward Island', 'https://ror.org/02xh9x144'], ['University of Prince Edward Island', 'https://ror.org/02xh9x144'], ['University of Lethbridge', 'https://ror.org/044j76961'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['Nipissing University', 'https://ror.org/05k14ba46'], ['University of Winnipeg', 'https://ror.org/02gdzyx04'], ['University of Winnipeg', 'https://ror.org/02gdzyx04'], ['St. Francis Xavier University', 'https://ror.org/01wcaxs37'], ['Nipissing University', 'https://ror.org/05k14ba46'], ["Queen's University", 'https://ror.org/02y72wh86'], ['Mount Royal University', 'https://ror.org/04evsam41'], ['Dalhousie University', 'https://ror.org/01e6qks80'], ['University of Windsor', 'https://ror.org/01gw3d370'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27']]</t>
+          <t>[['Dalhousie University', 'https://ror.org/01e6qks80'], ['Dalhousie University', 'https://ror.org/01e6qks80'], ['National Circus School', 'https://ror.org/05ge25h32'], ['University of Manitoba', 'https://ror.org/02gfys938']]</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="K74" t="b">
         <v>1</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1186/s12889-018-5892-9</t>
+          <t>https://doi.org/10.3389/fpubh.2019.00346</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2012525493</t>
+          <t>https://openalex.org/W3035800846</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.jmathb.2015.01.004</t>
+          <t>https://doi.org/10.1016/j.pmedr.2020.101149</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>The assessment of mathematical literacy of linguistic minority students: Results of a multi-method investigation</t>
+          <t>Testing a school-based program to promote digital health literacy and healthy lifestyle behaviours in intermediate elementary students: The Learning for Life program</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2015</v>
-      </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
+        <v>2020</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>cc-by-nc-nd</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Promoting digital health literacy and healthy lifestyle behaviours in children can lead to positive long-term health outcomes and prevent chronic diseases. However, there are few school-based interventions promoting this education to intermediate elementary students. The objective of this study was to test the effectiveness of a novel intervention to increase students' digital health literacy and health knowledge. Learning for Life is a classroom-based education program, developed for grade 4-7 students and delivered by teachers over six weeks. Three Canadian schools were recruited to deliver the intervention in 2018. This study had a pre-post design and no control group. Students' self-reported digital health literacy and healthy lifestyle behaviours were measured at pre-intervention (n = 126), post-intervention (n = 119), and two-month follow-up (n = 104). Students at pre-intervention had a mean (SD) age of 10.98 (0.56) years (57.1% females). Almost all (97%) students had unsupervised access to the Internet through a computer or smartphone. From pre- to post-intervention, students' digital health literacy increased (p = 0.009), but decreased from post-intervention to follow-up (p &lt; 0.001). Post-intervention, the majority of students could identify at least one healthy behaviour (e.g., exercising one hour/day) and reported making at least one healthy change in their lives (e.g., eating more fruits/vegetables). This study demonstrated that the Learning for Life intervention can improve intermediate elementary students' digital health literacy over the short-term and help them learn and retain healthy lifestyle knowledge and behaviours. These findings affirm the need for interventions promoting digital healthy literacy and healthy lifestyle behaviours for this age group.</t>
+        </is>
+      </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>['Wolff‐Michael Roth', 'Kadriye Ercikan', 'Marielle Simon', 'Romeo Fola']</t>
+          <t>['Antonia Hyman', 'Kurtis Stewart', 'Anne-Marie Jamin', 'Helen Novak Lauscher', 'Elizabeth Stacy', 'Gerry Kasten', 'Kendall Ho']</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>[['University of Victoria', 'https://ror.org/04s5mat29'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ['University of Ottawa', 'https://ror.org/03c4mmv16']]</t>
+          <t>[['University of British Columbia', 'https://ror.org/03rmrcq20'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['Vancouver Coastal Health', 'https://ror.org/03bd8jh67'], ['University of British Columbia', 'https://ror.org/03rmrcq20']]</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="K75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.jmathb.2015.01.004</t>
+          <t>https://doi.org/10.1016/j.pmedr.2020.101149</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2588450759</t>
+          <t>https://openalex.org/W2994090949</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1542/peds.2016-1961</t>
+          <t>https://doi.org/10.3389/feduc.2019.00120</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Parental Health Literacy and Outcomes of Childhood Nephrotic Syndrome</t>
+          <t>Measurement Comparability of Reading in the English and French Canadian Populations: Special Case of the 2011 Progress in International Reading Literacy Study</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2017</v>
-      </c>
-      <c r="F76" t="inlineStr"/>
+        <v>2019</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>cc-by</t>
+        </is>
+      </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Determine the association of parental health literacy with treatment response among children with nephrotic syndrome.This was a cohort study of children aged 1-18 with nephrotic syndrome and their parent. Health literacy was measured using the validated Short Test of Functional Health Literacy in Adults assessing reading comprehension and numeracy. Outcomes included initial relapse-free period, frequently relapsing disease, relapse rate, second-line medication use, and complete remission after therapy.Of 190 parents, 80% had adequate health literacy (score &gt;67 of 100), and higher scores were not correlated with higher education. Almost all achieved perfect numeracy scores (&gt;86%); numeracy was not associated with outcomes. After adjusting for immigration, education, and income, higher reading comprehension scores (tertile 3) compared with lower scores (tertile 1) were significantly associated with lower risk of first relapse (hazard ratio 0.67, 95% confidence interval [CI] 0.48-0.94, P trend = .02), lower odds of frequently relapsing disease (odds ratio [OR] 0.38, 95% CI 0.21-0.70, P trend = .002), lower relapse rate (rate ratio 0.77, 95% CI 0.73-0.80, P trend &lt; .001), and higher odds of complete remission after both initial steroids and cyclophosphamide (OR 2.07, 95% CI 1.36-3.16, P trend = .003; OR 5.97, 95% CI 2.42-14.7, P trend &lt; .001).Lower parental health literacy, specifically reading comprehension, is associated with higher relapse rates among children with nephrotic syndrome and fewer achieving complete remission. This underscores the importance of assessing and targeting health literacy for chronic management of childhood-onset diseases.</t>
+          <t>The purpose of this study is to examine item equivalence and score comparability of the Progress in International Reading Literacy Study (PIRLS) 2011for the Canadian French and English language groups. Two methods of differential item functioning were conducted to examine item equivalence across thirteen test booklets designed to assess reading literacy in early years of schooling. Four bilingual reviewers with expertise in reading literacy conducted independent, linguistic and cultural reviews to identify both the degree of item equivalence and potential sources of differences between language versions of released items. Results indicate that an average of 25% of items per booklet function differently at the item level. Reviews by experts indicate differences between the two language versions on some items flagged as displaying differential item function (DIF). Some of these were identified to have linguistic differences pointing to differential difficulty levels in the two language versions.</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>['Karlota Borges', 'Cathryn Sibbald', 'Neesha Hussain‐Shamsy', 'Jovanka Vasilevska‐Ristovska', 'Tonny Banh', 'Viral Patel', 'Josefina Brooke', 'Monica Piekut', 'Michele Reddon', 'Kimberly Aitken-Menezes', 'Ashley McNaughton', 'Rachel Pearl', 'Valérie S. Langlois', 'Seetha Radhakrishnan', 'Christoph Licht', 'Tino D. Piscione', 'Leo Levin', 'Damien Noone', 'Diane Hébert', 'Rulan S. Parekh']</t>
+          <t>['Shawna Goodrich', 'Kadriye Ercikan']</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>[['Institute for Clinical Evaluative Sciences', 'https://ror.org/05p6rhy72'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['Institute for Clinical Evaluative Sciences', 'https://ror.org/05p6rhy72'], ['Institute for Clinical Evaluative Sciences', 'https://ror.org/05p6rhy72'], ['Institute for Clinical Evaluative Sciences', 'https://ror.org/05p6rhy72'], ['Institute for Clinical Evaluative Sciences', 'https://ror.org/05p6rhy72'], ['Pediatric Nephrology of Alabama', 'https://ror.org/00zsny525'], ['Pediatric Nephrology of Alabama', 'https://ror.org/00zsny525'], ['Pediatric Nephrology of Alabama', 'https://ror.org/00zsny525'], ['Pediatric Nephrology of Alabama', 'https://ror.org/00zsny525'], ['Pediatric Nephrology of Alabama', 'https://ror.org/00zsny525'], ['Institute for Clinical Evaluative Sciences', 'https://ror.org/05p6rhy72'], ['Pediatric Nephrology of Alabama', 'https://ror.org/00zsny525'], ['Brampton Civic Hospital', 'https://ror.org/01q9kjc87'], ['William Osler Health System', 'https://ror.org/03d1xjg58'], ['Pediatric Nephrology of Alabama', 'https://ror.org/00zsny525'], ['Institute for Clinical Evaluative Sciences', 'https://ror.org/05p6rhy72'], ['Pediatric Nephrology of Alabama', 'https://ror.org/00zsny525'], ['Hospital for Sick Children', 'https://ror.org/057q4rt57'], ['Institute for Clinical Evaluative Sciences', 'https://ror.org/05p6rhy72'], ['Pediatric Nephrology of Alabama', 'https://ror.org/00zsny525'], ['Institute for Clinical Evaluative Sciences', 'https://ror.org/05p6rhy72'], ['Pediatric Nephrology of Alabama', 'https://ror.org/00zsny525'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['Institute for Clinical Evaluative Sciences', 'https://ror.org/05p6rhy72'], ['Pediatric Nephrology of Alabama', 'https://ror.org/00zsny525'], ['Institute for Clinical Evaluative Sciences', 'https://ror.org/05p6rhy72'], ['Pediatric Nephrology of Alabama', 'https://ror.org/00zsny525'], ['Institute for Clinical Evaluative Sciences', 'https://ror.org/05p6rhy72'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['Pediatric Nephrology of Alabama', 'https://ror.org/00zsny525'], ['University Health Network', 'https://ror.org/042xt5161'], ['Public Health Ontario', 'https://ror.org/025z8ah66']]</t>
+          <t>[['Department of National Defence', 'https://ror.org/035rreb34'], ['Educational Testing Service', 'https://ror.org/03b5q4637']]</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="K76" t="b">
         <v>1</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1542/peds.2016-1961</t>
+          <t>https://doi.org/10.3389/feduc.2019.00120</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2890722669</t>
+          <t>https://openalex.org/W3035439260</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://doi.org/10.7870/cjcmh-2018-002</t>
+          <t>https://doi.org/10.1177/2047173420927665</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Improving Mental Health Literacy in Post-Secondary Students: Field Testing the Feasibility and Potential Outcomes of a Peer-Led Approach</t>
+          <t>An assessment of personal financial literacy teaching and learning in Ontario high schools</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Transitions (2nd edition) is an evidence-based life-skills resource designed to help post-secondary students transition from high school to college or university. This study was an on-campus evaluation of peer-led seminars of the mental health content from Transitions. A cross-sectional survey was conducted to assess the mental health literacy of three groups of students: master trainers, student trainers, and seminar participants. Post-seminar, there were significant improvements in mental health knowledge and help-seeking, two key components of participants’ mental health literacy. This peer-led approach is a feasible option with the potential to improve student mental health literacy within a short time frame.</t>
+          <t>The purpose of the study was to examine the experiences of current high school students and teachers in Ontario regarding their experiences with personal financial curriculum and teaching at the secondary level, and to identify the ways in which this important educational experience may have helped prepare students to become financially literate. We considered this overarching issue using a transdisciplinary lens from the perspective of the three stakeholder groups. Using a case study research design, the first of its kind in Ontario or Canada on this topic, We utilized interviews and artifacts to uncover student and teacher experiential data across three high schools in southeastern Ontario. The major findings were that current students and teachers perceived curriculum and teaching experiences as seriously lacking in effectively preparing them to be financially literate, and that a fundamental reorientation around transdisciplinary, student-led learning was key to transforming such learning into a more meaningful and valuable educational experience. With mandatory, properly supported, student-oriented (transdisciplinary) instruction, the potential exists for more effective and valuable learning, resulting in better equipped high school students who were properly prepared to successfully navigate financial issues and the path ahead.</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>['Chris Gilham', 'Erin L. Austen', 'Yifeng Wei', 'Stan Kutcher']</t>
+          <t>['Murdoch Neil Matheson', 'Christopher DeLuca', 'Ian Matheson']</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>[['St. Francis Xavier University', 'https://ror.org/01wcaxs37'], ['Dalhousie University', 'https://ror.org/01e6qks80'], ['Izaak Walton Killam Health Centre', 'https://ror.org/0064zg438'], ['Bridge University', 'https://ror.org/00cbm0437'], ['Bridge University', 'https://ror.org/00cbm0437'], ['Dalhousie University', 'https://ror.org/01e6qks80'], ['St. Francis Xavier University', 'https://ror.org/01wcaxs37'], ['Izaak Walton Killam Health Centre', 'https://ror.org/0064zg438'], ['St. Francis Xavier University', 'https://ror.org/01wcaxs37'], ['Dalhousie University', 'https://ror.org/01e6qks80'], ['Bridge University', 'https://ror.org/00cbm0437'], ['Izaak Walton Killam Health Centre', 'https://ror.org/0064zg438'], ['Dalhousie University', 'https://ror.org/01e6qks80'], ['Bridge University', 'https://ror.org/00cbm0437'], ['St. Francis Xavier University', 'https://ror.org/01wcaxs37'], ['Izaak Walton Killam Health Centre', 'https://ror.org/0064zg438']]</t>
+          <t>[["Queen's University", 'https://ror.org/02y72wh86'], ["Queen's University", 'https://ror.org/02y72wh86'], ["Queen's University", 'https://ror.org/02y72wh86']]</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="K77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>https://doi.org/10.7870/cjcmh-2018-002</t>
+          <t>https://doi.org/10.1177/2047173420927665</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2737442553</t>
+          <t>https://openalex.org/W2983457005</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3138/cmlr.3665</t>
+          <t>https://doi.org/10.1080/02640414.2019.1689076</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Literacy Outcomes of a Chinese/English Bilingual Program in Ontario</t>
+          <t>Canadian Assessment of Physical Literacy in grades 7-9 (12-16 years): Preliminary validity and descriptive results</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>This study examined the performance of Mandarin-speaking students in a K–Grade 4 50/50 Chinese/English bilingual program. The program was intended to facilitate students’ learning of English and their adjustment to English-medium instruction within the school context. The bilingual-program students were compared to students from Mandarin-speaking backgrounds whose school instruction was conducted totally in English but who attended a weekly 2.5-hour Chinese language class conducted outside of the regular school day through the International Languages Program funded by the Ontario government. Students’ abilities in phonological awareness, vocabulary knowledge, morphological awareness, and word reading were measured. Results showed that students in the bilingual program who received less English instruction overall performed comparably in all English measures to their peers in the English-only programs. Some differences in favour of the bilingual-program students were observed in Chinese language and literacy measures, specifically in character recognition. Students in the bilingual program performed above grade norms on standardized measures of English literacy skills and in the Grade 3 provincial standardized testing of English reading and writing abilities.</t>
+          <t>Joel Blancharda , Nadine Van Wykb, Emily Ertela, Anastasia Alpousa &amp; Patricia E. Longmuir*aca Healthy Active Living and Obesity Research Group, Children's Hospital of Eastern Ontario Research Institute, Ottawa, Canadab Department of Health and Physical Education, Mount Royal University, Calgary, Canadac Faculty of Medicine, University of Ottawa, Ottawa, Canada</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>['Poh Wee Koh', 'Xi Chen', 'James Cummins', 'Jia Li']</t>
+          <t>['Joël Blanchard', 'Nadine Van Wyk', 'Emily Ertel', 'Anastasia Alpous', 'Patricia E. Longmuir']</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['Mount Royal University', 'https://ror.org/04evsam41'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Ottawa', 'https://ror.org/03c4mmv16']]</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="K78" t="b">
         <v>0</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3138/cmlr.3665</t>
+          <t>https://doi.org/10.1080/02640414.2019.1689076</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2895270365</t>
+          <t>https://openalex.org/W2990953305</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1186/s12889-018-5896-5</t>
+          <t>https://doi.org/10.1177/0017896919889647</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Cardiorespiratory fitness is associated with physical literacy in a large sample of Canadian children aged 8 to 12 years</t>
+          <t>Health-promoting skills for children: Evaluating the influence of a media literacy and food marketing intervention</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2018</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>cc-by</t>
-        </is>
-      </c>
+        <v>2019</v>
+      </c>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>The associations between cardiorespiratory fitness (CRF) and physical literacy in children are largely unknown. The aim of this study was to assess the relationships between CRF, measured using the 20-m shuttle run test (20mSRT), and components of physical literacy among Canadian children aged 8-12 years.A total of 9393 (49.9% girls) children, with a mean (SD) age of 10.1 (±1.2) years, from a cross-sectional surveillance study were included for this analysis. The SRT was evaluated using a standardized 15 m or 20 m protocol. All 15 m SRTs were converted to 20mSRT values using a standardized formula. The four domains of physical literacy (Physical Competence, Daily Behaviour, Motivation and Confidence, and Knowledge and Understanding) were measured using the Canadian Assessment of Physical Literacy. Tertiles were identified for 20mSRT laps, representing low, medium, and high CRF for each age and gender group. Cohen's d was used to calculate the effect size between the low and high CRF groups.CRF was strongly and favourably associated with all components of physical literacy among school-aged Canadian children. The effect size between low and high CRF tertile groups was large for the Physical Competence domain (Cohen's d range: 1.11-1.94) across age and gender groups, followed by moderate to large effect sizes for Motivation and Confidence (Cohen's d range: 0.54-1.18), small to moderate effect sizes for Daily Behaviour (Cohen's d range: 0.25-0.81), and marginal to moderate effect sizes for Knowledge and Understanding (Cohen's d range: 0.08-0.70).This study identified strong favourable associations between CRF and physical literacy and its constituent components in children aged 8-12 years. Future research should investigate the sensitivity and specificity of the 20mSRT in screening those with low physical literacy levels.</t>
+          <t>Background: Media literacy skills are needed to navigate high levels of food marketing promoting the consumption of unhealthy foods. Health-promoting media literacy education encourages children to use analytical skills to critically examine media messages in order to make informed health choices. Objective: To evaluate the influence of media literacy lesson plans for children focusing on critical knowledge around food marketing. Design: Evidence-based Media Literacy &amp;amp; Food Marketing lesson plans, designed for grades 3 to 6 (ages 8–11) and 6 to 9 (ages 11–14), were developed to fill the knowledge gaps children demonstrated with respect to assessing of the healthfulness of packaged foods. Setting: Two public schools in Calgary, Alberta, Canada. Methods: An educational intervention with pre-test/post-test design. The lesson plans were used by teachers in the classroom, and a questionnaire was created to assess children’s pre- and post-lesson levels of critical knowledge about food marketing. Results: In total, 71 students from grades 5, 7, 8 and 9 participated. Qualitative analysis of responses showed increased analysis and evaluation skills when it came to understanding of food marketing appeals, and increased ability to assess the nutritional content of packaged foods. Conclusion: This study is novel in its use of media literacy as a framework for understanding food packaging appeals. It highlights the importance of examining procedural and interpretive knowledge in the evaluation of critical media literacy skills around food. This allows researchers, educators and health practitioners to better gauge how children are able to apply nutrition information in different contexts to make informed food choices.</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>['Justin J. Lang', 'Jean‐Philippe Chaput', 'Patricia E. Longmuir', 'Joel D. Barnes', 'Kevin Belanger', 'Grant R. Tomkinson', 'Kristal D. Anderson', 'Brenda Bruner', 'Jennifer L. Copeland', 'Melanie Gregg', 'Nathan Hall', 'Angela M. Kolen', 'Kirstin N. Lane', 'Barbi Law', 'Dany J. MacDonald', 'Luc J. Martin', 'Travis J. Saunders', 'Dwayne P. Sheehan', 'Michelle Stone', 'Sarah J. Woodruff', 'Mark S. Tremblay']</t>
+          <t>['Emily Truman', 'Charlene Elliott']</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>[['Agricultural Research Institute of Ontario', 'https://ror.org/011n4tk56'], ['Agricultural Research Institute of Ontario', 'https://ror.org/011n4tk56'], ['Agricultural Research Institute of Ontario', 'https://ror.org/011n4tk56'], ['Agricultural Research Institute of Ontario', 'https://ror.org/011n4tk56'], ['Agricultural Research Institute of Ontario', 'https://ror.org/011n4tk56'], ['University of South Australia', 'https://ror.org/01p93h210'], ['University of North Dakota', 'https://ror.org/04a5szx83'], ['Camosun College', 'https://ror.org/02v6aqf52'], ['Nipissing University', 'https://ror.org/05k14ba46'], ['University of Lethbridge', 'https://ror.org/044j76961'], ['University of Winnipeg', 'https://ror.org/02gdzyx04'], ['University of Winnipeg', 'https://ror.org/02gdzyx04'], ['St. Francis Xavier University', 'https://ror.org/01wcaxs37'], ['Camosun College', 'https://ror.org/02v6aqf52'], ['Nipissing University', 'https://ror.org/05k14ba46'], ['University of Prince Edward Island', 'https://ror.org/02xh9x144'], ["Queen's University", 'https://ror.org/02y72wh86'], ['University of Prince Edward Island', 'https://ror.org/02xh9x144'], ['Mount Royal University', 'https://ror.org/04evsam41'], ['Dalhousie University', 'https://ror.org/01e6qks80'], ['University of Windsor', 'https://ror.org/01gw3d370'], ['Agricultural Research Institute of Ontario', 'https://ror.org/011n4tk56']]</t>
+          <t>[['University of Calgary', 'https://ror.org/03yjb2x39'], ['University of Calgary', 'https://ror.org/03yjb2x39']]</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="K79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1186/s12889-018-5896-5</t>
+          <t>https://doi.org/10.1177/0017896919889647</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2462681362</t>
+          <t>https://openalex.org/W3039959558</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1111/jppi.12160</t>
+          <t>https://doi.org/10.1177/0265532220930348</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>An Early Literacy Program for Young Children with Down Syndrome: Changes Observed over One Year</t>
+          <t>Change in home language environment and English literacy achievement over time: A multi-group latent growth curve modeling investigation</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Although much individual variability exists, most persons with Down syndrome (DS) experience marked expressive language delays and challenges with speech production, hearing, and verbal memory that may negatively affect literacy development. There is, however, a paucity of research with respect to early intervention literacy programs with this population. The authors describe an early intervention literacy program that used a hybrid approach to reading instruction combining whole-word (i.e., visual) and analytic (i.e., phonic or sound-based) reading strategies. They also detail the changes observed in the literacy and language abilities of the participants over 1 year. The participants were 15 English speaking Canadian students with DS aged 3–6 years (M age 4;11, pretreatment) who took part in a 45-week program. Weekly individual sessions with a certified teacher were augmented by regular homework. Each student's literacy and language abilities were assessed immediately pretreatment and posttreatment. Measures of letter name identification, letter sound identification, print concepts, and identification of taught sight words showed statistically significant changes. Letter name identification, letter sound identification, and number of sight words read pretreatment were all positively and significantly correlated with gains in word identification. There was also a clear difference regarding how many new sight words students were able to read posttreatment depending on whether they used abstract symbols to communicate (i.e., unprompted spoken words or signs) pretreatment. The authors note that this study provides support for literacy interventions that combine phonological awareness, word analysis, sight word training, and shared book reading with children with DS as young as 3 years of age with varying levels of language development.</t>
+          <t>In most studies investigating the educational outcomes of linguistically diverse students, variables that identify this population have been considered as static. In reality, owing to the dynamic nature of students and their families, students’ home language environments change over time. This study aims to understand how elementary school students’ home language environments change over time, and how longitudinal patterns of English literacy achievement across grades 3, 6, and 10 differ among students with various home language shift patterns in Ontario, Canada. The longitudinal cohort data of 89,609 students between grades 3 and 10 from the provincial assessments were analyzed for changes in their home language environment. A subsample of 18,000 students was used to examine different patterns of relative literacy performance over time and their associations with immigration background and early intervention programming using multi-group latent growth curve modeling. Our findings suggest a strong movement toward an English-dominant home language environment among multilingual students; yet, students whose homes remained as multilingual demonstrated the highest literacy achievement in the early grade as well as the highest improvement in relative performance over time. The paper draws implications for promoting students’ home language, instilling a positive view of multilingual competence.</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>['Paola Colozzo', 'Leah McKeil', 'Jill Petersen', 'Amanda N. Szabo‐Reed']</t>
+          <t>['Hyun-Ah Kim', 'Christine Barron', 'Jeanne Sinclair', 'Eunice Eunhee Jang']</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>[['University of British Columbia', 'https://ror.org/03rmrcq20'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['Down Syndrome Research Foundation', 'https://ror.org/04xayvx70'], ['Down Syndrome Research Foundation', 'https://ror.org/04xayvx70']]</t>
+          <t>[['University of Toronto', 'https://ror.org/03dbr7087'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['University of the Incarnate Word', 'https://ror.org/044a5dk27'], ['University of Toronto', 'https://ror.org/03dbr7087']]</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K80" t="b">
         <v>0</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1111/jppi.12160</t>
+          <t>https://doi.org/10.1177/0265532220930348</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2800995841</t>
+          <t>https://openalex.org/W3133989721</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://doi.org/10.17269/s41997-018-0048-3</t>
+          <t>https://doi.org/10.1139/apnm-2020-0957</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Assessing health literacy among older adults living in subsidized housing: a cross-sectional study</t>
+          <t>Characterization of physical literacy in children with chronic medical conditions compared with healthy controls: a cross-sectional study</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>To determine the physical literacy, defined as the capability for a physically active lifestyle, of children with medical conditions compared with healthy peers, this multicenter cross-sectional study recruited children with medical conditions from cardiology, neurology (including concussion), rheumatology, mental health, respirology, oncology, hematology, and rehabilitation (including cerebral palsy) clinics. Participants aged 8-12 years (N = 130; mean age: 10.0 ± 1.44 years; 44% female) were randomly matched to 3 healthy peers from a normative database, based on age, gender, and month of testing. Total physical literacy was assessed by the Canadian Assessment of Physical Literacy, a validated assessment of physical literacy measuring physical competence, daily behaviour, knowledge/understanding, and motivation/confidence. Total physical literacy mean scores (/100) did not differ (t(498) = -0.67; p = 0.44) between participants (61.0 ± 14.2) and matched healthy peers (62.0 ± 10.7). Children with medical conditions had lower mean physical competence scores (/30; -6.5 [-7.44 to -5.51]; p &lt; 0.001) but higher mean motivation/confidence scores (/30; 2.6 [1.67 to 3.63]; p &lt; 0.001). Mean daily behaviour and knowledge/understanding scores did not differ from matches (/30; 1.8 [0.26 to 3.33]; p = 0.02;/10; -0.04 [-0.38 to 0.30]; p = 0.81; respectively). Children with medical conditions are motivated to be physically active but demonstrate impaired movement skills and fitness, suggesting the need for targeted interventions to improve their physical competence. Novelty: Physical literacy in children with diverse chronic medical conditions is similar to healthy peers. Children with medical conditions have lower physical competence than healthy peers, but higher motivation and confidence. Physical competence (motor skill, fitness) interventions, rather than motivation or education, are needed for these youth.</t>
+        </is>
+      </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>['Gina Agarwal', 'Kendra Habing', 'Melissa Pirrie', 'Ric Angeles', 'Francine Marzanek', 'Jenna Parascandalo']</t>
+          <t>['Jeffrey Do', 'Angelica Blais', 'Brian M. Feldman', 'Leonardo R. Brandão', 'Jane Lougheed', 'Daniela Pohl', 'Robert J. Klaassen', 'Donna L. Johnston', 'Denise De Laat', 'Johannes Roth', 'Sherri L. Katz', 'Anna McCormick', 'F. Virginia Wright', 'Gail Macartney', 'Hugh J. McMillan', 'Sunita Venkateswaran', 'Erick Sell', 'Asif Doja', 'Katherine Matheson', 'Addo Boafo', 'Patricia E. Longmuir']</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>[['Impact', 'https://ror.org/05d9dsr70'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['McMaster University', 'https://ror.org/02fa3aq29'], ['McMaster University', 'https://ror.org/02fa3aq29']]</t>
+          <t>[['University of Ottawa', 'https://ror.org/03c4mmv16'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['Hospital for Sick Children', 'https://ror.org/057q4rt57'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['Hospital for Sick Children', 'https://ror.org/057q4rt57'], ['University of Toronto', 'https://ror.org/03dbr7087'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ['Holland Bloorview Kids Rehabilitation Hospital', 'https://ror.org/03qea8398'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ['University of Prince Edward Island', 'https://ror.org/02xh9x144'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Ottawa', 'https://ror.org/03c4mmv16']]</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="K81" t="b">
         <v>0</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>https://doi.org/10.17269/s41997-018-0048-3</t>
+          <t>https://doi.org/10.1139/apnm-2020-0957</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2894683557</t>
+          <t>https://openalex.org/W3011227050</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1186/s12889-018-5899-2</t>
+          <t>https://doi.org/10.1186/s40536-020-00080-3</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Refining the Canadian Assessment of Physical Literacy based on theory and factor analyses</t>
+          <t>Are large surveys of adult literacy skills as comparable over time as we think?</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -4466,52 +4490,52 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>The Canadian Assessment of Physical Literacy (CAPL) is a 25-indicator assessment tool comprising four domains of physical literacy: (1) Physical Competence, (2) Daily Behaviour, (3) Motivation and Confidence, and (4) Knowledge and Understanding. The purpose of this study was to re-examine the factor structure of CAPL scores and the relative weight of each domain for an overall physical literacy factor. Our goal was to maximize content representation, and reduce construct irrelevant variance and participant burden, to inform the development of CAPL-2 (a revised, shorter, and theoretically stronger version of CAPL).Canadian children (n = 10,034; Mage = 10.6, SD = 1.2; 50.1% girls) completed CAPL testing at one time point. Confirmatory factor analysis was used.Based on weak factor loadings (λs &lt; 0.32) and conceptual alignment, we removed body mass index, waist circumference, sit-and-reach flexibility, and grip strength as indicators of Physical Competence. Based on the factor loading (λ &lt; 0.35) and conceptual alignment, we removed screen time as an indicator of Daily Behaviour. To reduce redundancy, we removed children's activity compared to other children as an indicator of Motivation and Confidence. Based on low factor loadings (λs &lt; 0.35) and conceptual alignment, we removed knowledge of screen time guidelines, what it means to be healthy, how to improve fitness, activity preferences, and physical activity safety gear indicators from the Knowledge and Understanding domain. The final refined CAPL model was comprised of 14 indicators, and the four-factor correlated model fit the data well (r ranged from 0.08 to 0.76), albeit with an unexpected cross-loading from Daily Behaviour to knowledge of physical activity guidelines (mean- and variance-adjusted weighted least square [WLSMV] χ2(70) = 1221.29, p &lt; 0.001, Comparative Fit Index [CFI] = 0.947, root mean square error of approximation [RMSEA] = 0.041[0.039, 0.043]). Finally, our higher-order model with Physical Literacy as a factor with indicators of Physical Competence (λ = 0.68), Daily Behaviour (λ = 0.91), Motivation and Confidence (λ = 0.80), and Knowledge and Understanding (λ = 0.21) fit the data well.The scores from the revised and much shorter 14-indicator model of CAPL can be used to assess the four correlated domains of physical literacy and/or a higher-order aggregate physical literacy factor. The results of this investigation will inform the development of CAPL-2.</t>
+          <t>Abstract Recent literature shows that younger cohorts have lower levels of literacy ceteris paribus in Canada, the United States, Norway and other developed countries. Very few explanations are provided to justify the existence of this negative cohort effect. Yet this decline has serious implications for the economy, education system and society. In this paper, we focus on Canada and replicate the results published in the literature using the same methodology (synthetic cohorts). We use the same data from surveys of adult skills, namely the International Adult Literacy Survey (IALS), the Adult Literacy and Life Skills Survey (ALL) and the Survey of Adult Skills, a product of the OECD Programme for the International Assessment of Adult Competencies (PIAAC). Second, we conduct further analyses to better understand the effect of time on adults’ literacy skills. We then show that age has a negative effect on the literacy score, but also that a significant “period” effect (or rather a “survey” effect) can only be explained by a change in the instrument used to measure literacy skills from one survey to another. This article reveals that the negative cohort effect mentioned in the literature may be fallacious as it is exacerbated when the control for measuring instrument distortions is omitted. This paper contributes to advancing knowledge about the effect that age and cohort has on adult literacy levels in Canada. The results weaken the idea of a clear negative cohort effect; much of this effect would in fact be caused by a non-comparable methodology that systematically assigned individuals lower scores in the most recent survey cycles. These findings are important because they highlight the limitations of analyses that can be done with the synthetic cohort method using cross-sectional surveys on adult literacy skills not only in Canada, but also in all other countries where these surveys have been conducted.</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>['Katie E. Gunnell', 'Patricia E. Longmuir', 'Joel D. Barnes', 'Kevin Belanger', 'Mark S. Tremblay']</t>
+          <t>['Samuel Vézina', 'Alain Bélanger']</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>[["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27']]</t>
+          <t>[['Institut National de la Recherche Scientifique', 'https://ror.org/04td37d32'], ['International Institute for Applied Systems Analysis', 'https://ror.org/02wfhk785'], ['Institut National de la Recherche Scientifique', 'https://ror.org/04td37d32']]</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="K82" t="b">
         <v>1</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1186/s12889-018-5899-2</t>
+          <t>https://doi.org/10.1186/s40536-020-00080-3</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2725011375</t>
+          <t>https://openalex.org/W3035683435</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1186/s12955-017-0716-7</t>
+          <t>https://doi.org/10.1080/13811118.2020.1769783</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>The relationship between health literacy and quality of life among frequent users of health care services: a cross-sectional study</t>
+          <t>Depression and Suicide Literacy among Canadian Sexual and Gender Minorities</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -4520,722 +4544,710 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Although health literacy and quality of life are important concepts in health care, the link between them is unclear, especially for a population of frequent users of health care services with chronic diseases. Low health literacy is a common problem that has been linked to several negative health outcomes. Quality of life is an important health outcome in patient-centered care. Frequent users of health care services are a vulnerable population that deserves attention due to high costs and negative outcomes such as lower quality of life and higher mortality. The objective of this study was to examine the relationship between health literacy and the physical and mental components of quality of life among frequent users of health care services with chronic diseases. This study presents the cross-sectional analysis of data collected through the V1SAGES project, a randomized controlled trial on the effectiveness of a case management intervention in primary care in Quebec, Canada. Participants (n = 247) were frequent users of health care services presenting at least one chronic condition. Health literacy was measured by the Newest Vital Sign (NVS), and the physical and mental components of quality of life were evaluated by the Short Form Health Survey Version 2 (SF-12v2). The association between health literacy (independent variable) and the physical and mental components of quality of life was examined using biserial correlation. No association was found between health literacy and quality of life (physical component: r = 0.108, ρ = 0.11; mental component: r = 0.147, ρ = 0.15). This study suggests that there is no relationship between health literacy and the physical and mental components of quality of life among frequent users of health care services. NCT01719991 . Registered October 25, 2012.</t>
+          <t>The purpose of this study was to examine and compare depression and suicide literacy among Canadian sexual and gender minorities (SGM). Online surveys comprised of the 22-item depression literacy scale (D-LIT) and the 12-item literacy of suicide scale (LOSS) were completed by 2,778 individuals identifying as SGM. Relationships between depression and suicide literacy and demographic characteristics were evaluated using multivariable linear regression. Overall, SGM correctly answered 71.3% of the questions from the D-LIT and 76.5% of the LOSS. D-LIT scores were significantly lower among cisgender men and D-LIT and LOSS scores were lower among transgender women when compared to cisgender women. LOSS and D-LIT scores were significantly lower among SGM without a university degree (compared to those with a university degree) and among SGM from ethnic minority groups (compared to White SGM). D-LIT scores, but not LOSS scores, were significantly lower among Indigenous SGM compared to White SGM. The findings provide evidence of differences in suicide and depression literacy between SGM subgroups along multiple social axes. Interventions to increase depression and suicide literacy should be prioritized as part of a mental health promotion strategy for SGM, targeting subgroups with lower literacy levels, including cisgender men, transgender women, Indigenous people, racialized minorities, and those without a university degree.</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>['Éva Marjorie Couture', 'Maud‐Christine Chouinard', 'Martin Fortin', 'Catherine Hudon']</t>
+          <t>['Olivier Ferlatte', 'Travis Salway', 'John L. Oliffe', 'Simon Rice', 'Mark Gilbert', 'Ingrid Young', 'Lisa McDaid', 'John S. Ogrodniczuk', 'Rod Knight']</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>[['Université de Sherbrooke', 'https://ror.org/00kybxq39'], ['Université du Québec à Chicoutimi', 'https://ror.org/00y3hzd62'], ['Université de Sherbrooke', 'https://ror.org/00kybxq39'], ['Centre Hospitalier Universitaire de Sherbrooke', 'https://ror.org/020r51985']]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>68</v>
+        <v>8</v>
       </c>
       <c r="K83" t="b">
         <v>1</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1186/s12955-017-0716-7</t>
+          <t>https://doi.org/10.1080/13811118.2020.1769783</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2895497822</t>
+          <t>https://openalex.org/W3134845393</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1186/s12889-018-5897-4</t>
+          <t>https://doi.org/10.1016/j.arth.2021.02.075</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>The relationship between physical literacy scores and adherence to Canadian physical activity and sedentary behaviour guidelines</t>
+          <t>Musculoskeletal Health Literacy is Associated With Outcome and Satisfaction of Total Knee Arthroplasty</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2018</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>cc-by</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Physical literacy is an emerging construct in children's health promotion, and may impact their lifelong physical activity habits. However, recent data reveal that only a small portion of Canadian children are regularly physically active and/or meet sedentary behaviour guidelines. To our knowledge, no study has investigated the association between physical literacy and movement behaviour guidelines. Therefore, the purpose of this study was to examine the relationship between physical literacy scores in Canadian children who meet or do not meet physical activity and sedentary behaviour guidelines.Children (n = 2956; 56.6% girls) aged 8-12 years from 10 Canadian cities had their physical literacy levels measured using the Canadian Assessment of Physical Literacy, which consists of four domains (Physical Competence; Daily Behaviour; Knowledge and Understanding; and Motivation and Confidence) that are aggregated to provide a composite physical literacy score. Physical activity levels were measured by pedometers, and sedentary behaviour was assessed through self-report questionnaire. Analyses were conducted separately for each guideline, comparing participants meeting versus those not meeting the guidelines. Comparisons were performed using MANOVA and logistic regression to control for age, gender, and seasonality.Participants meeting physical activity guidelines or sedentary behaviour guidelines had higher physical literacy domain scores for Physical Competence and for Motivation and Confidence compared to those not meeting either guideline (both p &lt; 0.0001). Participants had increased odds of meeting physical activity guidelines and sedentary behaviour guidelines if they met the minimum recommended level of the Physical Competence and Motivation and Confidence domains. Significant age (OR 0.9; 95% CI: 0.8, 0.9), gender (OR 0.4; 95% CI: 0.3, 0.5) and seasonality effects (OR 1.6; 95% CI: 1.2, 2.2 spring and OR 1.7; 95% CI: 1.2, 2.5 summer, reference winter) were seen for physical activity guidelines, and age (OR 0.8; 95% CI: 0.7, 0.8) and gender effects (OR 1.7; 95% CI: 1.4, 2.0) for sedentary behaviour guidelines. Knowledge and Understanding of physical activity principles was not related to guideline adherence in either model.These cross-sectional findings demonstrate important associations between physical literacy and guideline adherence for physical activity and sedentary behaviour. Future research should explore the causality of these associations.</t>
-        </is>
-      </c>
+        <v>2021</v>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
-          <t>['Kevin Belanger', 'Joel D. Barnes', 'Patricia E. Longmuir', 'Kristal D. Anderson', 'Brenda Bruner', 'Jennifer L. Copeland', 'Melanie Gregg', 'Nathan Hall', 'Angela M. Kolen', 'Kirstin N. Lane', 'Barbi Law', 'Dany J. MacDonald', 'Luc J. Martin', 'Travis J. Saunders', 'Dwayne P. Sheehan', 'Michelle Stone', 'Sarah J. Woodruff', 'Mark S. Tremblay']</t>
+          <t>['Arvind S. Narayanan', 'Kurt E. Stoll', 'Lincoln F. Pratson', 'Feng‐Chang Lin', 'Christopher W. Olcott', 'Daniel J. Del Gaizo']</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>[["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['Camosun College', 'https://ror.org/02v6aqf52'], ['Nipissing University', 'https://ror.org/05k14ba46'], ['University of Lethbridge', 'https://ror.org/044j76961'], ['University of Winnipeg', 'https://ror.org/02gdzyx04'], ['University of Winnipeg', 'https://ror.org/02gdzyx04'], ['St. Francis Xavier University', 'https://ror.org/01wcaxs37'], ['Camosun College', 'https://ror.org/02v6aqf52'], ['Nipissing University', 'https://ror.org/05k14ba46'], ['University of Prince Edward Island', 'https://ror.org/02xh9x144'], ["Queen's University", 'https://ror.org/02y72wh86'], ['University of Prince Edward Island', 'https://ror.org/02xh9x144'], ['Mount Royal University', 'https://ror.org/04evsam41'], ['Dalhousie University', 'https://ror.org/01e6qks80'], ['University of Windsor', 'https://ror.org/01gw3d370'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27']]</t>
+          <t>[['University of North Carolina at Chapel Hill', 'https://ror.org/0130frc33'], ['University of North Carolina at Chapel Hill', 'https://ror.org/0130frc33'], ['University of North Carolina at Chapel Hill', 'https://ror.org/0130frc33'], ['University of North Carolina at Chapel Hill', 'https://ror.org/0130frc33'], ['University of North Carolina at Chapel Hill', 'https://ror.org/0130frc33'], ['University of North Carolina at Chapel Hill', 'https://ror.org/0130frc33']]</t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>137</v>
+        <v>28</v>
       </c>
       <c r="K84" t="b">
         <v>1</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1186/s12889-018-5897-4</t>
+          <t>https://doi.org/10.1016/j.arth.2021.02.075</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://openalex.org/W3110689777</t>
+          <t>https://openalex.org/W4360620777</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/02660830.2020.1855870</t>
+          <t>https://doi.org/10.33137/utmj.v100i1.39410</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>The automated literacies of e-recruitment and online services</t>
+          <t>Health literacy awareness among Canadian surgeons</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2020</v>
-      </c>
-      <c r="F85" t="inlineStr"/>
+        <v>2023</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>cc-by</t>
+        </is>
+      </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Online technologies have entered almost all spheres of life, introducing new challenges to how literacies are theorised, defined and taken up in adult literacy education settings. This process has accelerated during the COVID-19 pandemic and on a global scale, as more services, resources and information move online. An important, if under-studied example of this trend is e-recruitment. Job seekers increasingly rely upon automated platforms to find and apply for jobs, and their fate in these selection processes are often automated. Drawing on data from the German LEO study and ethnographic interviews with job seekers in community-based digital literacy classes in Canada, this article explores how adult job seekers experience e-recruitment platforms, examining promises of efficiency, convenience and fairness in light of embedded inequalities within algorithmic agencies. Located within constructs of digital inequality, new literacy studies and sociomaterial literacies, findings suggest the need to reconfigure skills discourses, literacy measurement projects, and literacies education to account for automated intelligences as new actors in the literacies landscape.</t>
+          <t>Adequate health literacy is essential to navigate the healthcare system and has a major role in peri-operative care and outcomes. Minimal information exists regarding surgeons’ understanding of health literacy, clinical implications, and awareness of universal measures of support. This study assessed Canadian surgeons’ perceptions of patients’ health literacy and their knowledge of available supportive resources. We conducted a cross-sectional study using an electronic survey distributed to surgeons at academic institutions. Data collected included sociodemographics, health literacy knowledge, and practice surrounding the use of supportive measures. Across four Canadian academic institutions (University of Toronto, McMaster University, University of Alberta, and University of Calgary), 35 surgeons from various surgical specialties, including general, plastic, and orthopedic surgery, completed the survey. Approximately 74% of surgeons reported familiarity with the concept “health literacy”, but they used general impressions to estimate their patients’ health literacy levels. Surgeons’ perceptions were that patients who had proficient health literacy represented 50% or less of their practice. However, knowledge of supportive tools for measuring patient health literacy was variable. Surgeons familiar with health literacy spent significantly more time (&amp;gt;15 minutes) counselling patients (38%, p=0.02) and used language at a 10th grade level or less (92%, p=0.04). Common supportive measures included using simple, non-medical terms (97%, n=34), repetition (83%, n=29), and drawing pictures/diagrams (83%, n=29). This study highlights the importance of surgeon awareness of health literacy and how improved awareness may guide patient-surgeon interactions and improve the quality of care.</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>['Suzanne Smythe', 'Anke Grotlüschen', 'Klaus Buddeberg']</t>
+          <t>['Josephine A. D’Abbondanza', 'Mélissa Roy', 'Karen Okrainec', 'Christine B. Novak', 'Herbert P. von Schroeder', 'David R. Urbach', 'Steven J. McCabe']</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>[['Simon Fraser University', 'https://ror.org/0213rcc28'], ['Universität Hamburg', 'https://ror.org/00g30e956'], ['Universität Hamburg', 'https://ror.org/00g30e956']]</t>
+          <t>[['University of Toronto', 'https://ror.org/03dbr7087'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['University of Toronto', 'https://ror.org/03dbr7087']]</t>
         </is>
       </c>
       <c r="J85" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="K85" t="b">
         <v>1</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/02660830.2020.1855870</t>
+          <t>https://doi.org/10.33137/utmj.v100i1.39410</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2916608537</t>
+          <t>https://openalex.org/W4281719045</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1177/1524839919827576</t>
+          <t>https://doi.org/10.1080/09500693.2022.2080887</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Health Literacy Among Canadian Men Experiencing Prostate Cancer</t>
+          <t>Associations between science dispositions and science literacy: a comparison of the United States and Canada</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>The objective was to describe the health literacy of a sample of Canadian men with prostate cancer and explore whether sociodemographic and health factors were related to men’s health literacy scores. A sample of 213 Canadian men ( M age = 68.71 years, SD = 7.44) diagnosed with prostate cancer were recruited from an online prostate cancer support website. The men completed the Health Literacy Questionnaire along with demographic, comorbidity, and prostate cancer treatment–related questions online. Of the 5-point scales, men’s health literacy scores were highest for “Understanding health information enough to know what to do” ( M = 4.04, SD = 0.48) and lowest for “Navigating the health care system” ( M = 3.80, SD = 0.58). Of the 4-point scales, men’s scores were highest for “Feeling understood and supported by health care professionals” ( M = 3.20, SD = 0.52) and lowest for “Having sufficient information to manage my health” ( M = 2.97, SD = 0.46). Regression analyses indicated that level of education was positively associated with health literacy scores, and men without comorbidities had higher health literacy scores. Age and years since diagnosis were unrelated to health literacy. Support in health system navigation and self-management of health may be important targets for intervention.</t>
+          <t>While the United States (U.S.) and Canada share features in their secondary education systems (e.g. proportion of immigrants), these nations have differences (e.g. linguistic ). Given the primacy of Canada over the U.S. vis-à-vis science literacy [as measured by the Programme International for Student Assessment (PISA)], underlying differences in science dispositions and school climate variables could exist. The PISA 2015 science-focused dataset, including 5712 students in 172 schools in the U.S. and 20,058 students in 645 schools in Canada, was modelled via multilevel methods to assess associations among science dispositions (epistemology, enjoyment, interest, instrumental, self-efficacy activities) and science literacy. Associations of school climate variables of instructional leadership, disciplinary climate and teaching support (the latter two in the context of science classes) with the above measures were evaluated. Disciplinary climate was more often associated with science dispositions (as outcome measures) in the U.S., while teaching support was most often associated with these measures for Canada. Disciplinary climate was associated with science literacy (as an outcome measure) in the U.S.; in contrast, no school climate measures were associated with science literacy in Canada. These results support an emphasis on disciplinary climate in U.S. science classrooms, but an emphasis on teaching support in Canadian science classrooms.</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>['Cherisse L. Seaton', 'John L. Oliffe', 'Simon Rice', 'Joan L. Bottorff', 'Steven T. Johnson', 'Susan Gordon', 'Suzanne K. Chambers']</t>
+          <t>['Larry J. Grabau', 'Louis Trudel', 'Xin Ma']</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>[['Kelowna General Hospital', 'https://ror.org/01j25h453'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['Kelowna General Hospital', 'https://ror.org/01j25h453'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['Orygen Youth Health', 'https://ror.org/00ej70p06'], ['The University of Melbourne', 'https://ror.org/01ej9dk98'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['Kelowna General Hospital', 'https://ror.org/01j25h453'], ['Athabasca University', 'https://ror.org/01y3xgc52'], ['Flinders University', 'https://ror.org/01kpzv902'], ['University of Technology Sydney', 'https://ror.org/03f0f6041'], ['Griffith University', 'https://ror.org/02sc3r913']]</t>
+          <t>[['University of Kentucky', 'https://ror.org/02k3smh20'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ['Kentucky Department of Education', 'https://ror.org/01hsff479'], ['University of Kentucky', 'https://ror.org/02k3smh20']]</t>
         </is>
       </c>
       <c r="J86" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K86" t="b">
         <v>0</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1177/1524839919827576</t>
+          <t>https://doi.org/10.1080/09500693.2022.2080887</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://openalex.org/W3193745980</t>
+          <t>https://openalex.org/W4389109305</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/ijerph18168646</t>
+          <t>https://doi.org/10.55016/ojs/ajer.v68i2.71334</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>An Integrated Framework to Conceptualize and Develop the Vancouver Airways Health Literacy Tool (VAHLT)</t>
+          <t>Cognitive Skills of Canadian Educators: An Analysis of PIAAC Data</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>There is currently no comprehensive tool to assess the functional health literacy (HL) skills of chronic airway disease (CAD) patients. The purpose of this article is to describe the development of a new HL measure, the Vancouver Airways Health Literacy Tool (VAHLT). The tool was developed through the following phases: (1) Tool conceptualization, consisting of: (A) a systematic review (SR), (B) focus group sessions with CAD patients to understand barriers and facilitators to CAD management, (C) a survey with key-informants to obtain strategies to mitigate self-management barriers and validate patient-derived topics, and (D) respiratory physicians’ review of the topics; (2) Scenario and item development; and (3) Tool testing and content validation. The SR identified the lack of a valid HL measurement tool for CAD patients. Patients provided an initial shortlist of disease-related self-care topics. Key-informants helped to finalize topics for inclusion. Respiratory physicians and patients contributed to the development of a scenario-based questionnaire, which was refined during three rounds of testing to develop a 44-item instrument comprising nine self-management passages. We highlight the holistic process of integrating information from the literature with knowledge gained from key stakeholders into our tool framework. Our approach to stakeholder engagement may be of interest to researchers developing similar tools, and could facilitate the development and testing of HL-based interventions to ultimately improve patient outcomes and reduce the burden on the healthcare system.</t>
+          <t>The purpose of this study was to conduct national and cross-country analyses to provide insights about educator cognitive skills in literacy, numeracy, and problem-solving within Canada and across nineteen countries using the PIAAC data. MANOVA results of profession differences within Canada demonstrated that educators outperformed other professions in general programs, health and welfare, and services but underperformed the professions in science, mathematics, and computing in all three domains. MANOVA results of educator differences across countries showed that educators in Canada outperformed those in Denmark, Estonia, the Russian Federation, and the United Kingdom in literacy, outperformed the United Kingdom in numeracy, and outperformed Denmark, Estonia, and the United Kingdom in problem-solving. Finally, multiple regression analyses identified statistically significant indicators of Canadian educators’ literacy, numeracy, and problem-solving proficiencies. The results of this study reveal and suggest that the cognitive skills of Canadian educators have the potential to be enhanced. Keywords: teacher cognitive skills, literacy, numeracy, problem-solving in technology-rich environments L'objectif de cette étude était de mener des analyses nationales et internationales afin de fournir des informations sur les compétences cognitives des éducateurs en matière de littératie, de numératie et de résolution de problèmes au Canada et dans dix-neuf pays à l'aide des données de l'enquête PIAAC. Les résultats de l'analyse MANOVA des différences entre les professions au Canada ont démontré que les éducateurs surpassent les autres professions dans les domaines des programmes généraux; de la santé et du bien-être; et des services, mais qu'ils sont moins performants que les autres professions en sciences, en mathématiques et en informatique dans les trois domaines. Les résultats de l'analyse MANOVA des différences entre les éducateurs des différents pays ont montré que les éducateurs du Canada surpassent ceux du Danemark, de l'Estonie, de la Fédération de Russie et du Royaume-Uni en littératie, surpassent ceux du Royaume-Uni en numératie et surpassent ceux du Danemark, de l'Estonie et du Royaume-Uni en résolution de problèmes. Enfin, les analyses de régression multiple ont permis d'identifier des indicateurs statistiquement significatifs des compétences des éducateurs canadiens en matière de littératie, de numératie et de résolution de problèmes. Les résultats de cette étude révèlent et suggèrent que les compétences cognitives des éducateurs canadiens ont le potentiel d'être améliorées. Mots clés : compétences cognitives des enseignants, littératie, numératie, résolution de problèmes dans des environnements riches en technologie</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>['Iraj Poureslami', 'Jacek A. Kopec', 'Noah Tregobov', 'Jessica Shum', 'Richard Sawatzky', 'Richard E. Hohn', 'J. Mark FitzGerald']</t>
+          <t>['Seyma Nur Yildirim Erbasli', 'Ying Cui']</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>[['University of British Columbia', 'https://ror.org/03rmrcq20'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['Western University', 'https://ror.org/02grkyz14'], ['Trinity Western University', 'https://ror.org/01j2kd606'], ['Simon Fraser University', 'https://ror.org/0213rcc28'], ['University of British Columbia', 'https://ror.org/03rmrcq20']]</t>
+          <t>[['University of Alberta', 'https://ror.org/0160cpw27'], ['University of Alberta', 'https://ror.org/0160cpw27']]</t>
         </is>
       </c>
       <c r="J87" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K87" t="b">
         <v>1</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/ijerph18168646</t>
+          <t>https://doi.org/10.55016/ojs/ajer.v68i2.71334</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2991461979</t>
+          <t>https://openalex.org/W4221018637</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3389/fpubh.2019.00346</t>
+          <t>https://doi.org/10.1080/10790268.2021.1963140</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Physical Literacy and Resilience in Children and Youth</t>
+          <t>Perceived eHealth literacy and health literacy among people with spinal cord injury: A cross-sectional study</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2019</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>cc-by</t>
-        </is>
-      </c>
+        <v>2022</v>
+      </c>
+      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Background There is growing interest in the relationship between physical and psychosocial factors related to resilience to better understand the antecedents of health and successful adaptation to challenges in and out of school, and across the lifespan. To further this understanding, a trans-disciplinary approach was used to investigate the association between the multidimensional constructs of physical literacy and resilience in children at a key stage in their development. Methods Cross-sectional data were collected from 227 school children aged 9-12 years old from five schools in [blinded]. Resilience was measured using the Child and Youth Resilience Measure, and physical literacy through the Physical Literacy Assessment for Youth tools. Data were provided by self-report, surrogate assessors of the child (physical education teachers and parents), and trained assessors for movement skills. These data were analysed using correlation and logistic regression. Results Resilience was significantly correlated with numerous indicators of physical literacy, including movement capacity, confidence, and competence, environmental engagement, and overall perceptions of physical literacy. Regressions indicated that resilience could be predicted by movement confidence and competence, environmental engagement, and overall physical literacy. Conclusions The findings of this study, using a constellation of sources, provide foundational evidence for the link between resilience and physical literacy among children, encouraging the importance of physical literacy development in schools. Longitudinal studies are required to further examine this relationship and how these previously unrelated fields may work together for a richer understanding of the interplay between the physical and psychological determinants of well-being.</t>
+          <t>Objectives: This purpose of this research was to (1) to evaluate eHealth and general health literacy levels among individuals with spinal cord injury (SCI) and (2) to identify relationships between eHealth literacy, general health literacy, and various sociodemographic factors.</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>['Philip Jefferies', 'Michael Ungar', 'Patrice Aubertin', 'Dean Kriellaars']</t>
+          <t>['Gurkaran Singh', 'Bonita Sawatzky', 'Laura Nimmon', 'W. Ben Mortenson']</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>[['Dalhousie University', 'https://ror.org/01e6qks80'], ['Dalhousie University', 'https://ror.org/01e6qks80'], ['National Circus School', 'https://ror.org/05ge25h32'], ['University of Manitoba', 'https://ror.org/02gfys938']]</t>
+          <t>[['University of British Columbia', 'https://ror.org/03rmrcq20'], ['International Collaboration On Repair Discoveries', 'https://ror.org/03ckrg061'], ['GF Strong Rehabilitation Centre', 'https://ror.org/02d4smc03'], ['International Collaboration On Repair Discoveries', 'https://ror.org/03ckrg061'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['International Collaboration On Repair Discoveries', 'https://ror.org/03ckrg061'], ['GF Strong Rehabilitation Centre', 'https://ror.org/02d4smc03']]</t>
         </is>
       </c>
       <c r="J88" t="n">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="K88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3389/fpubh.2019.00346</t>
+          <t>https://doi.org/10.1080/10790268.2021.1963140</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://openalex.org/W3035800846</t>
+          <t>https://openalex.org/W4221050125</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.pmedr.2020.101149</t>
+          <t>https://doi.org/10.1007/s42330-022-00196-4</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Testing a school-based program to promote digital health literacy and healthy lifestyle behaviours in intermediate elementary students: The Learning for Life program</t>
+          <t>The Development and Application of a Public Energy Literacy Instrument</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2020</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>cc-by-nc-nd</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Promoting digital health literacy and healthy lifestyle behaviours in children can lead to positive long-term health outcomes and prevent chronic diseases. However, there are few school-based interventions promoting this education to intermediate elementary students. The objective of this study was to test the effectiveness of a novel intervention to increase students' digital health literacy and health knowledge. Learning for Life is a classroom-based education program, developed for grade 4-7 students and delivered by teachers over six weeks. Three Canadian schools were recruited to deliver the intervention in 2018. This study had a pre-post design and no control group. Students' self-reported digital health literacy and healthy lifestyle behaviours were measured at pre-intervention (n = 126), post-intervention (n = 119), and two-month follow-up (n = 104). Students at pre-intervention had a mean (SD) age of 10.98 (0.56) years (57.1% females). Almost all (97%) students had unsupervised access to the Internet through a computer or smartphone. From pre- to post-intervention, students' digital health literacy increased (p = 0.009), but decreased from post-intervention to follow-up (p &lt; 0.001). Post-intervention, the majority of students could identify at least one healthy behaviour (e.g., exercising one hour/day) and reported making at least one healthy change in their lives (e.g., eating more fruits/vegetables). This study demonstrated that the Learning for Life intervention can improve intermediate elementary students' digital health literacy over the short-term and help them learn and retain healthy lifestyle knowledge and behaviours. These findings affirm the need for interventions promoting digital healthy literacy and healthy lifestyle behaviours for this age group.</t>
-        </is>
-      </c>
+        <v>2022</v>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>['Antonia Hyman', 'Kurtis Stewart', 'Anne-Marie Jamin', 'Helen Novak Lauscher', 'Elizabeth Stacy', 'Gerry Kasten', 'Kendall Ho']</t>
+          <t>['Runa Das', 'Russell Richman']</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>[['University of British Columbia', 'https://ror.org/03rmrcq20'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['Vancouver Coastal Health', 'https://ror.org/03bd8jh67'], ['University of British Columbia', 'https://ror.org/03rmrcq20']]</t>
+          <t>[['Royal Roads University', 'https://ror.org/05w4ste42'], ['Toronto Metropolitan University', 'https://ror.org/05g13zd79']]</t>
         </is>
       </c>
       <c r="J89" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="K89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.pmedr.2020.101149</t>
+          <t>https://doi.org/10.1007/s42330-022-00196-4</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2994090949</t>
+          <t>https://openalex.org/W4387169428</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3389/feduc.2019.00120</t>
+          <t>https://doi.org/10.1108/bfj-11-2022-1033</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Measurement Comparability of Reading in the English and French Canadian Populations: Special Case of the 2011 Progress in International Reading Literacy Study</t>
+          <t>Identifying individual factors associated with pleasure of eating healthy foods and plant/animal protein food consumption: findings from an exploratory study</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2019</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>cc-by</t>
-        </is>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>The purpose of this study is to examine item equivalence and score comparability of the Progress in International Reading Literacy Study (PIRLS) 2011for the Canadian French and English language groups. Two methods of differential item functioning were conducted to examine item equivalence across thirteen test booklets designed to assess reading literacy in early years of schooling. Four bilingual reviewers with expertise in reading literacy conducted independent, linguistic and cultural reviews to identify both the degree of item equivalence and potential sources of differences between language versions of released items. Results indicate that an average of 25% of items per booklet function differently at the item level. Reviews by experts indicate differences between the two language versions on some items flagged as displaying differential item function (DIF). Some of these were identified to have linguistic differences pointing to differential difficulty levels in the two language versions.</t>
+          <t>Purpose This study identifies new factors influencing the adoption of two recently promoted messages in Canada's updated food guide (FG): enhancing pleasure of eating healthy foods (PEHFs) and shifting food choices towards plant protein foods. Currently, limited and contradictory evidence is available regarding associations between environmental values, nutrition literacy, PEHFs, and plant/animal protein food consumption. Design/methodology/approach An online survey measuring environmental values; nutrition literacy, distinctively based on previous (2007) and most recent (2019) FG messages; PEHFs; and annual changes in the consumption of protein foods was sent to Quebec residents (N = 128). Findings Greater nutrition literacy of both 2007 and 2019 FGs and greater environmental values were associated with greater PEHFs (ß = 0.248, p &amp;lt; 0.01; ß = 0.209, p &amp;lt; 0.05; ß = 0.423, p &amp;lt; 0.001, respectively). Greater PEHFs was associated with greater consumption of plant protein foods (ß = 0.405, p &amp;lt; 0.001). Greater nutrition literacy of the 2007 FG was associated with greater consumption of animal protein foods (ß = 0.409, p &amp;lt; 0.001), whereas greater nutrition literacy of the 2019 FG was linked to lower consumption of animal protein foods (ß = −0.225, p &amp;lt; 0.05). Practical implications Enhancing PEHFs may require increasing general FG nutrition literacy and strengthening environmental values. To encourage plant protein food consumption and decrease animal protein food consumption, the authors recommend promoting PEHFs and increasing nutrition literacy based on newest FG recommendations. Originality/value This new evidence may help develop strategies promoting PEHFs and plant protein food consumption, thus increasing uptake of new FG recommendations.</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>['Shawna Goodrich', 'Kadriye Ercikan']</t>
+          <t>['Jessica Lambert-De Francesch', 'JoAnne Labrecque', 'Stéphanie Lessard']</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>[['Department of National Defence', 'https://ror.org/035rreb34'], ['Educational Testing Service', 'https://ror.org/03b5q4637']]</t>
+          <t>[['Université de Montréal', 'https://ror.org/0161xgx34'], ['HEC Montréal', 'https://ror.org/05ww3wq27'], ['Institut National de Santé Publique du Québec', 'https://ror.org/00kv63439']]</t>
         </is>
       </c>
       <c r="J90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3389/feduc.2019.00120</t>
+          <t>https://doi.org/10.1108/bfj-11-2022-1033</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://openalex.org/W3035439260</t>
+          <t>https://openalex.org/W4283369041</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1177/2047173420927665</t>
+          <t>https://doi.org/10.3390/ijerph19137669</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>An assessment of personal financial literacy teaching and learning in Ontario high schools</t>
+          <t>Measuring Health Literacy in Primary Healthcare: Adaptation and Validation of a French-Language Version of the Brief Health Literacy Screening among Patients with Chronic Conditions Seen in Primary Care</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>The purpose of the study was to examine the experiences of current high school students and teachers in Ontario regarding their experiences with personal financial curriculum and teaching at the secondary level, and to identify the ways in which this important educational experience may have helped prepare students to become financially literate. We considered this overarching issue using a transdisciplinary lens from the perspective of the three stakeholder groups. Using a case study research design, the first of its kind in Ontario or Canada on this topic, We utilized interviews and artifacts to uncover student and teacher experiential data across three high schools in southeastern Ontario. The major findings were that current students and teachers perceived curriculum and teaching experiences as seriously lacking in effectively preparing them to be financially literate, and that a fundamental reorientation around transdisciplinary, student-led learning was key to transforming such learning into a more meaningful and valuable educational experience. With mandatory, properly supported, student-oriented (transdisciplinary) instruction, the potential exists for more effective and valuable learning, resulting in better equipped high school students who were properly prepared to successfully navigate financial issues and the path ahead.</t>
+          <t>Background: The Brief Health Literacy Screening (BHLS) is a short self-report instrument developed to identify patients with inadequate health literacy. This study aimed to translate the BHLS into French Canadian (BHLS-FCv) and to evaluate its psychometric properties among patients with chronic conditions in primary care. Methods: The BHLS was translated into French using the Hawkins and Osborne’s method. Content validity was evaluated through cognitive interviews. A validation study of the BHLS-FCv was conducted in two primary care clinics in the province of Quebec (Canada) among adult patients with chronic conditions. Psychometric properties evaluated included: internal consistency (Cronbach’s alpha); test–retest reliability (intraclass correlation coefficient); and concurrent validity (Spearman’s correlations with the Health Literacy Questionnaire (HLQ)). Results: 178 participants completed the questionnaire at baseline and 47 completed the questionnaire two weeks later over the telephone. The average score was 13.3. Cronbach’s alpha for internal consistency was 0.77. The intraclass correlation coefficient for test–retest reliability was 0.69 (95% confidence interval: 0.45–0.83). Concurrent validity with Spearman’s correlation coefficient with three subscales of HLQ ranged from 0.28 to 0.58. Conclusions: The BHLS-FCv demonstrated acceptable psychometric properties and could be used in a population with chronic conditions in primary care.</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>['Murdoch Neil Matheson', 'Christopher DeLuca', 'Ian Matheson']</t>
+          <t>['Maud‐Christine Chouinard', 'Mireille Lambert', 'Mélissa Lavoie', 'Sylvie Lambert', 'Émilie Hudon', 'Olivier Dumont‐Samson', 'Catherine Hudon']</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>[["Queen's University", 'https://ror.org/02y72wh86'], ["Queen's University", 'https://ror.org/02y72wh86'], ["Queen's University", 'https://ror.org/02y72wh86']]</t>
+          <t>[['Université de Montréal', 'https://ror.org/0161xgx34'], ['Centre Intégré Universitaire de Santé et de Services Sociaux du Saguenay–Lac-Saint-Jean', 'https://ror.org/00vbjyq64'], ['Université du Québec à Chicoutimi', 'https://ror.org/00y3hzd62'], ['Université du Québec à Chicoutimi', 'https://ror.org/00y3hzd62'], ['Université de Sherbrooke', 'https://ror.org/00kybxq39'], ['Université de Sherbrooke', 'https://ror.org/00kybxq39'], ['Université de Sherbrooke', 'https://ror.org/00kybxq39']]</t>
         </is>
       </c>
       <c r="J91" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1177/2047173420927665</t>
+          <t>https://doi.org/10.3390/ijerph19137669</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2983457005</t>
+          <t>https://openalex.org/W4378086619</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/02640414.2019.1689076</t>
+          <t>https://doi.org/10.3390/socsci12060315</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Canadian Assessment of Physical Literacy in grades 7-9 (12-16 years): Preliminary validity and descriptive results</t>
+          <t>Adult Learner Perspectives on Skill- and Life-Based Outcomes Following Literacy Remediation</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2019</v>
-      </c>
-      <c r="F92" t="inlineStr"/>
+        <v>2023</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>cc-by</t>
+        </is>
+      </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Joel Blancharda , Nadine Van Wykb, Emily Ertela, Anastasia Alpousa &amp; Patricia E. Longmuir*aca Healthy Active Living and Obesity Research Group, Children's Hospital of Eastern Ontario Research Institute, Ottawa, Canadab Department of Health and Physical Education, Mount Royal University, Calgary, Canadac Faculty of Medicine, University of Ottawa, Ottawa, Canada</t>
+          <t>Using the situated expectancy value theory (SEVT), we explored self-perceived attainment perspectives of adults with low literacy on skill-based (i.e., reading, writing, listening, speaking) and life-based (i.e., management of day-to-day challenges, use of skills in daily living, confidence) improvements following a literacy-focused remediation program. Participants (N = 103; Canadian, urban adults) completed a remediation program for low literacy via one-on-one tutoring over a period of 1 year. Four to six months into the program, participants completed a survey that asked about their perspectives regarding improvements in skill- and life-based areas of functioning. A series of Chi-Square tests provided evidence for self-perceived improvements in skill-based functioning in reading, writing, listening and speaking. Perceived improvements were not noted in areas not targeted by the remediation, namely, math and computer literacy. Further, there was a significant, positive correlation between self-perceived improvement and (1) self-perceived ability to deal with daily challenges, (2) self-reported use of literacy skills in day-to-day activities, and (3) overall confidence. Together, these findings underscore the importance of including activity- and participation-based outcome measures when evaluating adult literacy remediation. In addition, this work demonstrates an application of SEVT to explore changes over time in continuing adult education.</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>['Joël Blanchard', 'Nadine Van Wyk', 'Emily Ertel', 'Anastasia Alpous', 'Patricia E. Longmuir']</t>
+          <t>['Jacqueline Cummine', 'Amberley Ostevik', 'Kulpreet Cheema', 'Angela Cullum']</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>[["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['Mount Royal University', 'https://ror.org/04evsam41'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Ottawa', 'https://ror.org/03c4mmv16']]</t>
+          <t>[['University of Alberta', 'https://ror.org/0160cpw27'], ['Women and Children’s Health Research Institute', 'https://ror.org/03e04kk51'], ['University of Alberta', 'https://ror.org/0160cpw27'], ['University of Alberta', 'https://ror.org/0160cpw27'], ['Women and Children’s Health Research Institute', 'https://ror.org/03e04kk51'], ['University of Alberta', 'https://ror.org/0160cpw27']]</t>
         </is>
       </c>
       <c r="J92" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="K92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/02640414.2019.1689076</t>
+          <t>https://doi.org/10.3390/socsci12060315</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://openalex.org/W2990953305</t>
+          <t>https://openalex.org/W4200243991</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1177/0017896919889647</t>
+          <t>https://doi.org/10.1080/17408989.2021.2014438</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Health-promoting skills for children: Evaluating the influence of a media literacy and food marketing intervention</t>
+          <t>PLitPE: an intervention for physical literacy enriched pedagogy in Canadian elementary school physical education classes</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Background: Media literacy skills are needed to navigate high levels of food marketing promoting the consumption of unhealthy foods. Health-promoting media literacy education encourages children to use analytical skills to critically examine media messages in order to make informed health choices. Objective: To evaluate the influence of media literacy lesson plans for children focusing on critical knowledge around food marketing. Design: Evidence-based Media Literacy &amp;amp; Food Marketing lesson plans, designed for grades 3 to 6 (ages 8–11) and 6 to 9 (ages 11–14), were developed to fill the knowledge gaps children demonstrated with respect to assessing of the healthfulness of packaged foods. Setting: Two public schools in Calgary, Alberta, Canada. Methods: An educational intervention with pre-test/post-test design. The lesson plans were used by teachers in the classroom, and a questionnaire was created to assess children’s pre- and post-lesson levels of critical knowledge about food marketing. Results: In total, 71 students from grades 5, 7, 8 and 9 participated. Qualitative analysis of responses showed increased analysis and evaluation skills when it came to understanding of food marketing appeals, and increased ability to assess the nutritional content of packaged foods. Conclusion: This study is novel in its use of media literacy as a framework for understanding food packaging appeals. It highlights the importance of examining procedural and interpretive knowledge in the evaluation of critical media literacy skills around food. This allows researchers, educators and health practitioners to better gauge how children are able to apply nutrition information in different contexts to make informed food choices.</t>
+          <t>Background: Although physical literacy is explicitly defined and integrated into Canadian provincial physical education curricula, limited empirical evidence substantiates the development of physical literacy in elementary physical education. Despite physical education curricular expectations, developing and assessing physical literacy in students may be difficult for teachers with little to no background in physical literacy or physical education.Purpose: The primary purpose was to explore the effect of a curricularly linked physical literacy enriched intervention in elementary school physical education. A secondary purpose involved an examination of the intervention's effects on sex differences.Design: A quasi-experimental controlled intervention trial with a matched comparison group was used to determine the impact of a curricular-based physical literacy enriched physical education intervention on students' development of physical literacy. Teachers (n = 6) and students (n = 131) from four Saskatchewan elementary schools participated in either a PLitPE (experimental) condition or a usual practice (control) condition. The PLitPE intervention was created using learning principles consistent with physical literacy and Self-Determination Theory. PLitPE instructional elements were developed with input from thirteen teachers who were members of the local school division's physical education professional learning community. An embedded professional development model was used where a mentor teacher was present to facilitate and support the implementation of the PLitPE intervention. The Physical Literacy Assessment for Youth tools were used to assess motor competence (PLAYfun), student self-description (PLAYself), and movement participation (PLAYinventory). Each domain of physical literacy (physical competence, psychological, and behavioural) was evaluated using these tools.Results: Significant differences, favouring PLitPE over control, were observed for average motor competence (M = 49.4, M = 40.0, p &lt; 0.001, PLAYfun), movement vocabulary (M = 10.3, M = 7.5, p &lt; 0.001, PLAYfun), environmental participation (M = 423.9, M = 390.1, p &lt; 0.05, PLAYself), and a reduction of sex differences on average motor competence and movement vocabulary. Statistically significant relationships with low to fair correlations between PLAYfun and PLAYself variables existed.Conclusions: This study provides empirical evidence supporting physical literacy enriched physical education. PLitPE developed the psychological domain (affective and cognitive) and significantly improved physical competence, however, the intervention did not manifest in improved behaviour. Concerning sex differences, the intervention yielded an equal and substantive improvement in both males and females in the intervention group. Future studies should consider the addition of reflective approaches, as well as the construction of positive challenges for children.</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>['Emily Truman', 'Charlene Elliott']</t>
+          <t>['Alexandra L. Stoddart', 'M. Louise Humbert', 'Serene Kerpan', 'Nicole Cameron', 'Dean Kriellaars']</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>[['University of Calgary', 'https://ror.org/03yjb2x39'], ['University of Calgary', 'https://ror.org/03yjb2x39']]</t>
+          <t>[['University of Regina', 'https://ror.org/03dzc0485'], ['University of Saskatchewan', 'https://ror.org/010x8gc63'], ['University of Saskatchewan', 'https://ror.org/010x8gc63'], ['University of Saskatchewan', 'https://ror.org/010x8gc63'], ['University of Ontario Institute of Technology', 'https://ror.org/016zre027'], ['University of Saskatchewan', 'https://ror.org/010x8gc63'], ['Saskatoon City Hospital', 'https://ror.org/0390t1205'], ['University of Manitoba', 'https://ror.org/02gfys938']]</t>
         </is>
       </c>
       <c r="J93" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K93" t="b">
         <v>0</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1177/0017896919889647</t>
+          <t>https://doi.org/10.1080/17408989.2021.2014438</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://openalex.org/W3039959558</t>
+          <t>https://openalex.org/W4226055404</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1177/0265532220930348</t>
+          <t>https://doi.org/10.1080/14635240.2022.2059543</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Change in home language environment and English literacy achievement over time: A multi-group latent growth curve modeling investigation</t>
+          <t>A cross-sectional study to assess health literacy levels among Canadian post-secondary students during the COVID-19 pandemic</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>In most studies investigating the educational outcomes of linguistically diverse students, variables that identify this population have been considered as static. In reality, owing to the dynamic nature of students and their families, students’ home language environments change over time. This study aims to understand how elementary school students’ home language environments change over time, and how longitudinal patterns of English literacy achievement across grades 3, 6, and 10 differ among students with various home language shift patterns in Ontario, Canada. The longitudinal cohort data of 89,609 students between grades 3 and 10 from the provincial assessments were analyzed for changes in their home language environment. A subsample of 18,000 students was used to examine different patterns of relative literacy performance over time and their associations with immigration background and early intervention programming using multi-group latent growth curve modeling. Our findings suggest a strong movement toward an English-dominant home language environment among multilingual students; yet, students whose homes remained as multilingual demonstrated the highest literacy achievement in the early grade as well as the highest improvement in relative performance over time. The paper draws implications for promoting students’ home language, instilling a positive view of multilingual competence.</t>
+          <t>To better understand the online information-seeking behaviors and health literacy levels of Canadian post-secondary students, a cross-sectional online bilingual survey was initiated during the first wave of COVID-19 in Canada. The survey was administered to Canadian post-secondary students from 1 July 2020, to 30 September 2020, through email invitations and social media platforms. The objective of this paper is to assess the online information-seeking behaviors and health literacy levels in relation to the coronavirus of Canadian post-secondary students during the COVID-19 pandemic. The online survey was developed using standardized tools, including the Digital Health Literacy Instrument, and newly developed measures of sociodemographic indicators and the information satisfaction scale. Sociodemographic factors and health literacy levels were analyzed using descriptive statistics. A total of 2,679 students partihigh levels of health literacy and could easily access online information related to COVID-19 to make health decisions. The most frequently used sources to obtain information about the coronavirus were search engines and websites of public sector agencies. While the majority of respondents found it easy to access and utilize online health information, continued development of these resources is vital to reducing the spread of COVID-19 and addressing misinformation. Accurate and well-maintained online resources are key preventative health measures to educate the public and ultimately lessen the burden on our healthcare system.</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>['Hyun-Ah Kim', 'Christine Barron', 'Jeanne Sinclair', 'Eunice Eunhee Jang']</t>
+          <t>['Simran Purewal', 'Paola Ardiles', 'Erica Di Ruggiero', 'Hussein Elhagehassan', 'John Flores', 'Sana Mahmood']</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>[['University of Toronto', 'https://ror.org/03dbr7087'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['University of the Incarnate Word', 'https://ror.org/044a5dk27'], ['University of Toronto', 'https://ror.org/03dbr7087']]</t>
+          <t>[['Simon Fraser University', 'https://ror.org/0213rcc28'], ['Simon Fraser University', 'https://ror.org/0213rcc28'], ['Public Health Ontario', 'https://ror.org/025z8ah66'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['Simon Fraser University', 'https://ror.org/0213rcc28'], ['Simon Fraser University', 'https://ror.org/0213rcc28'], ['University of Toronto', 'https://ror.org/03dbr7087']]</t>
         </is>
       </c>
       <c r="J94" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K94" t="b">
         <v>0</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1177/0265532220930348</t>
+          <t>https://doi.org/10.1080/14635240.2022.2059543</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://openalex.org/W3133989721</t>
+          <t>https://openalex.org/W4365452341</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1139/apnm-2020-0957</t>
+          <t>https://doi.org/10.3390/children10040720</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Characterization of physical literacy in children with chronic medical conditions compared with healthy controls: a cross-sectional study</t>
+          <t>Piloting the Virtual PLAYshop Program: A Parent-Focused Physical Literacy Intervention for Early Childhood</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2021</v>
-      </c>
-      <c r="F95" t="inlineStr"/>
+        <v>2023</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>cc-by</t>
+        </is>
+      </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>To determine the physical literacy, defined as the capability for a physically active lifestyle, of children with medical conditions compared with healthy peers, this multicenter cross-sectional study recruited children with medical conditions from cardiology, neurology (including concussion), rheumatology, mental health, respirology, oncology, hematology, and rehabilitation (including cerebral palsy) clinics. Participants aged 8-12 years (N = 130; mean age: 10.0 ± 1.44 years; 44% female) were randomly matched to 3 healthy peers from a normative database, based on age, gender, and month of testing. Total physical literacy was assessed by the Canadian Assessment of Physical Literacy, a validated assessment of physical literacy measuring physical competence, daily behaviour, knowledge/understanding, and motivation/confidence. Total physical literacy mean scores (/100) did not differ (t(498) = -0.67; p = 0.44) between participants (61.0 ± 14.2) and matched healthy peers (62.0 ± 10.7). Children with medical conditions had lower mean physical competence scores (/30; -6.5 [-7.44 to -5.51]; p &lt; 0.001) but higher mean motivation/confidence scores (/30; 2.6 [1.67 to 3.63]; p &lt; 0.001). Mean daily behaviour and knowledge/understanding scores did not differ from matches (/30; 1.8 [0.26 to 3.33]; p = 0.02;/10; -0.04 [-0.38 to 0.30]; p = 0.81; respectively). Children with medical conditions are motivated to be physically active but demonstrate impaired movement skills and fitness, suggesting the need for targeted interventions to improve their physical competence. Novelty: Physical literacy in children with diverse chronic medical conditions is similar to healthy peers. Children with medical conditions have lower physical competence than healthy peers, but higher motivation and confidence. Physical competence (motor skill, fitness) interventions, rather than motivation or education, are needed for these youth.</t>
+          <t>The PLAYshop program is a parent-focused physical literacy intervention for early childhood. This single-group mixed-methods pilot study aimed to explore the feasibility of virtually delivering and assessing the PLAYshop program. The virtual PLAYshop program included a virtual workshop, resources/basic equipment, and two booster emails (3-week and 6-week follow-up). Data on 34 preschool-aged children (3-5 years) and their parents from Edmonton and Victoria, Canada, were collected via an online questionnaire, virtual assessment session, and interview at single or multiple time points (baseline, post-workshop, 2-month follow-up). Intraclass correlation coefficients (ICCs), paired t-tests, repeated measures ANOVAs, and thematic analyses were conducted. Regarding feasibility, most parents (≥94%) were satisfied/extremely satisfied with the virtual workshop and planned to continue physical literacy activities post-workshop. The virtual assessment protocol for children's fundamental movement skills (FMS; overhand throw, underhand throw, horizontal jump, hop, one-leg balance) was feasible, with high completion rates (&gt;90%) and reliable scoring (ICC = 0.79-0.99). For positive changes in potential outcomes, a medium effect size was observed for children's hopping skills (d = 0.54), and large effect sizes were observed for several parental outcomes (partial η2 = 0.20-0.54). The findings support the feasibility and potential positive outcomes of the virtual PLAYshop program. A larger randomized controlled efficacy trial is recommended.</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>['Jeffrey Do', 'Angelica Blais', 'Brian M. Feldman', 'Leonardo R. Brandão', 'Jane Lougheed', 'Daniela Pohl', 'Robert J. Klaassen', 'Donna L. Johnston', 'Denise De Laat', 'Johannes Roth', 'Sherri L. Katz', 'Anna McCormick', 'F. Virginia Wright', 'Gail Macartney', 'Hugh J. McMillan', 'Sunita Venkateswaran', 'Erick Sell', 'Asif Doja', 'Katherine Matheson', 'Addo Boafo', 'Patricia E. Longmuir']</t>
+          <t>['Yeongho Hwang', 'Madison Boyd', 'Patti‐Jean Naylor', 'Ryan E. Rhodes', 'Sam Liu', 'Ramiah Moldenhauer', 'Qiang Li', 'Christopher I. Wright', 'E. Jean Buckler', 'Valerie Carson']</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>[['University of Ottawa', 'https://ror.org/03c4mmv16'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['Hospital for Sick Children', 'https://ror.org/057q4rt57'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['Hospital for Sick Children', 'https://ror.org/057q4rt57'], ['University of Toronto', 'https://ror.org/03dbr7087'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ['Holland Bloorview Kids Rehabilitation Hospital', 'https://ror.org/03qea8398'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ['University of Prince Edward Island', 'https://ror.org/02xh9x144'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ["Children's Hospital of Eastern Ontario", 'https://ror.org/05nsbhw27'], ['University of Ottawa', 'https://ror.org/03c4mmv16']]</t>
+          <t>[['University of Alberta', 'https://ror.org/0160cpw27'], ['University of Alberta', 'https://ror.org/0160cpw27'], ['University of Victoria', 'https://ror.org/04s5mat29'], ['University of Victoria', 'https://ror.org/04s5mat29'], ['University of Victoria', 'https://ror.org/04s5mat29'], ['University of Alberta', 'https://ror.org/0160cpw27'], ['University of Alberta', 'https://ror.org/0160cpw27'], ['University of Victoria', 'https://ror.org/04s5mat29'], ['University of Victoria', 'https://ror.org/04s5mat29'], ['University of Alberta', 'https://ror.org/0160cpw27']]</t>
         </is>
       </c>
       <c r="J95" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1139/apnm-2020-0957</t>
+          <t>https://doi.org/10.3390/children10040720</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://openalex.org/W3011227050</t>
+          <t>https://openalex.org/W4211052767</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1186/s40536-020-00080-3</t>
+          <t>https://doi.org/10.1016/j.ssmph.2022.101038</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Are large surveys of adult literacy skills as comparable over time as we think?</t>
+          <t>Literacy and self-rated health: Analysis of the Longitudinal and International Study of Adults (LISA)</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>cc-by</t>
+          <t>cc-by-nc-nd</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Abstract Recent literature shows that younger cohorts have lower levels of literacy ceteris paribus in Canada, the United States, Norway and other developed countries. Very few explanations are provided to justify the existence of this negative cohort effect. Yet this decline has serious implications for the economy, education system and society. In this paper, we focus on Canada and replicate the results published in the literature using the same methodology (synthetic cohorts). We use the same data from surveys of adult skills, namely the International Adult Literacy Survey (IALS), the Adult Literacy and Life Skills Survey (ALL) and the Survey of Adult Skills, a product of the OECD Programme for the International Assessment of Adult Competencies (PIAAC). Second, we conduct further analyses to better understand the effect of time on adults’ literacy skills. We then show that age has a negative effect on the literacy score, but also that a significant “period” effect (or rather a “survey” effect) can only be explained by a change in the instrument used to measure literacy skills from one survey to another. This article reveals that the negative cohort effect mentioned in the literature may be fallacious as it is exacerbated when the control for measuring instrument distortions is omitted. This paper contributes to advancing knowledge about the effect that age and cohort has on adult literacy levels in Canada. The results weaken the idea of a clear negative cohort effect; much of this effect would in fact be caused by a non-comparable methodology that systematically assigned individuals lower scores in the most recent survey cycles. These findings are important because they highlight the limitations of analyses that can be done with the synthetic cohort method using cross-sectional surveys on adult literacy skills not only in Canada, but also in all other countries where these surveys have been conducted.</t>
+          <t>The relationship between education and health is well-established. The empirical literature finds that individuals with higher levels of education experience lower risks of poor health outcomes compared to individuals with less education. Outstanding to this literature is the examination of a dimension of education - literacy - and its association with health. The objective of this study was to examine the relationship between literacy (reading, numeracy) and health (self-reported health). We use data from the 2012 wave of the Canadian Longitudinal International Survey of Adults (LISA). The LISA includes rich information on health, broader sociodemographic characteristics (income, age, sex, etc.) as well as information on literacy skills from the Program for International Assessment of Adult Competencies (PIAAC). Using logistic regression, we first reaffirm the association between education and self-reported health. We then find that after controlling for measures of literacy, understood as proficiency in reading and numeracy, the magnitude of effect of education on health is reduced. Skills in literacy reduce the risk of reporting poor health, but only for the older subset of respondents (ages 40-65). Our results suggest that literacy should not be understated in empirical research on education and health, and in fact serve to sharpen our understanding of how education impacts health by drawing attention to indirect pathways.</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>['Samuel Vézina', 'Alain Bélanger']</t>
+          <t>['Emma M. Macdonald', 'Emmanuelle Arpin', 'Amélie Quesnel‐Vallée']</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>[['Institut National de la Recherche Scientifique', 'https://ror.org/04td37d32'], ['International Institute for Applied Systems Analysis', 'https://ror.org/02wfhk785'], ['Institut National de la Recherche Scientifique', 'https://ror.org/04td37d32']]</t>
+          <t>[['McGill University', 'https://ror.org/01pxwe438'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['McGill University', 'https://ror.org/01pxwe438']]</t>
         </is>
       </c>
       <c r="J96" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K96" t="b">
         <v>1</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1186/s40536-020-00080-3</t>
+          <t>https://doi.org/10.1016/j.ssmph.2022.101038</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://openalex.org/W3035683435</t>
+          <t>https://openalex.org/W4327598178</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/13811118.2020.1769783</t>
+          <t>https://doi.org/10.3389/fspor.2023.1125072</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Depression and Suicide Literacy among Canadian Sexual and Gender Minorities</t>
+          <t>A cross-sectional study of Canadian children's valuation of literacies across social contexts</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -5244,148 +5256,148 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>The purpose of this study was to examine and compare depression and suicide literacy among Canadian sexual and gender minorities (SGM). Online surveys comprised of the 22-item depression literacy scale (D-LIT) and the 12-item literacy of suicide scale (LOSS) were completed by 2,778 individuals identifying as SGM. Relationships between depression and suicide literacy and demographic characteristics were evaluated using multivariable linear regression. Overall, SGM correctly answered 71.3% of the questions from the D-LIT and 76.5% of the LOSS. D-LIT scores were significantly lower among cisgender men and D-LIT and LOSS scores were lower among transgender women when compared to cisgender women. LOSS and D-LIT scores were significantly lower among SGM without a university degree (compared to those with a university degree) and among SGM from ethnic minority groups (compared to White SGM). D-LIT scores, but not LOSS scores, were significantly lower among Indigenous SGM compared to White SGM. The findings provide evidence of differences in suicide and depression literacy between SGM subgroups along multiple social axes. Interventions to increase depression and suicide literacy should be prioritized as part of a mental health promotion strategy for SGM, targeting subgroups with lower literacy levels, including cisgender men, transgender women, Indigenous people, racialized minorities, and those without a university degree.</t>
+          <t>Children, on average, do not engage in sufficient physical activity to reap the physical, mental, and social health benefits. Understanding the value that children place on movement across social contexts, and the relative ranking of this valuation, may help us to understand and intervene on activity levels.This exploratory study examined the valuation of reading/writing, math, and movement across three social contexts (school, home, with friends) among children 6-13 years of age (N = 7,845; 51.3% male). Subjective task values across contexts were assessed with the valuing literacies subscale of the PLAYself. One-way Kruskal-Wallis ANOVAs were performed to test for differences between contexts and between literacies, respectively.Sex differences and age-related variation were explored. Valuations of reading/writing (d = 1.16) and math (d = 1.33) decreased across context (school &gt; family &gt; friend), while the valuation of movement was relatively stable (d = 0.26). Valuations differed substantially with friends (p &lt; 0.001, d = 1.03). Sex dependent effect sizes were minimal (d = 0.05-0.11).Movement is highly valued by children across social contexts; thus, programming across contexts should be prioritized to align with their valuation.</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>['Olivier Ferlatte', 'Travis Salway', 'John L. Oliffe', 'Simon Rice', 'Mark Gilbert', 'Ingrid Young', 'Lisa McDaid', 'John S. Ogrodniczuk', 'Rod Knight']</t>
+          <t>['Emily Bremer', 'Philip Jefferies', 'John Cairney', 'Dean Kriellaars']</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[['Acadia University', 'https://ror.org/00839we02'], ['Dalhousie University', 'https://ror.org/01e6qks80'], ['The University of Queensland', 'https://ror.org/00rqy9422'], ['University of Manitoba', 'https://ror.org/02gfys938']]</t>
         </is>
       </c>
       <c r="J97" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K97" t="b">
         <v>1</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/13811118.2020.1769783</t>
+          <t>https://doi.org/10.3389/fspor.2023.1125072</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://openalex.org/W3134845393</t>
+          <t>https://openalex.org/W4391613780</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.arth.2021.02.075</t>
+          <t>https://doi.org/10.1186/s40561-024-00293-x</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Musculoskeletal Health Literacy is Associated With Outcome and Satisfaction of Total Knee Arthroplasty</t>
+          <t>Navigating the digital world: development of an evidence-based digital literacy program and assessment tool for youth</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2021</v>
-      </c>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>cc-by</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Abstract The rapid expansion of digital connectivity has provided youth with wide-ranging access to digital platforms for communication, entertainment, and education. In light of this profound shift, there have been growing concerns about online safety, data privacy, and cybersecurity. A critical factor influencing the ability of youth to responsibly navigate digital platforms is digital literacy. While digital literacy programs have been implemented in various regions worldwide, significant disparities remain not only in overall digital literacy levels, but also the assessment of digital literacy initiatives. To address these challenges, an environmental scan and literature review were conducted to identify existing digital literacy programs in Canada developed specifically for youth, as well as digital literacy assessment tools, respectively. The search encompassed peer-reviewed articles, organizational curricula, and assessment measures indexed in various databases and organization websites. The environmental scan identified 15 programs targeting key components of digital literacy such as data safety, cyberbullying, and digital media. The literature review identified 12 digital literacy assessment tools. Based on the findings, data were synthesized from shortlisted programs and assessment tools to inform the development of both a new digital literacy program and assessment tool to complement the youth-focused program. The new program focuses on four key components: (1) digital fluency, (2) digital privacy and safety, (3) ethics and empathy, and (4) consumer awareness. A 15-item assessment tool was also developed consisting of 4–5 questions specific to each program component. Given the growing importance of digital competencies, a youth-focused program and assessment tool are crucial for understanding and addressing digital literacy among this vulnerable cohort. This program's adaptability allows for customization across sociodemographic target groups, including culturally diverse and geographically remote communities—an aspect that has the potential to enhance digital literacy across settings. Implementing digital literacy programs can better prepare youth for an increasingly digital world, while minimizing potential risks associated with technology use.</t>
+        </is>
+      </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>['Arvind S. Narayanan', 'Kurt E. Stoll', 'Lincoln F. Pratson', 'Feng‐Chang Lin', 'Christopher W. Olcott', 'Daniel J. Del Gaizo']</t>
+          <t>['M. Claire Buchan', 'Jasmin Bhawra', 'Tarun Reddy Katapally']</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>[['University of North Carolina at Chapel Hill', 'https://ror.org/0130frc33'], ['University of North Carolina at Chapel Hill', 'https://ror.org/0130frc33'], ['University of North Carolina at Chapel Hill', 'https://ror.org/0130frc33'], ['University of North Carolina at Chapel Hill', 'https://ror.org/0130frc33'], ['University of North Carolina at Chapel Hill', 'https://ror.org/0130frc33'], ['University of North Carolina at Chapel Hill', 'https://ror.org/0130frc33']]</t>
+          <t>[['University of Waterloo', 'https://ror.org/01aff2v68'], ['Toronto Metropolitan University', 'https://ror.org/05g13zd79'], ['Western University', 'https://ror.org/02grkyz14']]</t>
         </is>
       </c>
       <c r="J98" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="K98" t="b">
         <v>1</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.arth.2021.02.075</t>
+          <t>https://doi.org/10.1186/s40561-024-00293-x</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://openalex.org/W4360620777</t>
+          <t>https://openalex.org/W4383710507</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://doi.org/10.33137/utmj.v100i1.39410</t>
+          <t>https://doi.org/10.1007/s11136-023-03447-5</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Health literacy awareness among Canadian surgeons</t>
+          <t>Measuring skill-based health literacy in chronic airway disease patients: the development and psychometric evaluation of the Vancouver airways health literacy tool (VAHLT)</t>
         </is>
       </c>
       <c r="E99" t="n">
         <v>2023</v>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>cc-by</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Adequate health literacy is essential to navigate the healthcare system and has a major role in peri-operative care and outcomes. Minimal information exists regarding surgeons’ understanding of health literacy, clinical implications, and awareness of universal measures of support. This study assessed Canadian surgeons’ perceptions of patients’ health literacy and their knowledge of available supportive resources. We conducted a cross-sectional study using an electronic survey distributed to surgeons at academic institutions. Data collected included sociodemographics, health literacy knowledge, and practice surrounding the use of supportive measures. Across four Canadian academic institutions (University of Toronto, McMaster University, University of Alberta, and University of Calgary), 35 surgeons from various surgical specialties, including general, plastic, and orthopedic surgery, completed the survey. Approximately 74% of surgeons reported familiarity with the concept “health literacy”, but they used general impressions to estimate their patients’ health literacy levels. Surgeons’ perceptions were that patients who had proficient health literacy represented 50% or less of their practice. However, knowledge of supportive tools for measuring patient health literacy was variable. Surgeons familiar with health literacy spent significantly more time (&amp;gt;15 minutes) counselling patients (38%, p=0.02) and used language at a 10th grade level or less (92%, p=0.04). Common supportive measures included using simple, non-medical terms (97%, n=34), repetition (83%, n=29), and drawing pictures/diagrams (83%, n=29). This study highlights the importance of surgeon awareness of health literacy and how improved awareness may guide patient-surgeon interactions and improve the quality of care.</t>
-        </is>
-      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
-          <t>['Josephine A. D’Abbondanza', 'Mélissa Roy', 'Karen Okrainec', 'Christine B. Novak', 'Herbert P. von Schroeder', 'David R. Urbach', 'Steven J. McCabe']</t>
+          <t>['Richard E. Hohn', 'Jacek A. Kopec', 'Richard Sawatzky', 'Iraj Poureslami', 'J. Mark FitzGerald']</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>[['University of Toronto', 'https://ror.org/03dbr7087'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['University of Toronto', 'https://ror.org/03dbr7087']]</t>
+          <t>[['Simon Fraser University', 'https://ror.org/0213rcc28'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['Trinity Western University', 'https://ror.org/01j2kd606'], ['Centre for Health Evaluation and Outcome Sciences', 'https://ror.org/04g6gva85'], ['Western University', 'https://ror.org/02grkyz14'], ['Providence Health Care', 'https://ror.org/03qqdf793'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['Vancouver Native Health Society', 'https://ror.org/04k296d46'], ['Vancouver Coastal Health', 'https://ror.org/03bd8jh67'], ['Vancouver Coastal Health Research Institute', 'https://ror.org/04htzww22'], ['Vancouver Coastal Health', 'https://ror.org/03bd8jh67'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['Vancouver Coastal Health Research Institute', 'https://ror.org/04htzww22']]</t>
         </is>
       </c>
       <c r="J99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>https://doi.org/10.33137/utmj.v100i1.39410</t>
+          <t>https://doi.org/10.1007/s11136-023-03447-5</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://openalex.org/W4281719045</t>
+          <t>https://openalex.org/W4309495336</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/09500693.2022.2080887</t>
+          <t>https://doi.org/10.4187/respcare.10441</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Associations between science dispositions and science literacy: a comparison of the United States and Canada</t>
+          <t>Evaluation of a New Performance-Based Health Literacy Measurement Tool for Individuals With Chronic Airways Disease</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -5394,738 +5406,26 @@
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>While the United States (U.S.) and Canada share features in their secondary education systems (e.g. proportion of immigrants), these nations have differences (e.g. linguistic ). Given the primacy of Canada over the U.S. vis-à-vis science literacy [as measured by the Programme International for Student Assessment (PISA)], underlying differences in science dispositions and school climate variables could exist. The PISA 2015 science-focused dataset, including 5712 students in 172 schools in the U.S. and 20,058 students in 645 schools in Canada, was modelled via multilevel methods to assess associations among science dispositions (epistemology, enjoyment, interest, instrumental, self-efficacy activities) and science literacy. Associations of school climate variables of instructional leadership, disciplinary climate and teaching support (the latter two in the context of science classes) with the above measures were evaluated. Disciplinary climate was more often associated with science dispositions (as outcome measures) in the U.S., while teaching support was most often associated with these measures for Canada. Disciplinary climate was associated with science literacy (as an outcome measure) in the U.S.; in contrast, no school climate measures were associated with science literacy in Canada. These results support an emphasis on disciplinary climate in U.S. science classrooms, but an emphasis on teaching support in Canadian science classrooms.</t>
+          <t>&lt;h3&gt;BACKGROUND:&lt;/h3&gt; Low health literacy is a global challenge. Health literacy is positively correlated with chronic airways diseas&lt;b&gt;e&lt;/b&gt; desirable outcomes. Despite the importance of health literacy in disease management, current health literacy measurement tools are suboptimal. As part of a multi-stage project to develop a performance-based, disease-specific Vancouver Airways Health Literacy Tool (VAHLT) for individuals with chronic airways disease, this study assessed the relationships between the VAHLT scores and characteristics of patients with chronic airways disease. The primary aim of the study was to provide preliminary evidence of construct validity of the VAHLT. &lt;h3&gt;METHODS:&lt;/h3&gt; A cross-sectional study design was applied. Study subjects were recruited from 6 specialty care clinics to complete the VAHLT measurement tool. Demographic and clinical data, including quality of life and disease control, were collected via validated questionnaires. The study subjects also completed a spirometry test. Inferential analysis was conducted by using mean difference testing and correlational methods. &lt;h3&gt;RESULTS:&lt;/h3&gt; A total of 320 subjects were recruited, and, after imputing missing data, 315 were ultimately analyzed. The subjects were predominantly women (61%), white (83%), had a post–high-school education (74%), and a mean ± SD age of 65.2 ± 13.2 y. Age was significantly negatively correlated with the VAHLT scores (&lt;i&gt;P&lt;/i&gt; = .004); the subjects with a post–high school education had significantly higher VAHLT scores than those with a high school education or less (&lt;i&gt;P&lt;/i&gt; &amp;lt; .001). No significant sex or ethnicity related differences in VAHLT scores were observed. For clinical outcomes, no significant differences were found between the VAHLT scores and disease severity or measures of quality of life and asthma control. &lt;h3&gt;CONCLUSIONS:&lt;/h3&gt; We report a chronic airways disease–specific health literacy measurement tool developed with the involvement of patients and professionals. Age and education were highly correlated with health literacy, which emphasizes the importance of addressing these factors in health literacy interventions among patients with chronic airways disease.</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>['Larry J. Grabau', 'Louis Trudel', 'Xin Ma']</t>
+          <t>['Iraj Poureslami', 'Ric E Hohn', 'Jacek A. Kopec', 'Richard Sawatzky', 'Shawn D. Aaron', 'Samir Gupta', 'Roger Goldstein', 'Louis‐Philippe Boulet', 'Noah Tregobov', 'Jessica Shum']</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>[['University of Kentucky', 'https://ror.org/02k3smh20'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ['Kentucky Department of Education', 'https://ror.org/01hsff479'], ['University of Kentucky', 'https://ror.org/02k3smh20']]</t>
+          <t>[['University of British Columbia', 'https://ror.org/03rmrcq20'], ['Vancouver Coastal Health Research Institute', 'https://ror.org/04htzww22'], ['Vancouver Native Health Society', 'https://ror.org/04k296d46'], ['Vancouver Coastal Health', 'https://ror.org/03bd8jh67'], ['Simon Fraser University', 'https://ror.org/0213rcc28'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['Trinity Western University', 'https://ror.org/01j2kd606'], ['Western University', 'https://ror.org/02grkyz14'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['West Park Healthcare Centre', 'https://ror.org/037y13578'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['Université Laval', 'https://ror.org/04sjchr03'], ['Vancouver Coastal Health', 'https://ror.org/03bd8jh67'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['Vancouver Coastal Health Research Institute', 'https://ror.org/04htzww22'], ['Vancouver Coastal Health', 'https://ror.org/03bd8jh67'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['Vancouver Coastal Health Research Institute', 'https://ror.org/04htzww22']]</t>
         </is>
       </c>
       <c r="J100" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K100" t="b">
         <v>0</v>
       </c>
       <c r="L100" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1080/09500693.2022.2080887</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="1" t="n">
-        <v>99</v>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>https://openalex.org/W4389109305</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.55016/ojs/ajer.v68i2.71334</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Cognitive Skills of Canadian Educators: An Analysis of PIAAC Data</t>
-        </is>
-      </c>
-      <c r="E101" t="n">
-        <v>2022</v>
-      </c>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>The purpose of this study was to conduct national and cross-country analyses to provide insights about educator cognitive skills in literacy, numeracy, and problem-solving within Canada and across nineteen countries using the PIAAC data. MANOVA results of profession differences within Canada demonstrated that educators outperformed other professions in general programs, health and welfare, and services but underperformed the professions in science, mathematics, and computing in all three domains. MANOVA results of educator differences across countries showed that educators in Canada outperformed those in Denmark, Estonia, the Russian Federation, and the United Kingdom in literacy, outperformed the United Kingdom in numeracy, and outperformed Denmark, Estonia, and the United Kingdom in problem-solving. Finally, multiple regression analyses identified statistically significant indicators of Canadian educators’ literacy, numeracy, and problem-solving proficiencies. The results of this study reveal and suggest that the cognitive skills of Canadian educators have the potential to be enhanced. Keywords: teacher cognitive skills, literacy, numeracy, problem-solving in technology-rich environments L'objectif de cette étude était de mener des analyses nationales et internationales afin de fournir des informations sur les compétences cognitives des éducateurs en matière de littératie, de numératie et de résolution de problèmes au Canada et dans dix-neuf pays à l'aide des données de l'enquête PIAAC. Les résultats de l'analyse MANOVA des différences entre les professions au Canada ont démontré que les éducateurs surpassent les autres professions dans les domaines des programmes généraux; de la santé et du bien-être; et des services, mais qu'ils sont moins performants que les autres professions en sciences, en mathématiques et en informatique dans les trois domaines. Les résultats de l'analyse MANOVA des différences entre les éducateurs des différents pays ont montré que les éducateurs du Canada surpassent ceux du Danemark, de l'Estonie, de la Fédération de Russie et du Royaume-Uni en littératie, surpassent ceux du Royaume-Uni en numératie et surpassent ceux du Danemark, de l'Estonie et du Royaume-Uni en résolution de problèmes. Enfin, les analyses de régression multiple ont permis d'identifier des indicateurs statistiquement significatifs des compétences des éducateurs canadiens en matière de littératie, de numératie et de résolution de problèmes. Les résultats de cette étude révèlent et suggèrent que les compétences cognitives des éducateurs canadiens ont le potentiel d'être améliorées. Mots clés : compétences cognitives des enseignants, littératie, numératie, résolution de problèmes dans des environnements riches en technologie</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>['Seyma Nur Yildirim Erbasli', 'Ying Cui']</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>[['University of Alberta', 'https://ror.org/0160cpw27'], ['University of Alberta', 'https://ror.org/0160cpw27']]</t>
-        </is>
-      </c>
-      <c r="J101" t="n">
-        <v>0</v>
-      </c>
-      <c r="K101" t="b">
-        <v>1</v>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.55016/ojs/ajer.v68i2.71334</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>https://openalex.org/W4221018637</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1080/10790268.2021.1963140</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Perceived eHealth literacy and health literacy among people with spinal cord injury: A cross-sectional study</t>
-        </is>
-      </c>
-      <c r="E102" t="n">
-        <v>2022</v>
-      </c>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>Objectives: This purpose of this research was to (1) to evaluate eHealth and general health literacy levels among individuals with spinal cord injury (SCI) and (2) to identify relationships between eHealth literacy, general health literacy, and various sociodemographic factors.</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>['Gurkaran Singh', 'Bonita Sawatzky', 'Laura Nimmon', 'W. Ben Mortenson']</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>[['University of British Columbia', 'https://ror.org/03rmrcq20'], ['International Collaboration On Repair Discoveries', 'https://ror.org/03ckrg061'], ['GF Strong Rehabilitation Centre', 'https://ror.org/02d4smc03'], ['International Collaboration On Repair Discoveries', 'https://ror.org/03ckrg061'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['International Collaboration On Repair Discoveries', 'https://ror.org/03ckrg061'], ['GF Strong Rehabilitation Centre', 'https://ror.org/02d4smc03']]</t>
-        </is>
-      </c>
-      <c r="J102" t="n">
-        <v>10</v>
-      </c>
-      <c r="K102" t="b">
-        <v>0</v>
-      </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1080/10790268.2021.1963140</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="1" t="n">
-        <v>101</v>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>https://openalex.org/W4221050125</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1007/s42330-022-00196-4</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>The Development and Application of a Public Energy Literacy Instrument</t>
-        </is>
-      </c>
-      <c r="E103" t="n">
-        <v>2022</v>
-      </c>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>['Runa Das', 'Russell Richman']</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>[['Royal Roads University', 'https://ror.org/05w4ste42'], ['Toronto Metropolitan University', 'https://ror.org/05g13zd79']]</t>
-        </is>
-      </c>
-      <c r="J103" t="n">
-        <v>10</v>
-      </c>
-      <c r="K103" t="b">
-        <v>0</v>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1007/s42330-022-00196-4</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="1" t="n">
-        <v>102</v>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>https://openalex.org/W4387169428</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1108/bfj-11-2022-1033</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Identifying individual factors associated with pleasure of eating healthy foods and plant/animal protein food consumption: findings from an exploratory study</t>
-        </is>
-      </c>
-      <c r="E104" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>Purpose This study identifies new factors influencing the adoption of two recently promoted messages in Canada's updated food guide (FG): enhancing pleasure of eating healthy foods (PEHFs) and shifting food choices towards plant protein foods. Currently, limited and contradictory evidence is available regarding associations between environmental values, nutrition literacy, PEHFs, and plant/animal protein food consumption. Design/methodology/approach An online survey measuring environmental values; nutrition literacy, distinctively based on previous (2007) and most recent (2019) FG messages; PEHFs; and annual changes in the consumption of protein foods was sent to Quebec residents (N = 128). Findings Greater nutrition literacy of both 2007 and 2019 FGs and greater environmental values were associated with greater PEHFs (ß = 0.248, p &amp;lt; 0.01; ß = 0.209, p &amp;lt; 0.05; ß = 0.423, p &amp;lt; 0.001, respectively). Greater PEHFs was associated with greater consumption of plant protein foods (ß = 0.405, p &amp;lt; 0.001). Greater nutrition literacy of the 2007 FG was associated with greater consumption of animal protein foods (ß = 0.409, p &amp;lt; 0.001), whereas greater nutrition literacy of the 2019 FG was linked to lower consumption of animal protein foods (ß = −0.225, p &amp;lt; 0.05). Practical implications Enhancing PEHFs may require increasing general FG nutrition literacy and strengthening environmental values. To encourage plant protein food consumption and decrease animal protein food consumption, the authors recommend promoting PEHFs and increasing nutrition literacy based on newest FG recommendations. Originality/value This new evidence may help develop strategies promoting PEHFs and plant protein food consumption, thus increasing uptake of new FG recommendations.</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>['Jessica Lambert-De Francesch', 'JoAnne Labrecque', 'Stéphanie Lessard']</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>[['Université de Montréal', 'https://ror.org/0161xgx34'], ['HEC Montréal', 'https://ror.org/05ww3wq27'], ['Institut National de Santé Publique du Québec', 'https://ror.org/00kv63439']]</t>
-        </is>
-      </c>
-      <c r="J104" t="n">
-        <v>2</v>
-      </c>
-      <c r="K104" t="b">
-        <v>0</v>
-      </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1108/bfj-11-2022-1033</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="1" t="n">
-        <v>103</v>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>https://openalex.org/W4283369041</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/ijerph19137669</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Measuring Health Literacy in Primary Healthcare: Adaptation and Validation of a French-Language Version of the Brief Health Literacy Screening among Patients with Chronic Conditions Seen in Primary Care</t>
-        </is>
-      </c>
-      <c r="E105" t="n">
-        <v>2022</v>
-      </c>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>Background: The Brief Health Literacy Screening (BHLS) is a short self-report instrument developed to identify patients with inadequate health literacy. This study aimed to translate the BHLS into French Canadian (BHLS-FCv) and to evaluate its psychometric properties among patients with chronic conditions in primary care. Methods: The BHLS was translated into French using the Hawkins and Osborne’s method. Content validity was evaluated through cognitive interviews. A validation study of the BHLS-FCv was conducted in two primary care clinics in the province of Quebec (Canada) among adult patients with chronic conditions. Psychometric properties evaluated included: internal consistency (Cronbach’s alpha); test–retest reliability (intraclass correlation coefficient); and concurrent validity (Spearman’s correlations with the Health Literacy Questionnaire (HLQ)). Results: 178 participants completed the questionnaire at baseline and 47 completed the questionnaire two weeks later over the telephone. The average score was 13.3. Cronbach’s alpha for internal consistency was 0.77. The intraclass correlation coefficient for test–retest reliability was 0.69 (95% confidence interval: 0.45–0.83). Concurrent validity with Spearman’s correlation coefficient with three subscales of HLQ ranged from 0.28 to 0.58. Conclusions: The BHLS-FCv demonstrated acceptable psychometric properties and could be used in a population with chronic conditions in primary care.</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>['Maud‐Christine Chouinard', 'Mireille Lambert', 'Mélissa Lavoie', 'Sylvie Lambert', 'Émilie Hudon', 'Olivier Dumont‐Samson', 'Catherine Hudon']</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>[['Université de Montréal', 'https://ror.org/0161xgx34'], ['Centre Intégré Universitaire de Santé et de Services Sociaux du Saguenay–Lac-Saint-Jean', 'https://ror.org/00vbjyq64'], ['Université du Québec à Chicoutimi', 'https://ror.org/00y3hzd62'], ['Université du Québec à Chicoutimi', 'https://ror.org/00y3hzd62'], ['Université de Sherbrooke', 'https://ror.org/00kybxq39'], ['Université de Sherbrooke', 'https://ror.org/00kybxq39'], ['Université de Sherbrooke', 'https://ror.org/00kybxq39']]</t>
-        </is>
-      </c>
-      <c r="J105" t="n">
-        <v>4</v>
-      </c>
-      <c r="K105" t="b">
-        <v>1</v>
-      </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/ijerph19137669</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="1" t="n">
-        <v>104</v>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>https://openalex.org/W4378086619</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/socsci12060315</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Adult Learner Perspectives on Skill- and Life-Based Outcomes Following Literacy Remediation</t>
-        </is>
-      </c>
-      <c r="E106" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>cc-by</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>Using the situated expectancy value theory (SEVT), we explored self-perceived attainment perspectives of adults with low literacy on skill-based (i.e., reading, writing, listening, speaking) and life-based (i.e., management of day-to-day challenges, use of skills in daily living, confidence) improvements following a literacy-focused remediation program. Participants (N = 103; Canadian, urban adults) completed a remediation program for low literacy via one-on-one tutoring over a period of 1 year. Four to six months into the program, participants completed a survey that asked about their perspectives regarding improvements in skill- and life-based areas of functioning. A series of Chi-Square tests provided evidence for self-perceived improvements in skill-based functioning in reading, writing, listening and speaking. Perceived improvements were not noted in areas not targeted by the remediation, namely, math and computer literacy. Further, there was a significant, positive correlation between self-perceived improvement and (1) self-perceived ability to deal with daily challenges, (2) self-reported use of literacy skills in day-to-day activities, and (3) overall confidence. Together, these findings underscore the importance of including activity- and participation-based outcome measures when evaluating adult literacy remediation. In addition, this work demonstrates an application of SEVT to explore changes over time in continuing adult education.</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>['Jacqueline Cummine', 'Amberley Ostevik', 'Kulpreet Cheema', 'Angela Cullum']</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>[['University of Alberta', 'https://ror.org/0160cpw27'], ['Women and Children’s Health Research Institute', 'https://ror.org/03e04kk51'], ['University of Alberta', 'https://ror.org/0160cpw27'], ['University of Alberta', 'https://ror.org/0160cpw27'], ['Women and Children’s Health Research Institute', 'https://ror.org/03e04kk51'], ['University of Alberta', 'https://ror.org/0160cpw27']]</t>
-        </is>
-      </c>
-      <c r="J106" t="n">
-        <v>1</v>
-      </c>
-      <c r="K106" t="b">
-        <v>1</v>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/socsci12060315</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="1" t="n">
-        <v>105</v>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>https://openalex.org/W4200243991</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1080/17408989.2021.2014438</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>PLitPE: an intervention for physical literacy enriched pedagogy in Canadian elementary school physical education classes</t>
-        </is>
-      </c>
-      <c r="E107" t="n">
-        <v>2021</v>
-      </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>Background: Although physical literacy is explicitly defined and integrated into Canadian provincial physical education curricula, limited empirical evidence substantiates the development of physical literacy in elementary physical education. Despite physical education curricular expectations, developing and assessing physical literacy in students may be difficult for teachers with little to no background in physical literacy or physical education.Purpose: The primary purpose was to explore the effect of a curricularly linked physical literacy enriched intervention in elementary school physical education. A secondary purpose involved an examination of the intervention's effects on sex differences.Design: A quasi-experimental controlled intervention trial with a matched comparison group was used to determine the impact of a curricular-based physical literacy enriched physical education intervention on students' development of physical literacy. Teachers (n = 6) and students (n = 131) from four Saskatchewan elementary schools participated in either a PLitPE (experimental) condition or a usual practice (control) condition. The PLitPE intervention was created using learning principles consistent with physical literacy and Self-Determination Theory. PLitPE instructional elements were developed with input from thirteen teachers who were members of the local school division's physical education professional learning community. An embedded professional development model was used where a mentor teacher was present to facilitate and support the implementation of the PLitPE intervention. The Physical Literacy Assessment for Youth tools were used to assess motor competence (PLAYfun), student self-description (PLAYself), and movement participation (PLAYinventory). Each domain of physical literacy (physical competence, psychological, and behavioural) was evaluated using these tools.Results: Significant differences, favouring PLitPE over control, were observed for average motor competence (M = 49.4, M = 40.0, p &lt; 0.001, PLAYfun), movement vocabulary (M = 10.3, M = 7.5, p &lt; 0.001, PLAYfun), environmental participation (M = 423.9, M = 390.1, p &lt; 0.05, PLAYself), and a reduction of sex differences on average motor competence and movement vocabulary. Statistically significant relationships with low to fair correlations between PLAYfun and PLAYself variables existed.Conclusions: This study provides empirical evidence supporting physical literacy enriched physical education. PLitPE developed the psychological domain (affective and cognitive) and significantly improved physical competence, however, the intervention did not manifest in improved behaviour. Concerning sex differences, the intervention yielded an equal and substantive improvement in both males and females in the intervention group. Future studies should consider the addition of reflective approaches, as well as the construction of positive challenges for children.</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>['Alexandra L. Stoddart', 'M. Louise Humbert', 'Serene Kerpan', 'Nicole Cameron', 'Dean Kriellaars']</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>[['University of Regina', 'https://ror.org/03dzc0485'], ['University of Saskatchewan', 'https://ror.org/010x8gc63'], ['University of Saskatchewan', 'https://ror.org/010x8gc63'], ['University of Saskatchewan', 'https://ror.org/010x8gc63'], ['University of Ontario Institute of Technology', 'https://ror.org/016zre027'], ['University of Saskatchewan', 'https://ror.org/010x8gc63'], ['Saskatoon City Hospital', 'https://ror.org/0390t1205'], ['University of Manitoba', 'https://ror.org/02gfys938']]</t>
-        </is>
-      </c>
-      <c r="J107" t="n">
-        <v>10</v>
-      </c>
-      <c r="K107" t="b">
-        <v>0</v>
-      </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1080/17408989.2021.2014438</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="1" t="n">
-        <v>106</v>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>https://openalex.org/W4226055404</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1080/14635240.2022.2059543</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>A cross-sectional study to assess health literacy levels among Canadian post-secondary students during the COVID-19 pandemic</t>
-        </is>
-      </c>
-      <c r="E108" t="n">
-        <v>2022</v>
-      </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>To better understand the online information-seeking behaviors and health literacy levels of Canadian post-secondary students, a cross-sectional online bilingual survey was initiated during the first wave of COVID-19 in Canada. The survey was administered to Canadian post-secondary students from 1 July 2020, to 30 September 2020, through email invitations and social media platforms. The objective of this paper is to assess the online information-seeking behaviors and health literacy levels in relation to the coronavirus of Canadian post-secondary students during the COVID-19 pandemic. The online survey was developed using standardized tools, including the Digital Health Literacy Instrument, and newly developed measures of sociodemographic indicators and the information satisfaction scale. Sociodemographic factors and health literacy levels were analyzed using descriptive statistics. A total of 2,679 students partihigh levels of health literacy and could easily access online information related to COVID-19 to make health decisions. The most frequently used sources to obtain information about the coronavirus were search engines and websites of public sector agencies. While the majority of respondents found it easy to access and utilize online health information, continued development of these resources is vital to reducing the spread of COVID-19 and addressing misinformation. Accurate and well-maintained online resources are key preventative health measures to educate the public and ultimately lessen the burden on our healthcare system.</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>['Simran Purewal', 'Paola Ardiles', 'Erica Di Ruggiero', 'Hussein Elhagehassan', 'John Flores', 'Sana Mahmood']</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>[['Simon Fraser University', 'https://ror.org/0213rcc28'], ['Simon Fraser University', 'https://ror.org/0213rcc28'], ['Public Health Ontario', 'https://ror.org/025z8ah66'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['Simon Fraser University', 'https://ror.org/0213rcc28'], ['Simon Fraser University', 'https://ror.org/0213rcc28'], ['University of Toronto', 'https://ror.org/03dbr7087']]</t>
-        </is>
-      </c>
-      <c r="J108" t="n">
-        <v>2</v>
-      </c>
-      <c r="K108" t="b">
-        <v>0</v>
-      </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1080/14635240.2022.2059543</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="1" t="n">
-        <v>107</v>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>https://openalex.org/W4365452341</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/children10040720</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Piloting the Virtual PLAYshop Program: A Parent-Focused Physical Literacy Intervention for Early Childhood</t>
-        </is>
-      </c>
-      <c r="E109" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>cc-by</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>The PLAYshop program is a parent-focused physical literacy intervention for early childhood. This single-group mixed-methods pilot study aimed to explore the feasibility of virtually delivering and assessing the PLAYshop program. The virtual PLAYshop program included a virtual workshop, resources/basic equipment, and two booster emails (3-week and 6-week follow-up). Data on 34 preschool-aged children (3-5 years) and their parents from Edmonton and Victoria, Canada, were collected via an online questionnaire, virtual assessment session, and interview at single or multiple time points (baseline, post-workshop, 2-month follow-up). Intraclass correlation coefficients (ICCs), paired t-tests, repeated measures ANOVAs, and thematic analyses were conducted. Regarding feasibility, most parents (≥94%) were satisfied/extremely satisfied with the virtual workshop and planned to continue physical literacy activities post-workshop. The virtual assessment protocol for children's fundamental movement skills (FMS; overhand throw, underhand throw, horizontal jump, hop, one-leg balance) was feasible, with high completion rates (&gt;90%) and reliable scoring (ICC = 0.79-0.99). For positive changes in potential outcomes, a medium effect size was observed for children's hopping skills (d = 0.54), and large effect sizes were observed for several parental outcomes (partial η2 = 0.20-0.54). The findings support the feasibility and potential positive outcomes of the virtual PLAYshop program. A larger randomized controlled efficacy trial is recommended.</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>['Yeongho Hwang', 'Madison Boyd', 'Patti‐Jean Naylor', 'Ryan E. Rhodes', 'Sam Liu', 'Ramiah Moldenhauer', 'Qiang Li', 'Christopher I. Wright', 'E. Jean Buckler', 'Valerie Carson']</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>[['University of Alberta', 'https://ror.org/0160cpw27'], ['University of Alberta', 'https://ror.org/0160cpw27'], ['University of Victoria', 'https://ror.org/04s5mat29'], ['University of Victoria', 'https://ror.org/04s5mat29'], ['University of Victoria', 'https://ror.org/04s5mat29'], ['University of Alberta', 'https://ror.org/0160cpw27'], ['University of Alberta', 'https://ror.org/0160cpw27'], ['University of Victoria', 'https://ror.org/04s5mat29'], ['University of Victoria', 'https://ror.org/04s5mat29'], ['University of Alberta', 'https://ror.org/0160cpw27']]</t>
-        </is>
-      </c>
-      <c r="J109" t="n">
-        <v>5</v>
-      </c>
-      <c r="K109" t="b">
-        <v>1</v>
-      </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/children10040720</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="1" t="n">
-        <v>108</v>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>https://openalex.org/W4211052767</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.ssmph.2022.101038</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Literacy and self-rated health: Analysis of the Longitudinal and International Study of Adults (LISA)</t>
-        </is>
-      </c>
-      <c r="E110" t="n">
-        <v>2022</v>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>cc-by-nc-nd</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>The relationship between education and health is well-established. The empirical literature finds that individuals with higher levels of education experience lower risks of poor health outcomes compared to individuals with less education. Outstanding to this literature is the examination of a dimension of education - literacy - and its association with health. The objective of this study was to examine the relationship between literacy (reading, numeracy) and health (self-reported health). We use data from the 2012 wave of the Canadian Longitudinal International Survey of Adults (LISA). The LISA includes rich information on health, broader sociodemographic characteristics (income, age, sex, etc.) as well as information on literacy skills from the Program for International Assessment of Adult Competencies (PIAAC). Using logistic regression, we first reaffirm the association between education and self-reported health. We then find that after controlling for measures of literacy, understood as proficiency in reading and numeracy, the magnitude of effect of education on health is reduced. Skills in literacy reduce the risk of reporting poor health, but only for the older subset of respondents (ages 40-65). Our results suggest that literacy should not be understated in empirical research on education and health, and in fact serve to sharpen our understanding of how education impacts health by drawing attention to indirect pathways.</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>['Emma M. Macdonald', 'Emmanuelle Arpin', 'Amélie Quesnel‐Vallée']</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>[['McGill University', 'https://ror.org/01pxwe438'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['McGill University', 'https://ror.org/01pxwe438']]</t>
-        </is>
-      </c>
-      <c r="J110" t="n">
-        <v>1</v>
-      </c>
-      <c r="K110" t="b">
-        <v>1</v>
-      </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.ssmph.2022.101038</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="1" t="n">
-        <v>109</v>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>https://openalex.org/W4327598178</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3389/fspor.2023.1125072</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>A cross-sectional study of Canadian children's valuation of literacies across social contexts</t>
-        </is>
-      </c>
-      <c r="E111" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>cc-by</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>Children, on average, do not engage in sufficient physical activity to reap the physical, mental, and social health benefits. Understanding the value that children place on movement across social contexts, and the relative ranking of this valuation, may help us to understand and intervene on activity levels.This exploratory study examined the valuation of reading/writing, math, and movement across three social contexts (school, home, with friends) among children 6-13 years of age (N = 7,845; 51.3% male). Subjective task values across contexts were assessed with the valuing literacies subscale of the PLAYself. One-way Kruskal-Wallis ANOVAs were performed to test for differences between contexts and between literacies, respectively.Sex differences and age-related variation were explored. Valuations of reading/writing (d = 1.16) and math (d = 1.33) decreased across context (school &gt; family &gt; friend), while the valuation of movement was relatively stable (d = 0.26). Valuations differed substantially with friends (p &lt; 0.001, d = 1.03). Sex dependent effect sizes were minimal (d = 0.05-0.11).Movement is highly valued by children across social contexts; thus, programming across contexts should be prioritized to align with their valuation.</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>['Emily Bremer', 'Philip Jefferies', 'John Cairney', 'Dean Kriellaars']</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>[['Acadia University', 'https://ror.org/00839we02'], ['Dalhousie University', 'https://ror.org/01e6qks80'], ['The University of Queensland', 'https://ror.org/00rqy9422'], ['University of Manitoba', 'https://ror.org/02gfys938']]</t>
-        </is>
-      </c>
-      <c r="J111" t="n">
-        <v>5</v>
-      </c>
-      <c r="K111" t="b">
-        <v>1</v>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3389/fspor.2023.1125072</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="1" t="n">
-        <v>110</v>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>https://openalex.org/W4391613780</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1186/s40561-024-00293-x</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Navigating the digital world: development of an evidence-based digital literacy program and assessment tool for youth</t>
-        </is>
-      </c>
-      <c r="E112" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>cc-by</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>Abstract The rapid expansion of digital connectivity has provided youth with wide-ranging access to digital platforms for communication, entertainment, and education. In light of this profound shift, there have been growing concerns about online safety, data privacy, and cybersecurity. A critical factor influencing the ability of youth to responsibly navigate digital platforms is digital literacy. While digital literacy programs have been implemented in various regions worldwide, significant disparities remain not only in overall digital literacy levels, but also the assessment of digital literacy initiatives. To address these challenges, an environmental scan and literature review were conducted to identify existing digital literacy programs in Canada developed specifically for youth, as well as digital literacy assessment tools, respectively. The search encompassed peer-reviewed articles, organizational curricula, and assessment measures indexed in various databases and organization websites. The environmental scan identified 15 programs targeting key components of digital literacy such as data safety, cyberbullying, and digital media. The literature review identified 12 digital literacy assessment tools. Based on the findings, data were synthesized from shortlisted programs and assessment tools to inform the development of both a new digital literacy program and assessment tool to complement the youth-focused program. The new program focuses on four key components: (1) digital fluency, (2) digital privacy and safety, (3) ethics and empathy, and (4) consumer awareness. A 15-item assessment tool was also developed consisting of 4–5 questions specific to each program component. Given the growing importance of digital competencies, a youth-focused program and assessment tool are crucial for understanding and addressing digital literacy among this vulnerable cohort. This program's adaptability allows for customization across sociodemographic target groups, including culturally diverse and geographically remote communities—an aspect that has the potential to enhance digital literacy across settings. Implementing digital literacy programs can better prepare youth for an increasingly digital world, while minimizing potential risks associated with technology use.</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>['M. Claire Buchan', 'Jasmin Bhawra', 'Tarun Reddy Katapally']</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>[['University of Waterloo', 'https://ror.org/01aff2v68'], ['Toronto Metropolitan University', 'https://ror.org/05g13zd79'], ['Western University', 'https://ror.org/02grkyz14']]</t>
-        </is>
-      </c>
-      <c r="J112" t="n">
-        <v>16</v>
-      </c>
-      <c r="K112" t="b">
-        <v>1</v>
-      </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1186/s40561-024-00293-x</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="1" t="n">
-        <v>111</v>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>https://openalex.org/W4383710507</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1007/s11136-023-03447-5</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Measuring skill-based health literacy in chronic airway disease patients: the development and psychometric evaluation of the Vancouver airways health literacy tool (VAHLT)</t>
-        </is>
-      </c>
-      <c r="E113" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>['Richard E. Hohn', 'Jacek A. Kopec', 'Richard Sawatzky', 'Iraj Poureslami', 'J. Mark FitzGerald']</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>[['Simon Fraser University', 'https://ror.org/0213rcc28'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['Trinity Western University', 'https://ror.org/01j2kd606'], ['Centre for Health Evaluation and Outcome Sciences', 'https://ror.org/04g6gva85'], ['Western University', 'https://ror.org/02grkyz14'], ['Providence Health Care', 'https://ror.org/03qqdf793'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['Vancouver Native Health Society', 'https://ror.org/04k296d46'], ['Vancouver Coastal Health', 'https://ror.org/03bd8jh67'], ['Vancouver Coastal Health Research Institute', 'https://ror.org/04htzww22'], ['Vancouver Coastal Health', 'https://ror.org/03bd8jh67'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['Vancouver Coastal Health Research Institute', 'https://ror.org/04htzww22']]</t>
-        </is>
-      </c>
-      <c r="J113" t="n">
-        <v>0</v>
-      </c>
-      <c r="K113" t="b">
-        <v>0</v>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1007/s11136-023-03447-5</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="1" t="n">
-        <v>112</v>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>https://openalex.org/W4309495336</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.4187/respcare.10441</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>Evaluation of a New Performance-Based Health Literacy Measurement Tool for Individuals With Chronic Airways Disease</t>
-        </is>
-      </c>
-      <c r="E114" t="n">
-        <v>2022</v>
-      </c>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>&lt;h3&gt;BACKGROUND:&lt;/h3&gt; Low health literacy is a global challenge. Health literacy is positively correlated with chronic airways diseas&lt;b&gt;e&lt;/b&gt; desirable outcomes. Despite the importance of health literacy in disease management, current health literacy measurement tools are suboptimal. As part of a multi-stage project to develop a performance-based, disease-specific Vancouver Airways Health Literacy Tool (VAHLT) for individuals with chronic airways disease, this study assessed the relationships between the VAHLT scores and characteristics of patients with chronic airways disease. The primary aim of the study was to provide preliminary evidence of construct validity of the VAHLT. &lt;h3&gt;METHODS:&lt;/h3&gt; A cross-sectional study design was applied. Study subjects were recruited from 6 specialty care clinics to complete the VAHLT measurement tool. Demographic and clinical data, including quality of life and disease control, were collected via validated questionnaires. The study subjects also completed a spirometry test. Inferential analysis was conducted by using mean difference testing and correlational methods. &lt;h3&gt;RESULTS:&lt;/h3&gt; A total of 320 subjects were recruited, and, after imputing missing data, 315 were ultimately analyzed. The subjects were predominantly women (61%), white (83%), had a post–high-school education (74%), and a mean ± SD age of 65.2 ± 13.2 y. Age was significantly negatively correlated with the VAHLT scores (&lt;i&gt;P&lt;/i&gt; = .004); the subjects with a post–high school education had significantly higher VAHLT scores than those with a high school education or less (&lt;i&gt;P&lt;/i&gt; &amp;lt; .001). No significant sex or ethnicity related differences in VAHLT scores were observed. For clinical outcomes, no significant differences were found between the VAHLT scores and disease severity or measures of quality of life and asthma control. &lt;h3&gt;CONCLUSIONS:&lt;/h3&gt; We report a chronic airways disease–specific health literacy measurement tool developed with the involvement of patients and professionals. Age and education were highly correlated with health literacy, which emphasizes the importance of addressing these factors in health literacy interventions among patients with chronic airways disease.</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>['Iraj Poureslami', 'Ric E Hohn', 'Jacek A. Kopec', 'Richard Sawatzky', 'Shawn D. Aaron', 'Samir Gupta', 'Roger Goldstein', 'Louis‐Philippe Boulet', 'Noah Tregobov', 'Jessica Shum']</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>[['University of British Columbia', 'https://ror.org/03rmrcq20'], ['Vancouver Coastal Health Research Institute', 'https://ror.org/04htzww22'], ['Vancouver Native Health Society', 'https://ror.org/04k296d46'], ['Vancouver Coastal Health', 'https://ror.org/03bd8jh67'], ['Simon Fraser University', 'https://ror.org/0213rcc28'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['Trinity Western University', 'https://ror.org/01j2kd606'], ['Western University', 'https://ror.org/02grkyz14'], ['University of Ottawa', 'https://ror.org/03c4mmv16'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['West Park Healthcare Centre', 'https://ror.org/037y13578'], ['University of Toronto', 'https://ror.org/03dbr7087'], ['Université Laval', 'https://ror.org/04sjchr03'], ['Vancouver Coastal Health', 'https://ror.org/03bd8jh67'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['Vancouver Coastal Health Research Institute', 'https://ror.org/04htzww22'], ['Vancouver Coastal Health', 'https://ror.org/03bd8jh67'], ['University of British Columbia', 'https://ror.org/03rmrcq20'], ['Vancouver Coastal Health Research Institute', 'https://ror.org/04htzww22']]</t>
-        </is>
-      </c>
-      <c r="J114" t="n">
-        <v>1</v>
-      </c>
-      <c r="K114" t="b">
-        <v>0</v>
-      </c>
-      <c r="L114" t="inlineStr">
         <is>
           <t>https://doi.org/10.4187/respcare.10441</t>
         </is>
